--- a/flask_backend/test_output/result_table_v2.xlsx
+++ b/flask_backend/test_output/result_table_v2.xlsx
@@ -3078,7 +3078,7 @@
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -3373,7 +3373,7 @@
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -3403,7 +3403,7 @@
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -7389,7 +7389,7 @@
     <row r="240" ht="14" customHeight="1">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
@@ -7719,7 +7719,7 @@
     <row r="251" ht="14" customHeight="1">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
@@ -7779,7 +7779,7 @@
     <row r="253" ht="14" customHeight="1">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -7809,7 +7809,7 @@
     <row r="254" ht="14" customHeight="1">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
@@ -7895,7 +7895,7 @@
     <row r="257" ht="14" customHeight="1">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <row r="258" ht="14" customHeight="1">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="279" ht="14" customHeight="1">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -8876,7 +8876,7 @@
     <row r="291" ht="14" customHeight="1">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -11795,7 +11795,7 @@
     <row r="395" ht="14" customHeight="1">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B395" s="5" t="inlineStr">
@@ -11825,7 +11825,7 @@
     <row r="396" ht="14" customHeight="1">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B396" s="5" t="inlineStr">
@@ -11855,7 +11855,7 @@
     <row r="397" ht="14" customHeight="1">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
@@ -11885,7 +11885,7 @@
     <row r="398" ht="14" customHeight="1">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B398" s="5" t="inlineStr">
@@ -11915,7 +11915,7 @@
     <row r="399" ht="14" customHeight="1">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B399" s="5" t="inlineStr">
@@ -11945,7 +11945,7 @@
     <row r="400" ht="14" customHeight="1">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B400" s="5" t="inlineStr">
@@ -11975,7 +11975,7 @@
     <row r="401" ht="14" customHeight="1">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B401" s="5" t="inlineStr">
@@ -12005,7 +12005,7 @@
     <row r="402" ht="14" customHeight="1">
       <c r="A402" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B402" s="5" t="inlineStr">
@@ -12035,7 +12035,7 @@
     <row r="403" ht="14" customHeight="1">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B403" s="5" t="inlineStr">
@@ -12065,7 +12065,7 @@
     <row r="404" ht="14" customHeight="1">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B404" s="5" t="inlineStr">
@@ -12147,7 +12147,7 @@
     <row r="407" ht="14" customHeight="1">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B407" s="5" t="inlineStr">
@@ -12177,7 +12177,7 @@
     <row r="408" ht="14" customHeight="1">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B408" s="5" t="inlineStr">
@@ -12207,7 +12207,7 @@
     <row r="409" ht="14" customHeight="1">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B409" s="5" t="inlineStr">
@@ -12237,7 +12237,7 @@
     <row r="410" ht="14" customHeight="1">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B410" s="5" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="411" ht="14" customHeight="1">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B411" s="5" t="inlineStr">
@@ -12297,7 +12297,7 @@
     <row r="412" ht="14" customHeight="1">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B412" s="5" t="inlineStr">
@@ -12327,7 +12327,7 @@
     <row r="413" ht="14" customHeight="1">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B413" s="5" t="inlineStr">
@@ -12357,7 +12357,7 @@
     <row r="414" ht="14" customHeight="1">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B414" s="5" t="inlineStr">
@@ -12387,7 +12387,7 @@
     <row r="415" ht="14" customHeight="1">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B415" s="5" t="inlineStr">
@@ -12417,7 +12417,7 @@
     <row r="416" ht="14" customHeight="1">
       <c r="A416" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B416" s="5" t="inlineStr">
@@ -12447,7 +12447,7 @@
     <row r="417" ht="14" customHeight="1">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B417" s="5" t="inlineStr">
@@ -12477,7 +12477,7 @@
     <row r="418" ht="14" customHeight="1">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B418" s="5" t="inlineStr">
@@ -12507,7 +12507,7 @@
     <row r="419" ht="14" customHeight="1">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B419" s="5" t="inlineStr">
@@ -12537,7 +12537,7 @@
     <row r="420" ht="14" customHeight="1">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B420" s="5" t="inlineStr">
@@ -12567,7 +12567,7 @@
     <row r="421" ht="14" customHeight="1">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B421" s="5" t="inlineStr">
@@ -12597,7 +12597,7 @@
     <row r="422" ht="14" customHeight="1">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B422" s="5" t="inlineStr">
@@ -12627,7 +12627,7 @@
     <row r="423" ht="14" customHeight="1">
       <c r="A423" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B423" s="5" t="inlineStr">
@@ -12657,7 +12657,7 @@
     <row r="424" ht="14" customHeight="1">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B424" s="5" t="inlineStr">
@@ -12687,7 +12687,7 @@
     <row r="425" ht="14" customHeight="1">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B425" s="5" t="inlineStr">
@@ -12717,7 +12717,7 @@
     <row r="426" ht="14" customHeight="1">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B426" s="5" t="inlineStr">
@@ -12747,7 +12747,7 @@
     <row r="427" ht="14" customHeight="1">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B427" s="5" t="inlineStr">
@@ -12807,7 +12807,7 @@
     <row r="429" ht="14" customHeight="1">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B429" s="5" t="inlineStr">
@@ -12837,7 +12837,7 @@
     <row r="430" ht="14" customHeight="1">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B430" s="5" t="inlineStr">
@@ -12893,7 +12893,7 @@
     <row r="432" ht="14" customHeight="1">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B432" s="5" t="inlineStr">
@@ -12923,7 +12923,7 @@
     <row r="433" ht="14" customHeight="1">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B433" s="5" t="inlineStr">
@@ -13005,7 +13005,7 @@
     <row r="436" ht="14" customHeight="1">
       <c r="A436" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B436" s="5" t="inlineStr">
@@ -13035,7 +13035,7 @@
     <row r="437" ht="14" customHeight="1">
       <c r="A437" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B437" s="5" t="inlineStr">
@@ -13065,7 +13065,7 @@
     <row r="438" ht="14" customHeight="1">
       <c r="A438" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B438" s="5" t="inlineStr">
@@ -13184,7 +13184,7 @@
     <row r="443" ht="14" customHeight="1">
       <c r="A443" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B443" s="5" t="inlineStr">
@@ -13214,7 +13214,7 @@
     <row r="444" ht="14" customHeight="1">
       <c r="A444" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B444" s="5" t="inlineStr">
@@ -13244,7 +13244,7 @@
     <row r="445" ht="14" customHeight="1">
       <c r="A445" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B445" s="5" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="447" ht="14" customHeight="1">
       <c r="A447" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B447" s="5" t="inlineStr">
@@ -13334,7 +13334,7 @@
     <row r="448" ht="14" customHeight="1">
       <c r="A448" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B448" s="5" t="inlineStr">
@@ -13364,7 +13364,7 @@
     <row r="449" ht="14" customHeight="1">
       <c r="A449" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B449" s="5" t="inlineStr">
@@ -13394,7 +13394,7 @@
     <row r="450" ht="14" customHeight="1">
       <c r="A450" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B450" s="5" t="inlineStr">
@@ -21850,7 +21850,7 @@
     <row r="179" ht="14" customHeight="1">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B179" s="5" t="inlineStr">
@@ -21878,7 +21878,7 @@
     <row r="180" ht="14" customHeight="1">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B180" s="5" t="inlineStr">
@@ -21906,7 +21906,7 @@
     <row r="181" ht="14" customHeight="1">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B181" s="5" t="inlineStr">
@@ -21934,7 +21934,7 @@
     <row r="182" ht="14" customHeight="1">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B182" s="5" t="inlineStr">
@@ -21964,7 +21964,7 @@
     <row r="183" ht="14" customHeight="1">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B183" s="5" t="inlineStr">
@@ -21994,7 +21994,7 @@
     <row r="184" ht="14" customHeight="1">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B184" s="5" t="inlineStr">
@@ -22024,7 +22024,7 @@
     <row r="185" ht="14" customHeight="1">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B185" s="5" t="inlineStr">
@@ -22054,7 +22054,7 @@
     <row r="186" ht="14" customHeight="1">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B186" s="5" t="inlineStr">
@@ -22084,7 +22084,7 @@
     <row r="187" ht="14" customHeight="1">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B187" s="5" t="inlineStr">
@@ -22114,7 +22114,7 @@
     <row r="188" ht="14" customHeight="1">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B188" s="5" t="inlineStr">
@@ -22144,7 +22144,7 @@
     <row r="189" ht="14" customHeight="1">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B189" s="5" t="inlineStr">
@@ -22172,7 +22172,7 @@
     <row r="190" ht="14" customHeight="1">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B190" s="5" t="inlineStr">
@@ -22202,7 +22202,7 @@
     <row r="191" ht="14" customHeight="1">
       <c r="A191" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B191" s="5" t="inlineStr">
@@ -22230,7 +22230,7 @@
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -22258,7 +22258,7 @@
     <row r="193" ht="14" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
@@ -22286,7 +22286,7 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -22314,7 +22314,7 @@
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
@@ -22344,7 +22344,7 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
@@ -22374,7 +22374,7 @@
     <row r="197" ht="14" customHeight="1">
       <c r="A197" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B197" s="5" t="inlineStr">
@@ -22404,7 +22404,7 @@
     <row r="198" ht="14" customHeight="1">
       <c r="A198" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B198" s="5" t="inlineStr">
@@ -22434,7 +22434,7 @@
     <row r="199" ht="14" customHeight="1">
       <c r="A199" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B199" s="5" t="inlineStr">
@@ -22464,7 +22464,7 @@
     <row r="200" ht="14" customHeight="1">
       <c r="A200" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B200" s="5" t="inlineStr">
@@ -22494,7 +22494,7 @@
     <row r="201" ht="14" customHeight="1">
       <c r="A201" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B201" s="5" t="inlineStr">
@@ -22524,7 +22524,7 @@
     <row r="202" ht="14" customHeight="1">
       <c r="A202" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B202" s="5" t="inlineStr">
@@ -22552,7 +22552,7 @@
     <row r="203" ht="14" customHeight="1">
       <c r="A203" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B203" s="5" t="inlineStr">
@@ -22580,7 +22580,7 @@
     <row r="204" ht="14" customHeight="1">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">

--- a/flask_backend/test_output/result_table_v2.xlsx
+++ b/flask_backend/test_output/result_table_v2.xlsx
@@ -651,7 +651,7 @@
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -711,7 +711,7 @@
     <row r="6" ht="14" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2C</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1011,7 +1011,7 @@
     <row r="16" ht="14" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="17" ht="14" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1071,7 +1071,7 @@
     <row r="18" ht="14" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -1131,7 +1131,7 @@
     <row r="20" ht="14" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1159,7 +1159,11 @@
       </c>
     </row>
     <row r="21" ht="14" customHeight="1">
-      <c r="A21" s="11" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t>CODECHAOS 27</t>
@@ -1217,7 +1221,7 @@
     <row r="23" ht="14" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1307,7 +1311,7 @@
     <row r="26" ht="14" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1337,7 +1341,7 @@
     <row r="27" ht="14" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1367,7 +1371,7 @@
     <row r="28" ht="14" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>1C</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
@@ -1397,7 +1401,7 @@
     <row r="29" ht="14" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>1B</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
@@ -1697,7 +1701,7 @@
     <row r="39" ht="14" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>1B</t>
+          <t>1A</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -1845,7 +1849,11 @@
       </c>
     </row>
     <row r="44" ht="14" customHeight="1">
-      <c r="A44" s="11" t="inlineStr"/>
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -1871,7 +1879,11 @@
       </c>
     </row>
     <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="11" t="inlineStr"/>
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -1897,7 +1909,11 @@
       </c>
     </row>
     <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="11" t="inlineStr"/>
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>1A</t>
+        </is>
+      </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -2560,7 +2576,11 @@
       </c>
     </row>
     <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="11" t="inlineStr"/>
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
           <t>MEGARIDE F50</t>
@@ -2826,7 +2846,11 @@
       </c>
     </row>
     <row r="78" ht="14" customHeight="1">
-      <c r="A78" s="11" t="inlineStr"/>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
           <t>MEGARIDE F50</t>
@@ -2882,7 +2906,11 @@
       </c>
     </row>
     <row r="80" ht="14" customHeight="1">
-      <c r="A80" s="11" t="inlineStr"/>
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
           <t>GHOST SPRINT BOOT W</t>
@@ -2908,7 +2936,11 @@
       </c>
     </row>
     <row r="81" ht="14" customHeight="1">
-      <c r="A81" s="11" t="inlineStr"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
           <t>GHOST SPRINT BOOT W</t>
@@ -3024,7 +3056,11 @@
       </c>
     </row>
     <row r="85" ht="14" customHeight="1">
-      <c r="A85" s="11" t="inlineStr"/>
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -3050,7 +3086,11 @@
       </c>
     </row>
     <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="11" t="inlineStr"/>
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -3078,7 +3118,7 @@
     <row r="87" ht="14" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="B87" s="5" t="inlineStr">
@@ -3226,7 +3266,11 @@
       </c>
     </row>
     <row r="92" ht="14" customHeight="1">
-      <c r="A92" s="11" t="inlineStr"/>
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -3252,7 +3296,11 @@
       </c>
     </row>
     <row r="93" ht="14" customHeight="1">
-      <c r="A93" s="11" t="inlineStr"/>
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -3278,7 +3326,11 @@
       </c>
     </row>
     <row r="94" ht="14" customHeight="1">
-      <c r="A94" s="11" t="inlineStr"/>
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -3343,7 +3395,7 @@
     <row r="97" ht="14" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B97" s="5" t="inlineStr">
@@ -3373,7 +3425,7 @@
     <row r="98" ht="14" customHeight="1">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B98" s="5" t="inlineStr">
@@ -3403,7 +3455,7 @@
     <row r="99" ht="14" customHeight="1">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B99" s="5" t="inlineStr">
@@ -3431,7 +3483,11 @@
       </c>
     </row>
     <row r="100" ht="14" customHeight="1">
-      <c r="A100" s="11" t="inlineStr"/>
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
           <t>OZWEEGO J</t>
@@ -3459,7 +3515,7 @@
     <row r="101" ht="14" customHeight="1">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B101" s="5" t="inlineStr">
@@ -3489,7 +3545,7 @@
     <row r="102" ht="14" customHeight="1">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B102" s="5" t="inlineStr">
@@ -3549,7 +3605,7 @@
     <row r="104" ht="14" customHeight="1">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="B104" s="5" t="inlineStr">
@@ -3579,7 +3635,7 @@
     <row r="105" ht="14" customHeight="1">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="B105" s="5" t="inlineStr">
@@ -3609,7 +3665,7 @@
     <row r="106" ht="14" customHeight="1">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="B106" s="5" t="inlineStr">
@@ -3759,7 +3815,7 @@
     <row r="111" ht="14" customHeight="1">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>3A</t>
         </is>
       </c>
       <c r="B111" s="5" t="inlineStr">
@@ -3819,7 +3875,7 @@
     <row r="113" ht="14" customHeight="1">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B113" s="5" t="inlineStr">
@@ -3847,7 +3903,11 @@
       </c>
     </row>
     <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="11" t="inlineStr"/>
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -3875,7 +3935,7 @@
     <row r="115" ht="14" customHeight="1">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B115" s="5" t="inlineStr">
@@ -3995,7 +4055,7 @@
     <row r="119" ht="14" customHeight="1">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B119" s="5" t="inlineStr">
@@ -4025,7 +4085,7 @@
     <row r="120" ht="14" customHeight="1">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>3B</t>
         </is>
       </c>
       <c r="B120" s="5" t="inlineStr">
@@ -4053,7 +4113,11 @@
       </c>
     </row>
     <row r="121" ht="14" customHeight="1">
-      <c r="A121" s="11" t="inlineStr"/>
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -4139,7 +4203,11 @@
       </c>
     </row>
     <row r="124" ht="14" customHeight="1">
-      <c r="A124" s="11" t="inlineStr"/>
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -4165,7 +4233,11 @@
       </c>
     </row>
     <row r="125" ht="14" customHeight="1">
-      <c r="A125" s="11" t="inlineStr"/>
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -4191,7 +4263,11 @@
       </c>
     </row>
     <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="11" t="inlineStr"/>
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -4217,7 +4293,11 @@
       </c>
     </row>
     <row r="127" ht="14" customHeight="1">
-      <c r="A127" s="11" t="inlineStr"/>
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -4243,7 +4323,11 @@
       </c>
     </row>
     <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="11" t="inlineStr"/>
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>3A</t>
+        </is>
+      </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -4278,7 +4362,7 @@
     <row r="130" ht="14" customHeight="1">
       <c r="A130" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B130" s="5" t="inlineStr">
@@ -4338,7 +4422,7 @@
     <row r="132" ht="14" customHeight="1">
       <c r="A132" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>5B</t>
         </is>
       </c>
       <c r="B132" s="5" t="inlineStr">
@@ -4366,7 +4450,11 @@
       </c>
     </row>
     <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="11" t="inlineStr"/>
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
           <t>SL 72 RTN</t>
@@ -4452,7 +4540,11 @@
       </c>
     </row>
     <row r="136" ht="14" customHeight="1">
-      <c r="A136" s="11" t="inlineStr"/>
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
           <t>SL 72 RS</t>
@@ -4628,7 +4720,11 @@
       </c>
     </row>
     <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="11" t="inlineStr"/>
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
           <t>SL 72 RS</t>
@@ -4656,7 +4752,7 @@
     <row r="143" ht="14" customHeight="1">
       <c r="A143" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B143" s="5" t="inlineStr">
@@ -4686,7 +4782,7 @@
     <row r="144" ht="14" customHeight="1">
       <c r="A144" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B144" s="5" t="inlineStr">
@@ -4716,7 +4812,7 @@
     <row r="145" ht="14" customHeight="1">
       <c r="A145" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B145" s="5" t="inlineStr">
@@ -4746,7 +4842,7 @@
     <row r="146" ht="14" customHeight="1">
       <c r="A146" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B146" s="5" t="inlineStr">
@@ -4776,7 +4872,7 @@
     <row r="147" ht="14" customHeight="1">
       <c r="A147" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B147" s="5" t="inlineStr">
@@ -4806,7 +4902,7 @@
     <row r="148" ht="14" customHeight="1">
       <c r="A148" s="4" t="inlineStr">
         <is>
-          <t>3B</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B148" s="5" t="inlineStr">
@@ -4924,7 +5020,11 @@
       </c>
     </row>
     <row r="152" ht="14" customHeight="1">
-      <c r="A152" s="11" t="inlineStr"/>
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -4952,7 +5052,7 @@
     <row r="153" ht="14" customHeight="1">
       <c r="A153" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>5C</t>
         </is>
       </c>
       <c r="B153" s="5" t="inlineStr">
@@ -5070,7 +5170,11 @@
       </c>
     </row>
     <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="11" t="inlineStr"/>
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5098,7 +5202,7 @@
     <row r="158" ht="14" customHeight="1">
       <c r="A158" s="4" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B158" s="5" t="inlineStr">
@@ -5128,7 +5232,7 @@
     <row r="159" ht="14" customHeight="1">
       <c r="A159" s="4" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B159" s="5" t="inlineStr">
@@ -5218,7 +5322,7 @@
     <row r="162" ht="14" customHeight="1">
       <c r="A162" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>5B</t>
         </is>
       </c>
       <c r="B162" s="5" t="inlineStr">
@@ -5246,7 +5350,11 @@
       </c>
     </row>
     <row r="163" ht="14" customHeight="1">
-      <c r="A163" s="11" t="inlineStr"/>
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -5302,7 +5410,11 @@
       </c>
     </row>
     <row r="165" ht="14" customHeight="1">
-      <c r="A165" s="11" t="inlineStr"/>
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
           <t>SL 72 RS</t>
@@ -5330,7 +5442,7 @@
     <row r="166" ht="14" customHeight="1">
       <c r="A166" s="4" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B166" s="5" t="inlineStr">
@@ -5360,7 +5472,7 @@
     <row r="167" ht="14" customHeight="1">
       <c r="A167" s="4" t="inlineStr">
         <is>
-          <t>3A</t>
+          <t>5A</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
@@ -5388,7 +5500,11 @@
       </c>
     </row>
     <row r="168" ht="14" customHeight="1">
-      <c r="A168" s="11" t="inlineStr"/>
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>5B</t>
+        </is>
+      </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -5414,7 +5530,11 @@
       </c>
     </row>
     <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="11" t="inlineStr"/>
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -5440,7 +5560,11 @@
       </c>
     </row>
     <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="11" t="inlineStr"/>
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -5466,7 +5590,11 @@
       </c>
     </row>
     <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="11" t="inlineStr"/>
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -5492,7 +5620,11 @@
       </c>
     </row>
     <row r="172" ht="14" customHeight="1">
-      <c r="A172" s="11" t="inlineStr"/>
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>5A</t>
+        </is>
+      </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -5525,11 +5657,7 @@
       </c>
     </row>
     <row r="174" ht="14" customHeight="1">
-      <c r="A174" s="4" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+      <c r="A174" s="11" t="inlineStr"/>
       <c r="B174" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG</t>
@@ -5555,11 +5683,7 @@
       </c>
     </row>
     <row r="175" ht="14" customHeight="1">
-      <c r="A175" s="4" t="inlineStr">
-        <is>
-          <t>3B</t>
-        </is>
-      </c>
+      <c r="A175" s="11" t="inlineStr"/>
       <c r="B175" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG</t>
@@ -5585,11 +5709,7 @@
       </c>
     </row>
     <row r="176" ht="14" customHeight="1">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A176" s="11" t="inlineStr"/>
       <c r="B176" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5615,11 +5735,7 @@
       </c>
     </row>
     <row r="177" ht="14" customHeight="1">
-      <c r="A177" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A177" s="11" t="inlineStr"/>
       <c r="B177" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5671,11 +5787,7 @@
       </c>
     </row>
     <row r="179" ht="14" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A179" s="11" t="inlineStr"/>
       <c r="B179" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5701,11 +5813,7 @@
       </c>
     </row>
     <row r="180" ht="14" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A180" s="11" t="inlineStr"/>
       <c r="B180" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5757,11 +5865,7 @@
       </c>
     </row>
     <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
+      <c r="A182" s="11" t="inlineStr"/>
       <c r="B182" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG W</t>
@@ -5787,11 +5891,7 @@
       </c>
     </row>
     <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="4" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
+      <c r="A183" s="11" t="inlineStr"/>
       <c r="B183" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG W</t>
@@ -5817,11 +5917,7 @@
       </c>
     </row>
     <row r="184" ht="14" customHeight="1">
-      <c r="A184" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A184" s="11" t="inlineStr"/>
       <c r="B184" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5847,11 +5943,7 @@
       </c>
     </row>
     <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>5A</t>
-        </is>
-      </c>
+      <c r="A185" s="11" t="inlineStr"/>
       <c r="B185" s="5" t="inlineStr">
         <is>
           <t>ORGN ULTRA TECH</t>
@@ -5877,11 +5969,7 @@
       </c>
     </row>
     <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="4" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
+      <c r="A186" s="11" t="inlineStr"/>
       <c r="B186" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG</t>
@@ -5907,11 +5995,7 @@
       </c>
     </row>
     <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="4" t="inlineStr">
-        <is>
-          <t>3A</t>
-        </is>
-      </c>
+      <c r="A187" s="11" t="inlineStr"/>
       <c r="B187" s="5" t="inlineStr">
         <is>
           <t>LA TRAINER OG</t>
@@ -6024,7 +6108,7 @@
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
@@ -6084,7 +6168,7 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>6A</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
@@ -6144,7 +6228,7 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
@@ -6202,7 +6286,11 @@
       </c>
     </row>
     <row r="198" ht="14" customHeight="1">
-      <c r="A198" s="11" t="inlineStr"/>
+      <c r="A198" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
           <t>SAMBA GOLF</t>
@@ -6228,7 +6316,11 @@
       </c>
     </row>
     <row r="199" ht="14" customHeight="1">
-      <c r="A199" s="11" t="inlineStr"/>
+      <c r="A199" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
           <t>SAMBA GOLF</t>
@@ -6376,7 +6468,7 @@
     <row r="204" ht="14" customHeight="1">
       <c r="A204" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B204" s="5" t="inlineStr">
@@ -6406,7 +6498,7 @@
     <row r="205" ht="14" customHeight="1">
       <c r="A205" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B205" s="5" t="inlineStr">
@@ -6436,7 +6528,7 @@
     <row r="206" ht="14" customHeight="1">
       <c r="A206" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B206" s="5" t="inlineStr">
@@ -6494,7 +6586,11 @@
       </c>
     </row>
     <row r="208" ht="14" customHeight="1">
-      <c r="A208" s="11" t="inlineStr"/>
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
           <t>GHOST MOTO LOW W</t>
@@ -6552,7 +6648,7 @@
     <row r="210" ht="14" customHeight="1">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
@@ -6730,7 +6826,11 @@
       </c>
     </row>
     <row r="216" ht="14" customHeight="1">
-      <c r="A216" s="11" t="inlineStr"/>
+      <c r="A216" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
           <t>SAMBA GOLF</t>
@@ -6756,7 +6856,11 @@
       </c>
     </row>
     <row r="217" ht="14" customHeight="1">
-      <c r="A217" s="11" t="inlineStr"/>
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
           <t>SAMBA GOLF</t>
@@ -6784,7 +6888,7 @@
     <row r="218" ht="14" customHeight="1">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>6A</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
@@ -6812,7 +6916,11 @@
       </c>
     </row>
     <row r="219" ht="14" customHeight="1">
-      <c r="A219" s="11" t="inlineStr"/>
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
           <t>SAMBA GOLF</t>
@@ -6840,7 +6948,7 @@
     <row r="220" ht="14" customHeight="1">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>6A</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
@@ -6868,7 +6976,11 @@
       </c>
     </row>
     <row r="221" ht="14" customHeight="1">
-      <c r="A221" s="11" t="inlineStr"/>
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
           <t>F50 TUNIT MEGA JAH JAH</t>
@@ -6926,7 +7038,7 @@
     <row r="223" ht="14" customHeight="1">
       <c r="A223" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B223" s="5" t="inlineStr">
@@ -6956,7 +7068,7 @@
     <row r="224" ht="14" customHeight="1">
       <c r="A224" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B224" s="5" t="inlineStr">
@@ -6984,7 +7096,11 @@
       </c>
     </row>
     <row r="225" ht="14" customHeight="1">
-      <c r="A225" s="11" t="inlineStr"/>
+      <c r="A225" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -7010,7 +7126,11 @@
       </c>
     </row>
     <row r="226" ht="14" customHeight="1">
-      <c r="A226" s="11" t="inlineStr"/>
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -7036,7 +7156,11 @@
       </c>
     </row>
     <row r="227" ht="14" customHeight="1">
-      <c r="A227" s="11" t="inlineStr"/>
+      <c r="A227" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -7062,7 +7186,11 @@
       </c>
     </row>
     <row r="228" ht="14" customHeight="1">
-      <c r="A228" s="11" t="inlineStr"/>
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -7088,7 +7216,11 @@
       </c>
     </row>
     <row r="229" ht="14" customHeight="1">
-      <c r="A229" s="11" t="inlineStr"/>
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -7114,7 +7246,11 @@
       </c>
     </row>
     <row r="230" ht="14" customHeight="1">
-      <c r="A230" s="11" t="inlineStr"/>
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
           <t>MF2608</t>
@@ -7239,7 +7375,7 @@
     <row r="235" ht="14" customHeight="1">
       <c r="A235" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B235" s="5" t="inlineStr">
@@ -7299,7 +7435,7 @@
     <row r="237" ht="14" customHeight="1">
       <c r="A237" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B237" s="5" t="inlineStr">
@@ -7389,7 +7525,7 @@
     <row r="240" ht="14" customHeight="1">
       <c r="A240" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B240" s="5" t="inlineStr">
@@ -7479,7 +7615,7 @@
     <row r="243" ht="14" customHeight="1">
       <c r="A243" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
@@ -7689,7 +7825,7 @@
     <row r="250" ht="14" customHeight="1">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
@@ -7719,7 +7855,7 @@
     <row r="251" ht="14" customHeight="1">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
@@ -7779,7 +7915,7 @@
     <row r="253" ht="14" customHeight="1">
       <c r="A253" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B253" s="5" t="inlineStr">
@@ -7809,7 +7945,7 @@
     <row r="254" ht="14" customHeight="1">
       <c r="A254" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B254" s="5" t="inlineStr">
@@ -7837,7 +7973,11 @@
       </c>
     </row>
     <row r="255" ht="14" customHeight="1">
-      <c r="A255" s="11" t="inlineStr"/>
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
           <t>TOKYO MJ W</t>
@@ -7865,7 +8005,7 @@
     <row r="256" ht="14" customHeight="1">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
@@ -7895,7 +8035,7 @@
     <row r="257" ht="14" customHeight="1">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
@@ -7925,7 +8065,7 @@
     <row r="258" ht="14" customHeight="1">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
@@ -7953,7 +8093,11 @@
       </c>
     </row>
     <row r="259" ht="14" customHeight="1">
-      <c r="A259" s="11" t="inlineStr"/>
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
           <t>TOKYO W</t>
@@ -8039,7 +8183,11 @@
       </c>
     </row>
     <row r="262" ht="14" customHeight="1">
-      <c r="A262" s="11" t="inlineStr"/>
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -8065,7 +8213,11 @@
       </c>
     </row>
     <row r="263" ht="14" customHeight="1">
-      <c r="A263" s="11" t="inlineStr"/>
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -8091,7 +8243,11 @@
       </c>
     </row>
     <row r="264" ht="14" customHeight="1">
-      <c r="A264" s="11" t="inlineStr"/>
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -8246,7 +8402,7 @@
     <row r="270" ht="14" customHeight="1">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
@@ -8336,7 +8492,7 @@
     <row r="273" ht="14" customHeight="1">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
@@ -8426,7 +8582,7 @@
     <row r="276" ht="14" customHeight="1">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
@@ -8516,7 +8672,7 @@
     <row r="279" ht="14" customHeight="1">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
@@ -8816,7 +8972,7 @@
     <row r="289" ht="14" customHeight="1">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
@@ -8876,7 +9032,7 @@
     <row r="291" ht="14" customHeight="1">
       <c r="A291" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B291" s="5" t="inlineStr">
@@ -8906,7 +9062,7 @@
     <row r="292" ht="14" customHeight="1">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
@@ -8934,7 +9090,11 @@
       </c>
     </row>
     <row r="293" ht="14" customHeight="1">
-      <c r="A293" s="11" t="inlineStr"/>
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -8962,7 +9122,7 @@
     <row r="294" ht="14" customHeight="1">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
@@ -8990,7 +9150,11 @@
       </c>
     </row>
     <row r="295" ht="14" customHeight="1">
-      <c r="A295" s="11" t="inlineStr"/>
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>8C</t>
+        </is>
+      </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
           <t>TOKYO MJ W</t>
@@ -9168,7 +9332,7 @@
     <row r="301" ht="14" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
@@ -9196,7 +9360,11 @@
       </c>
     </row>
     <row r="302" ht="14" customHeight="1">
-      <c r="A302" s="11" t="inlineStr"/>
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>8C</t>
+        </is>
+      </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
           <t>HANDBALL SPEZIAL</t>
@@ -9222,7 +9390,11 @@
       </c>
     </row>
     <row r="303" ht="14" customHeight="1">
-      <c r="A303" s="11" t="inlineStr"/>
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -9248,7 +9420,11 @@
       </c>
     </row>
     <row r="304" ht="14" customHeight="1">
-      <c r="A304" s="11" t="inlineStr"/>
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -9274,7 +9450,11 @@
       </c>
     </row>
     <row r="305" ht="14" customHeight="1">
-      <c r="A305" s="11" t="inlineStr"/>
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -9300,7 +9480,11 @@
       </c>
     </row>
     <row r="306" ht="14" customHeight="1">
-      <c r="A306" s="11" t="inlineStr"/>
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -9326,7 +9510,11 @@
       </c>
     </row>
     <row r="307" ht="14" customHeight="1">
-      <c r="A307" s="11" t="inlineStr"/>
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -9449,7 +9637,11 @@
       </c>
     </row>
     <row r="312" ht="14" customHeight="1">
-      <c r="A312" s="11" t="inlineStr"/>
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
           <t>OZGAIA W</t>
@@ -9475,7 +9667,11 @@
       </c>
     </row>
     <row r="313" ht="14" customHeight="1">
-      <c r="A313" s="11" t="inlineStr"/>
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
           <t>OZGAIA W</t>
@@ -9773,7 +9969,7 @@
     <row r="323" ht="14" customHeight="1">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
@@ -10221,7 +10417,11 @@
       </c>
     </row>
     <row r="338" ht="14" customHeight="1">
-      <c r="A338" s="11" t="inlineStr"/>
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
           <t>SL 72 OG W</t>
@@ -10279,7 +10479,7 @@
     <row r="340" ht="14" customHeight="1">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B340" s="5" t="inlineStr">
@@ -10309,7 +10509,7 @@
     <row r="341" ht="14" customHeight="1">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
@@ -10427,7 +10627,11 @@
       </c>
     </row>
     <row r="345" ht="14" customHeight="1">
-      <c r="A345" s="11" t="inlineStr"/>
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0</t>
@@ -10455,7 +10659,7 @@
     <row r="346" ht="14" customHeight="1">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B346" s="5" t="inlineStr">
@@ -10483,7 +10687,11 @@
       </c>
     </row>
     <row r="347" ht="14" customHeight="1">
-      <c r="A347" s="11" t="inlineStr"/>
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -10509,7 +10717,11 @@
       </c>
     </row>
     <row r="348" ht="14" customHeight="1">
-      <c r="A348" s="11" t="inlineStr"/>
+      <c r="A348" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -10535,7 +10747,11 @@
       </c>
     </row>
     <row r="349" ht="14" customHeight="1">
-      <c r="A349" s="11" t="inlineStr"/>
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -10561,7 +10777,11 @@
       </c>
     </row>
     <row r="350" ht="14" customHeight="1">
-      <c r="A350" s="11" t="inlineStr"/>
+      <c r="A350" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -10587,7 +10807,11 @@
       </c>
     </row>
     <row r="351" ht="14" customHeight="1">
-      <c r="A351" s="11" t="inlineStr"/>
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -10622,7 +10846,7 @@
     <row r="353" ht="14" customHeight="1">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
@@ -10650,7 +10874,11 @@
       </c>
     </row>
     <row r="354" ht="14" customHeight="1">
-      <c r="A354" s="11" t="inlineStr"/>
+      <c r="A354" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
           <t>OZGAIA W</t>
@@ -10676,7 +10904,11 @@
       </c>
     </row>
     <row r="355" ht="14" customHeight="1">
-      <c r="A355" s="11" t="inlineStr"/>
+      <c r="A355" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B355" s="5" t="inlineStr">
         <is>
           <t>OZGAIA W</t>
@@ -11032,7 +11264,11 @@
       </c>
     </row>
     <row r="367" ht="14" customHeight="1">
-      <c r="A367" s="11" t="inlineStr"/>
+      <c r="A367" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
           <t>SPEZIAL GOLF</t>
@@ -11058,7 +11294,11 @@
       </c>
     </row>
     <row r="368" ht="14" customHeight="1">
-      <c r="A368" s="11" t="inlineStr"/>
+      <c r="A368" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B368" s="5" t="inlineStr">
         <is>
           <t>SPEZIAL GOLF</t>
@@ -11084,7 +11324,11 @@
       </c>
     </row>
     <row r="369" ht="14" customHeight="1">
-      <c r="A369" s="11" t="inlineStr"/>
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -11110,7 +11354,11 @@
       </c>
     </row>
     <row r="370" ht="14" customHeight="1">
-      <c r="A370" s="11" t="inlineStr"/>
+      <c r="A370" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
       <c r="B370" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -11226,7 +11474,11 @@
       </c>
     </row>
     <row r="374" ht="14" customHeight="1">
-      <c r="A374" s="11" t="inlineStr"/>
+      <c r="A374" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
       <c r="B374" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -11282,7 +11534,11 @@
       </c>
     </row>
     <row r="376" ht="14" customHeight="1">
-      <c r="A376" s="11" t="inlineStr"/>
+      <c r="A376" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B376" s="5" t="inlineStr">
         <is>
           <t>HANDBALL SPEZIAL</t>
@@ -11308,7 +11564,11 @@
       </c>
     </row>
     <row r="377" ht="14" customHeight="1">
-      <c r="A377" s="11" t="inlineStr"/>
+      <c r="A377" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
           <t>HANDBALL SPEZIAL</t>
@@ -11484,7 +11744,11 @@
       </c>
     </row>
     <row r="383" ht="14" customHeight="1">
-      <c r="A383" s="11" t="inlineStr"/>
+      <c r="A383" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
           <t>HANDBALL SPEZIAL</t>
@@ -11512,7 +11776,7 @@
     <row r="384" ht="14" customHeight="1">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B384" s="5" t="inlineStr">
@@ -11542,7 +11806,7 @@
     <row r="385" ht="14" customHeight="1">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B385" s="5" t="inlineStr">
@@ -11572,7 +11836,7 @@
     <row r="386" ht="14" customHeight="1">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>5B</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B386" s="5" t="inlineStr">
@@ -11600,7 +11864,11 @@
       </c>
     </row>
     <row r="387" ht="14" customHeight="1">
-      <c r="A387" s="11" t="inlineStr"/>
+      <c r="A387" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -11626,7 +11894,11 @@
       </c>
     </row>
     <row r="388" ht="14" customHeight="1">
-      <c r="A388" s="11" t="inlineStr"/>
+      <c r="A388" s="4" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
       <c r="B388" s="5" t="inlineStr">
         <is>
           <t>HANDBALL SPEZIAL</t>
@@ -11682,7 +11954,11 @@
       </c>
     </row>
     <row r="390" ht="14" customHeight="1">
-      <c r="A390" s="11" t="inlineStr"/>
+      <c r="A390" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B390" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -11708,7 +11984,11 @@
       </c>
     </row>
     <row r="391" ht="14" customHeight="1">
-      <c r="A391" s="11" t="inlineStr"/>
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -11734,7 +12014,11 @@
       </c>
     </row>
     <row r="392" ht="14" customHeight="1">
-      <c r="A392" s="11" t="inlineStr"/>
+      <c r="A392" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B392" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -11760,7 +12044,11 @@
       </c>
     </row>
     <row r="393" ht="14" customHeight="1">
-      <c r="A393" s="11" t="inlineStr"/>
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
       <c r="B393" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -11855,7 +12143,7 @@
     <row r="397" ht="14" customHeight="1">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
@@ -12035,7 +12323,7 @@
     <row r="403" ht="14" customHeight="1">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B403" s="5" t="inlineStr">
@@ -12093,7 +12381,11 @@
       </c>
     </row>
     <row r="405" ht="14" customHeight="1">
-      <c r="A405" s="11" t="inlineStr"/>
+      <c r="A405" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
           <t>ADIPOWER 26 SL BOA</t>
@@ -12119,7 +12411,11 @@
       </c>
     </row>
     <row r="406" ht="14" customHeight="1">
-      <c r="A406" s="11" t="inlineStr"/>
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
       <c r="B406" s="5" t="inlineStr">
         <is>
           <t>ADIPOWER 26 SL BOA</t>
@@ -12777,7 +13073,7 @@
     <row r="428" ht="14" customHeight="1">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>1A</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B428" s="5" t="inlineStr">
@@ -12865,7 +13161,11 @@
       </c>
     </row>
     <row r="431" ht="14" customHeight="1">
-      <c r="A431" s="11" t="inlineStr"/>
+      <c r="A431" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
       <c r="B431" s="5" t="inlineStr">
         <is>
           <t>ADIPOWER 26 SL BOA</t>
@@ -12951,7 +13251,11 @@
       </c>
     </row>
     <row r="434" ht="14" customHeight="1">
-      <c r="A434" s="11" t="inlineStr"/>
+      <c r="A434" s="4" t="inlineStr">
+        <is>
+          <t>11B1</t>
+        </is>
+      </c>
       <c r="B434" s="5" t="inlineStr">
         <is>
           <t>W S2G 26 LEATHER</t>
@@ -12977,7 +13281,11 @@
       </c>
     </row>
     <row r="435" ht="14" customHeight="1">
-      <c r="A435" s="11" t="inlineStr"/>
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>11B1</t>
+        </is>
+      </c>
       <c r="B435" s="5" t="inlineStr">
         <is>
           <t>W S2G 26 LEATHER</t>
@@ -13095,7 +13403,7 @@
     <row r="439" ht="14" customHeight="1">
       <c r="A439" s="4" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B439" s="5" t="inlineStr">
@@ -13123,7 +13431,11 @@
       </c>
     </row>
     <row r="440" ht="14" customHeight="1">
-      <c r="A440" s="11" t="inlineStr"/>
+      <c r="A440" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
       <c r="B440" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -13149,7 +13461,11 @@
       </c>
     </row>
     <row r="441" ht="14" customHeight="1">
-      <c r="A441" s="11" t="inlineStr"/>
+      <c r="A441" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
       <c r="B441" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -13424,7 +13740,7 @@
     <row r="451" ht="14" customHeight="1">
       <c r="A451" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B451" s="5" t="inlineStr">
@@ -13454,7 +13770,7 @@
     <row r="452" ht="14" customHeight="1">
       <c r="A452" s="4" t="inlineStr">
         <is>
-          <t>12C</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B452" s="5" t="inlineStr">
@@ -13482,7 +13798,11 @@
       </c>
     </row>
     <row r="453" ht="14" customHeight="1">
-      <c r="A453" s="11" t="inlineStr"/>
+      <c r="A453" s="4" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
       <c r="B453" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -13538,7 +13858,11 @@
       </c>
     </row>
     <row r="455" ht="14" customHeight="1">
-      <c r="A455" s="11" t="inlineStr"/>
+      <c r="A455" s="4" t="inlineStr">
+        <is>
+          <t>11B2</t>
+        </is>
+      </c>
       <c r="B455" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -13564,7 +13888,11 @@
       </c>
     </row>
     <row r="456" ht="14" customHeight="1">
-      <c r="A456" s="11" t="inlineStr"/>
+      <c r="A456" s="4" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
       <c r="B456" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -13590,7 +13918,11 @@
       </c>
     </row>
     <row r="457" ht="14" customHeight="1">
-      <c r="A457" s="11" t="inlineStr"/>
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
       <c r="B457" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -13616,7 +13948,11 @@
       </c>
     </row>
     <row r="458" ht="14" customHeight="1">
-      <c r="A458" s="11" t="inlineStr"/>
+      <c r="A458" s="4" t="inlineStr">
+        <is>
+          <t>11B2</t>
+        </is>
+      </c>
       <c r="B458" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -13642,7 +13978,11 @@
       </c>
     </row>
     <row r="459" ht="14" customHeight="1">
-      <c r="A459" s="11" t="inlineStr"/>
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>11B2</t>
+        </is>
+      </c>
       <c r="B459" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -13767,7 +14107,7 @@
     <row r="464" ht="14" customHeight="1">
       <c r="A464" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B464" s="5" t="inlineStr">
@@ -13797,7 +14137,7 @@
     <row r="465" ht="14" customHeight="1">
       <c r="A465" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B465" s="5" t="inlineStr">
@@ -13915,7 +14255,11 @@
       </c>
     </row>
     <row r="469" ht="14" customHeight="1">
-      <c r="A469" s="11" t="inlineStr"/>
+      <c r="A469" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
       <c r="B469" s="5" t="inlineStr">
         <is>
           <t>1609ER RS</t>
@@ -13971,7 +14315,11 @@
       </c>
     </row>
     <row r="471" ht="14" customHeight="1">
-      <c r="A471" s="11" t="inlineStr"/>
+      <c r="A471" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
       <c r="B471" s="5" t="inlineStr">
         <is>
           <t>1609ER RS</t>
@@ -14027,7 +14375,11 @@
       </c>
     </row>
     <row r="473" ht="14" customHeight="1">
-      <c r="A473" s="11" t="inlineStr"/>
+      <c r="A473" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
       <c r="B473" s="5" t="inlineStr">
         <is>
           <t>1609ER RS</t>
@@ -14055,7 +14407,7 @@
     <row r="474" ht="14" customHeight="1">
       <c r="A474" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B474" s="5" t="inlineStr">
@@ -14083,7 +14435,11 @@
       </c>
     </row>
     <row r="475" ht="14" customHeight="1">
-      <c r="A475" s="11" t="inlineStr"/>
+      <c r="A475" s="4" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
       <c r="B475" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -14141,7 +14497,7 @@
     <row r="477" ht="14" customHeight="1">
       <c r="A477" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B477" s="5" t="inlineStr">
@@ -14171,7 +14527,7 @@
     <row r="478" ht="14" customHeight="1">
       <c r="A478" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B478" s="5" t="inlineStr">
@@ -14229,7 +14585,11 @@
       </c>
     </row>
     <row r="480" ht="14" customHeight="1">
-      <c r="A480" s="11" t="inlineStr"/>
+      <c r="A480" s="4" t="inlineStr">
+        <is>
+          <t>12D</t>
+        </is>
+      </c>
       <c r="B480" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -14255,7 +14615,11 @@
       </c>
     </row>
     <row r="481" ht="14" customHeight="1">
-      <c r="A481" s="11" t="inlineStr"/>
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>12D</t>
+        </is>
+      </c>
       <c r="B481" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -14281,7 +14645,11 @@
       </c>
     </row>
     <row r="482" ht="14" customHeight="1">
-      <c r="A482" s="11" t="inlineStr"/>
+      <c r="A482" s="4" t="inlineStr">
+        <is>
+          <t>12D</t>
+        </is>
+      </c>
       <c r="B482" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 W</t>
@@ -14309,7 +14677,7 @@
     <row r="483" ht="14" customHeight="1">
       <c r="A483" s="4" t="inlineStr">
         <is>
-          <t>5B</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B483" s="5" t="inlineStr">
@@ -14339,7 +14707,7 @@
     <row r="484" ht="14" customHeight="1">
       <c r="A484" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B484" s="5" t="inlineStr">
@@ -14367,7 +14735,11 @@
       </c>
     </row>
     <row r="485" ht="14" customHeight="1">
-      <c r="A485" s="11" t="inlineStr"/>
+      <c r="A485" s="4" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
       <c r="B485" s="5" t="inlineStr">
         <is>
           <t>MF2603</t>
@@ -14393,7 +14765,11 @@
       </c>
     </row>
     <row r="486" ht="14" customHeight="1">
-      <c r="A486" s="11" t="inlineStr"/>
+      <c r="A486" s="4" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
       <c r="B486" s="5" t="inlineStr">
         <is>
           <t>MF2604</t>
@@ -14419,7 +14795,11 @@
       </c>
     </row>
     <row r="487" ht="14" customHeight="1">
-      <c r="A487" s="11" t="inlineStr"/>
+      <c r="A487" s="4" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
       <c r="B487" s="5" t="inlineStr">
         <is>
           <t>MF2605</t>
@@ -14445,7 +14825,11 @@
       </c>
     </row>
     <row r="488" ht="14" customHeight="1">
-      <c r="A488" s="11" t="inlineStr"/>
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
       <c r="B488" s="5" t="inlineStr">
         <is>
           <t>MF2606</t>
@@ -14471,7 +14855,11 @@
       </c>
     </row>
     <row r="489" ht="14" customHeight="1">
-      <c r="A489" s="11" t="inlineStr"/>
+      <c r="A489" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
       <c r="B489" s="5" t="inlineStr">
         <is>
           <t>MF2607</t>
@@ -14504,11 +14892,7 @@
       </c>
     </row>
     <row r="491" ht="14" customHeight="1">
-      <c r="A491" s="4" t="inlineStr">
-        <is>
-          <t>6C</t>
-        </is>
-      </c>
+      <c r="A491" s="11" t="inlineStr"/>
       <c r="B491" s="5" t="inlineStr">
         <is>
           <t>SAMBA</t>
@@ -14534,11 +14918,7 @@
       </c>
     </row>
     <row r="492" ht="14" customHeight="1">
-      <c r="A492" s="4" t="inlineStr">
-        <is>
-          <t>8A</t>
-        </is>
-      </c>
+      <c r="A492" s="11" t="inlineStr"/>
       <c r="B492" s="5" t="inlineStr">
         <is>
           <t>SAMBA</t>
@@ -14616,11 +14996,7 @@
       </c>
     </row>
     <row r="495" ht="14" customHeight="1">
-      <c r="A495" s="4" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
+      <c r="A495" s="11" t="inlineStr"/>
       <c r="B495" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -14646,11 +15022,7 @@
       </c>
     </row>
     <row r="496" ht="14" customHeight="1">
-      <c r="A496" s="4" t="inlineStr">
-        <is>
-          <t>9B</t>
-        </is>
-      </c>
+      <c r="A496" s="11" t="inlineStr"/>
       <c r="B496" s="5" t="inlineStr">
         <is>
           <t>ADISTAR XLG 2.0 J</t>
@@ -14813,11 +15185,7 @@
       </c>
     </row>
     <row r="503" ht="14" customHeight="1">
-      <c r="A503" s="4" t="inlineStr">
-        <is>
-          <t>2C</t>
-        </is>
-      </c>
+      <c r="A503" s="11" t="inlineStr"/>
       <c r="B503" s="5" t="inlineStr">
         <is>
           <t>RETROCROSS 25</t>
@@ -14843,11 +15211,7 @@
       </c>
     </row>
     <row r="504" ht="14" customHeight="1">
-      <c r="A504" s="4" t="inlineStr">
-        <is>
-          <t>8A</t>
-        </is>
-      </c>
+      <c r="A504" s="11" t="inlineStr"/>
       <c r="B504" s="5" t="inlineStr">
         <is>
           <t>SAMBA</t>
@@ -14873,11 +15237,7 @@
       </c>
     </row>
     <row r="505" ht="14" customHeight="1">
-      <c r="A505" s="4" t="inlineStr">
-        <is>
-          <t>2C</t>
-        </is>
-      </c>
+      <c r="A505" s="11" t="inlineStr"/>
       <c r="B505" s="5" t="inlineStr">
         <is>
           <t>RETROCROSS 25</t>
@@ -14903,11 +15263,7 @@
       </c>
     </row>
     <row r="506" ht="14" customHeight="1">
-      <c r="A506" s="4" t="inlineStr">
-        <is>
-          <t>2C</t>
-        </is>
-      </c>
+      <c r="A506" s="11" t="inlineStr"/>
       <c r="B506" s="5" t="inlineStr">
         <is>
           <t>RETROCROSS 25</t>
@@ -14933,11 +15289,7 @@
       </c>
     </row>
     <row r="507" ht="14" customHeight="1">
-      <c r="A507" s="4" t="inlineStr">
-        <is>
-          <t>2B</t>
-        </is>
-      </c>
+      <c r="A507" s="11" t="inlineStr"/>
       <c r="B507" s="5" t="inlineStr">
         <is>
           <t>TOKYO W</t>
@@ -14963,11 +15315,7 @@
       </c>
     </row>
     <row r="508" ht="14" customHeight="1">
-      <c r="A508" s="4" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
-      </c>
+      <c r="A508" s="11" t="inlineStr"/>
       <c r="B508" s="5" t="inlineStr">
         <is>
           <t>MEGARIDE F50</t>

--- a/flask_backend/test_output/result_table_v2.xlsx
+++ b/flask_backend/test_output/result_table_v2.xlsx
@@ -585,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J480"/>
+  <dimension ref="A1:J449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4964,7 +4964,7 @@
         </is>
       </c>
       <c r="D149" s="7" t="n">
-        <v>14375</v>
+        <v>12083</v>
       </c>
       <c r="E149" s="8" t="n"/>
       <c r="F149" s="8" t="n"/>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="D152" s="7" t="n">
-        <v>12808</v>
+        <v>636</v>
       </c>
       <c r="E152" s="8" t="n"/>
       <c r="F152" s="8" t="n"/>
@@ -5075,16 +5075,16 @@
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>HP5123</t>
+          <t>SL 72 RTN</t>
         </is>
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>HP5123</t>
+          <t>IH5569</t>
         </is>
       </c>
       <c r="D153" s="7" t="n">
-        <v>3530</v>
+        <v>830</v>
       </c>
       <c r="E153" s="8" t="n"/>
       <c r="F153" s="8" t="n"/>
@@ -5105,16 +5105,16 @@
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>HP5124</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C154" s="6" t="inlineStr">
         <is>
-          <t>HP5124</t>
+          <t>JI1281</t>
         </is>
       </c>
       <c r="D154" s="7" t="n">
-        <v>5030</v>
+        <v>16</v>
       </c>
       <c r="E154" s="8" t="n"/>
       <c r="F154" s="8" t="n"/>
@@ -5135,16 +5135,16 @@
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RTN</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C155" s="6" t="inlineStr">
         <is>
-          <t>IH5569</t>
+          <t>JI1282</t>
         </is>
       </c>
       <c r="D155" s="7" t="n">
-        <v>830</v>
+        <v>1399</v>
       </c>
       <c r="E155" s="8" t="n"/>
       <c r="F155" s="8" t="n"/>
@@ -5170,11 +5170,11 @@
       </c>
       <c r="C156" s="6" t="inlineStr">
         <is>
-          <t>JI1281</t>
+          <t>JQ9555</t>
         </is>
       </c>
       <c r="D156" s="7" t="n">
-        <v>16</v>
+        <v>951</v>
       </c>
       <c r="E156" s="8" t="n"/>
       <c r="F156" s="8" t="n"/>
@@ -5200,11 +5200,11 @@
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>JI1282</t>
+          <t>KH9644</t>
         </is>
       </c>
       <c r="D157" s="7" t="n">
-        <v>3464</v>
+        <v>181</v>
       </c>
       <c r="E157" s="8" t="n"/>
       <c r="F157" s="8" t="n"/>
@@ -5230,11 +5230,11 @@
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>JQ9555</t>
+          <t>KH9646</t>
         </is>
       </c>
       <c r="D158" s="7" t="n">
-        <v>951</v>
+        <v>502</v>
       </c>
       <c r="E158" s="8" t="n"/>
       <c r="F158" s="8" t="n"/>
@@ -5260,11 +5260,11 @@
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>KH9644</t>
+          <t>KH9647</t>
         </is>
       </c>
       <c r="D159" s="7" t="n">
-        <v>829</v>
+        <v>310</v>
       </c>
       <c r="E159" s="8" t="n"/>
       <c r="F159" s="8" t="n"/>
@@ -5290,11 +5290,11 @@
       </c>
       <c r="C160" s="6" t="inlineStr">
         <is>
-          <t>KH9646</t>
+          <t>KH9648</t>
         </is>
       </c>
       <c r="D160" s="7" t="n">
-        <v>1350</v>
+        <v>1777</v>
       </c>
       <c r="E160" s="8" t="n"/>
       <c r="F160" s="8" t="n"/>
@@ -5320,11 +5320,11 @@
       </c>
       <c r="C161" s="6" t="inlineStr">
         <is>
-          <t>KH9647</t>
+          <t>KH9650</t>
         </is>
       </c>
       <c r="D161" s="7" t="n">
-        <v>310</v>
+        <v>749</v>
       </c>
       <c r="E161" s="8" t="n"/>
       <c r="F161" s="8" t="n"/>
@@ -5350,11 +5350,11 @@
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>KH9648</t>
+          <t>KH9651</t>
         </is>
       </c>
       <c r="D162" s="7" t="n">
-        <v>2209</v>
+        <v>1012</v>
       </c>
       <c r="E162" s="8" t="n"/>
       <c r="F162" s="8" t="n"/>
@@ -5380,11 +5380,11 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>KH9650</t>
+          <t>KH9652</t>
         </is>
       </c>
       <c r="D163" s="7" t="n">
-        <v>749</v>
+        <v>1912</v>
       </c>
       <c r="E163" s="8" t="n"/>
       <c r="F163" s="8" t="n"/>
@@ -5410,11 +5410,11 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>KH9651</t>
+          <t>KH9653</t>
         </is>
       </c>
       <c r="D164" s="7" t="n">
-        <v>1012</v>
+        <v>1755</v>
       </c>
       <c r="E164" s="8" t="n"/>
       <c r="F164" s="8" t="n"/>
@@ -5440,11 +5440,11 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>KH9652</t>
+          <t>KJ1674</t>
         </is>
       </c>
       <c r="D165" s="7" t="n">
-        <v>2640</v>
+        <v>2012</v>
       </c>
       <c r="E165" s="8" t="n"/>
       <c r="F165" s="8" t="n"/>
@@ -5465,16 +5465,16 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>SL 72 RS J</t>
         </is>
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>KH9653</t>
+          <t>KJ7404</t>
         </is>
       </c>
       <c r="D166" s="7" t="n">
-        <v>6668</v>
+        <v>300</v>
       </c>
       <c r="E166" s="8" t="n"/>
       <c r="F166" s="8" t="n"/>
@@ -5487,54 +5487,27 @@
         </is>
       </c>
     </row>
-    <row r="167" ht="14" customHeight="1">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>5C</t>
-        </is>
-      </c>
-      <c r="B167" s="5" t="inlineStr">
-        <is>
-          <t>SL 72 RS</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>KH9656</t>
-        </is>
-      </c>
-      <c r="D167" s="7" t="n">
-        <v>1466</v>
-      </c>
-      <c r="E167" s="8" t="n"/>
-      <c r="F167" s="8" t="n"/>
-      <c r="G167" s="8" t="n"/>
-      <c r="H167" s="9" t="n"/>
-      <c r="I167" s="9" t="n"/>
-      <c r="J167" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>── 說明表 ──</t>
         </is>
       </c>
     </row>
     <row r="168" ht="14" customHeight="1">
-      <c r="A168" s="4" t="inlineStr">
-        <is>
-          <t>5C</t>
-        </is>
-      </c>
+      <c r="A168" s="11" t="inlineStr"/>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>LA TRAINER OG</t>
         </is>
       </c>
       <c r="C168" s="6" t="inlineStr">
         <is>
-          <t>KH9658</t>
+          <t>KH9680</t>
         </is>
       </c>
       <c r="D168" s="7" t="n">
-        <v>583</v>
+        <v>1373</v>
       </c>
       <c r="E168" s="8" t="n"/>
       <c r="F168" s="8" t="n"/>
@@ -5548,23 +5521,19 @@
       </c>
     </row>
     <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="4" t="inlineStr">
-        <is>
-          <t>5C</t>
-        </is>
-      </c>
+      <c r="A169" s="11" t="inlineStr"/>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>LA TRAINER OG</t>
         </is>
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>KJ1674</t>
+          <t>KH9681</t>
         </is>
       </c>
       <c r="D169" s="7" t="n">
-        <v>2715</v>
+        <v>836</v>
       </c>
       <c r="E169" s="8" t="n"/>
       <c r="F169" s="8" t="n"/>
@@ -5578,23 +5547,19 @@
       </c>
     </row>
     <row r="170" ht="14" customHeight="1">
-      <c r="A170" s="4" t="inlineStr">
-        <is>
-          <t>5C</t>
-        </is>
-      </c>
+      <c r="A170" s="11" t="inlineStr"/>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS J</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>KJ7404</t>
+          <t>KI7557</t>
         </is>
       </c>
       <c r="D170" s="7" t="n">
-        <v>600</v>
+        <v>3000</v>
       </c>
       <c r="E170" s="8" t="n"/>
       <c r="F170" s="8" t="n"/>
@@ -5608,23 +5573,19 @@
       </c>
     </row>
     <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="4" t="inlineStr">
-        <is>
-          <t>5C</t>
-        </is>
-      </c>
+      <c r="A171" s="11" t="inlineStr"/>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>LA1750</t>
+          <t>KI7558</t>
         </is>
       </c>
       <c r="D171" s="7" t="n">
-        <v>305</v>
+        <v>8500</v>
       </c>
       <c r="E171" s="8" t="n"/>
       <c r="F171" s="8" t="n"/>
@@ -5637,10 +5598,29 @@
         </is>
       </c>
     </row>
-    <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>── 說明表 ──</t>
+    <row r="172" ht="14" customHeight="1">
+      <c r="A172" s="11" t="inlineStr"/>
+      <c r="B172" s="5" t="inlineStr">
+        <is>
+          <t>ORGN ULTRA TECH</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>KI9862</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E172" s="8" t="n"/>
+      <c r="F172" s="8" t="n"/>
+      <c r="G172" s="8" t="n"/>
+      <c r="H172" s="9" t="n"/>
+      <c r="I172" s="9" t="n"/>
+      <c r="J172" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -5648,16 +5628,16 @@
       <c r="A173" s="11" t="inlineStr"/>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>LA TRAINER OG</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>KH9680</t>
+          <t>KJ5260</t>
         </is>
       </c>
       <c r="D173" s="7" t="n">
-        <v>1373</v>
+        <v>1195</v>
       </c>
       <c r="E173" s="8" t="n"/>
       <c r="F173" s="8" t="n"/>
@@ -5674,16 +5654,16 @@
       <c r="A174" s="11" t="inlineStr"/>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>LA TRAINER OG</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>KH9681</t>
+          <t>KJ5261</t>
         </is>
       </c>
       <c r="D174" s="7" t="n">
-        <v>836</v>
+        <v>608</v>
       </c>
       <c r="E174" s="8" t="n"/>
       <c r="F174" s="8" t="n"/>
@@ -5705,11 +5685,11 @@
       </c>
       <c r="C175" s="6" t="inlineStr">
         <is>
-          <t>KI7557</t>
+          <t>KJ8322</t>
         </is>
       </c>
       <c r="D175" s="7" t="n">
-        <v>3000</v>
+        <v>900</v>
       </c>
       <c r="E175" s="8" t="n"/>
       <c r="F175" s="8" t="n"/>
@@ -5726,16 +5706,16 @@
       <c r="A176" s="11" t="inlineStr"/>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>LA TRAINER OG W</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
         <is>
-          <t>KI7558</t>
+          <t>KK2438</t>
         </is>
       </c>
       <c r="D176" s="7" t="n">
-        <v>8500</v>
+        <v>554</v>
       </c>
       <c r="E176" s="8" t="n"/>
       <c r="F176" s="8" t="n"/>
@@ -5752,16 +5732,16 @@
       <c r="A177" s="11" t="inlineStr"/>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>LA TRAINER OG W</t>
         </is>
       </c>
       <c r="C177" s="6" t="inlineStr">
         <is>
-          <t>KI9862</t>
+          <t>KK2445</t>
         </is>
       </c>
       <c r="D177" s="7" t="n">
-        <v>5000</v>
+        <v>1113</v>
       </c>
       <c r="E177" s="8" t="n"/>
       <c r="F177" s="8" t="n"/>
@@ -5783,11 +5763,11 @@
       </c>
       <c r="C178" s="6" t="inlineStr">
         <is>
-          <t>KJ5260</t>
+          <t>KZ6381</t>
         </is>
       </c>
       <c r="D178" s="7" t="n">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="E178" s="8" t="n"/>
       <c r="F178" s="8" t="n"/>
@@ -5809,11 +5789,11 @@
       </c>
       <c r="C179" s="6" t="inlineStr">
         <is>
-          <t>KJ5261</t>
+          <t>KZ6382</t>
         </is>
       </c>
       <c r="D179" s="7" t="n">
-        <v>608</v>
+        <v>1200</v>
       </c>
       <c r="E179" s="8" t="n"/>
       <c r="F179" s="8" t="n"/>
@@ -5830,12 +5810,12 @@
       <c r="A180" s="11" t="inlineStr"/>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>LA TRAINER OG</t>
         </is>
       </c>
       <c r="C180" s="6" t="inlineStr">
         <is>
-          <t>KJ8322</t>
+          <t>LA7413</t>
         </is>
       </c>
       <c r="D180" s="7" t="n">
@@ -5856,16 +5836,16 @@
       <c r="A181" s="11" t="inlineStr"/>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>LA TRAINER OG W</t>
+          <t>LA TRAINER OG</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>KK2438</t>
+          <t>LA7414</t>
         </is>
       </c>
       <c r="D181" s="7" t="n">
-        <v>554</v>
+        <v>900</v>
       </c>
       <c r="E181" s="8" t="n"/>
       <c r="F181" s="8" t="n"/>
@@ -5878,46 +5858,31 @@
         </is>
       </c>
     </row>
-    <row r="182" ht="14" customHeight="1">
-      <c r="A182" s="11" t="inlineStr"/>
-      <c r="B182" s="5" t="inlineStr">
-        <is>
-          <t>LA TRAINER OG W</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>KK2445</t>
-        </is>
-      </c>
-      <c r="D182" s="7" t="n">
-        <v>1113</v>
-      </c>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="8" t="n"/>
-      <c r="G182" s="8" t="n"/>
-      <c r="H182" s="9" t="n"/>
-      <c r="I182" s="9" t="n"/>
-      <c r="J182" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="182" ht="16" customHeight="1">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>── 6部 ──</t>
         </is>
       </c>
     </row>
     <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="11" t="inlineStr"/>
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>KZ6381</t>
+          <t>IG6045</t>
         </is>
       </c>
       <c r="D183" s="7" t="n">
-        <v>1200</v>
+        <v>33906</v>
       </c>
       <c r="E183" s="8" t="n"/>
       <c r="F183" s="8" t="n"/>
@@ -5931,19 +5896,23 @@
       </c>
     </row>
     <row r="184" ht="14" customHeight="1">
-      <c r="A184" s="11" t="inlineStr"/>
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>MEGARIDE</t>
         </is>
       </c>
       <c r="C184" s="6" t="inlineStr">
         <is>
-          <t>KZ6382</t>
+          <t>JH5523</t>
         </is>
       </c>
       <c r="D184" s="7" t="n">
-        <v>1200</v>
+        <v>620</v>
       </c>
       <c r="E184" s="8" t="n"/>
       <c r="F184" s="8" t="n"/>
@@ -5957,19 +5926,23 @@
       </c>
     </row>
     <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="11" t="inlineStr"/>
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>LA TRAINER OG</t>
+          <t>MEGARIDE</t>
         </is>
       </c>
       <c r="C185" s="6" t="inlineStr">
         <is>
-          <t>LA7413</t>
+          <t>JP9626</t>
         </is>
       </c>
       <c r="D185" s="7" t="n">
-        <v>900</v>
+        <v>967</v>
       </c>
       <c r="E185" s="8" t="n"/>
       <c r="F185" s="8" t="n"/>
@@ -5983,19 +5956,23 @@
       </c>
     </row>
     <row r="186" ht="14" customHeight="1">
-      <c r="A186" s="11" t="inlineStr"/>
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>LA TRAINER OG</t>
+          <t>MEGA GHOSTRIDE W</t>
         </is>
       </c>
       <c r="C186" s="6" t="inlineStr">
         <is>
-          <t>LA7414</t>
+          <t>JQ0553</t>
         </is>
       </c>
       <c r="D186" s="7" t="n">
-        <v>900</v>
+        <v>161</v>
       </c>
       <c r="E186" s="8" t="n"/>
       <c r="F186" s="8" t="n"/>
@@ -6008,10 +5985,33 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="3" t="inlineStr">
-        <is>
-          <t>── 6部 ──</t>
+    <row r="187" ht="14" customHeight="1">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
+      <c r="B187" s="5" t="inlineStr">
+        <is>
+          <t>MEGARIDE</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>KH9590</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="n">
+        <v>2457</v>
+      </c>
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
+      <c r="G187" s="8" t="n"/>
+      <c r="H187" s="9" t="n"/>
+      <c r="I187" s="9" t="n"/>
+      <c r="J187" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -6023,16 +6023,16 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>MEGA GHOSTRIDE W</t>
         </is>
       </c>
       <c r="C188" s="6" t="inlineStr">
         <is>
-          <t>IG6045</t>
+          <t>KI4673</t>
         </is>
       </c>
       <c r="D188" s="7" t="n">
-        <v>33906</v>
+        <v>1453</v>
       </c>
       <c r="E188" s="8" t="n"/>
       <c r="F188" s="8" t="n"/>
@@ -6053,16 +6053,16 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>MEGARIDE</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C189" s="6" t="inlineStr">
         <is>
-          <t>JH5523</t>
+          <t>KJ7892</t>
         </is>
       </c>
       <c r="D189" s="7" t="n">
-        <v>620</v>
+        <v>1800</v>
       </c>
       <c r="E189" s="8" t="n"/>
       <c r="F189" s="8" t="n"/>
@@ -6083,16 +6083,16 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>MEGARIDE</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C190" s="6" t="inlineStr">
         <is>
-          <t>JP9626</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D190" s="7" t="n">
-        <v>967</v>
+        <v>5436</v>
       </c>
       <c r="E190" s="8" t="n"/>
       <c r="F190" s="8" t="n"/>
@@ -6113,16 +6113,16 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>MEGA GHOSTRIDE W</t>
+          <t>F50 TUNIT MEGA JAH JAH</t>
         </is>
       </c>
       <c r="C191" s="6" t="inlineStr">
         <is>
-          <t>JQ0553</t>
+          <t>LA3614</t>
         </is>
       </c>
       <c r="D191" s="7" t="n">
-        <v>161</v>
+        <v>909</v>
       </c>
       <c r="E191" s="8" t="n"/>
       <c r="F191" s="8" t="n"/>
@@ -6138,21 +6138,21 @@
     <row r="192" ht="14" customHeight="1">
       <c r="A192" s="4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>MEGARIDE</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C192" s="6" t="inlineStr">
         <is>
-          <t>KH9590</t>
+          <t>HQ7636</t>
         </is>
       </c>
       <c r="D192" s="7" t="n">
-        <v>2457</v>
+        <v>2257</v>
       </c>
       <c r="E192" s="8" t="n"/>
       <c r="F192" s="8" t="n"/>
@@ -6168,21 +6168,21 @@
     <row r="193" ht="14" customHeight="1">
       <c r="A193" s="4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>MEGA GHOSTRIDE W</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C193" s="6" t="inlineStr">
         <is>
-          <t>KI4673</t>
+          <t>HQ7638</t>
         </is>
       </c>
       <c r="D193" s="7" t="n">
-        <v>1453</v>
+        <v>241</v>
       </c>
       <c r="E193" s="8" t="n"/>
       <c r="F193" s="8" t="n"/>
@@ -6198,21 +6198,21 @@
     <row r="194" ht="14" customHeight="1">
       <c r="A194" s="4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>KJ7892</t>
+          <t>JQ6439</t>
         </is>
       </c>
       <c r="D194" s="7" t="n">
-        <v>1800</v>
+        <v>304</v>
       </c>
       <c r="E194" s="8" t="n"/>
       <c r="F194" s="8" t="n"/>
@@ -6228,21 +6228,21 @@
     <row r="195" ht="14" customHeight="1">
       <c r="A195" s="4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KI0435</t>
         </is>
       </c>
       <c r="D195" s="7" t="n">
-        <v>5436</v>
+        <v>759</v>
       </c>
       <c r="E195" s="8" t="n"/>
       <c r="F195" s="8" t="n"/>
@@ -6258,21 +6258,21 @@
     <row r="196" ht="14" customHeight="1">
       <c r="A196" s="4" t="inlineStr">
         <is>
-          <t>6A</t>
+          <t>6B</t>
         </is>
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>F50 TUNIT MEGA JAH JAH</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
         <is>
-          <t>LA3614</t>
+          <t>KI0436</t>
         </is>
       </c>
       <c r="D196" s="7" t="n">
-        <v>909</v>
+        <v>1204</v>
       </c>
       <c r="E196" s="8" t="n"/>
       <c r="F196" s="8" t="n"/>
@@ -6293,16 +6293,16 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>HQ7636</t>
+          <t>KI4563</t>
         </is>
       </c>
       <c r="D197" s="7" t="n">
-        <v>2257</v>
+        <v>800</v>
       </c>
       <c r="E197" s="8" t="n"/>
       <c r="F197" s="8" t="n"/>
@@ -6328,11 +6328,11 @@
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>HQ7638</t>
+          <t>KI4564</t>
         </is>
       </c>
       <c r="D198" s="7" t="n">
-        <v>241</v>
+        <v>403</v>
       </c>
       <c r="E198" s="8" t="n"/>
       <c r="F198" s="8" t="n"/>
@@ -6353,16 +6353,16 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>GHOST MOTO LOW W</t>
         </is>
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>JQ6439</t>
+          <t>KI4566</t>
         </is>
       </c>
       <c r="D199" s="7" t="n">
-        <v>304</v>
+        <v>1715</v>
       </c>
       <c r="E199" s="8" t="n"/>
       <c r="F199" s="8" t="n"/>
@@ -6383,16 +6383,16 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
         <is>
-          <t>KI0435</t>
+          <t>KI4568</t>
         </is>
       </c>
       <c r="D200" s="7" t="n">
-        <v>759</v>
+        <v>1390</v>
       </c>
       <c r="E200" s="8" t="n"/>
       <c r="F200" s="8" t="n"/>
@@ -6413,16 +6413,16 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
         <is>
-          <t>KI0436</t>
+          <t>KI4569</t>
         </is>
       </c>
       <c r="D201" s="7" t="n">
-        <v>1204</v>
+        <v>3064</v>
       </c>
       <c r="E201" s="8" t="n"/>
       <c r="F201" s="8" t="n"/>
@@ -6448,11 +6448,11 @@
       </c>
       <c r="C202" s="6" t="inlineStr">
         <is>
-          <t>KI4563</t>
+          <t>KI4570</t>
         </is>
       </c>
       <c r="D202" s="7" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E202" s="8" t="n"/>
       <c r="F202" s="8" t="n"/>
@@ -6478,11 +6478,11 @@
       </c>
       <c r="C203" s="6" t="inlineStr">
         <is>
-          <t>KI4564</t>
+          <t>KI4571</t>
         </is>
       </c>
       <c r="D203" s="7" t="n">
-        <v>403</v>
+        <v>280</v>
       </c>
       <c r="E203" s="8" t="n"/>
       <c r="F203" s="8" t="n"/>
@@ -6503,16 +6503,16 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>GHOST MOTO LOW W</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C204" s="6" t="inlineStr">
         <is>
-          <t>KI4566</t>
+          <t>KI4572</t>
         </is>
       </c>
       <c r="D204" s="7" t="n">
-        <v>1715</v>
+        <v>140</v>
       </c>
       <c r="E204" s="8" t="n"/>
       <c r="F204" s="8" t="n"/>
@@ -6538,11 +6538,11 @@
       </c>
       <c r="C205" s="6" t="inlineStr">
         <is>
-          <t>KI4568</t>
+          <t>KJ0645</t>
         </is>
       </c>
       <c r="D205" s="7" t="n">
-        <v>1390</v>
+        <v>1483</v>
       </c>
       <c r="E205" s="8" t="n"/>
       <c r="F205" s="8" t="n"/>
@@ -6568,11 +6568,11 @@
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>KI4569</t>
+          <t>LA4019</t>
         </is>
       </c>
       <c r="D206" s="7" t="n">
-        <v>3064</v>
+        <v>190</v>
       </c>
       <c r="E206" s="8" t="n"/>
       <c r="F206" s="8" t="n"/>
@@ -6598,11 +6598,11 @@
       </c>
       <c r="C207" s="6" t="inlineStr">
         <is>
-          <t>KI4570</t>
+          <t>LA7682</t>
         </is>
       </c>
       <c r="D207" s="7" t="n">
-        <v>100</v>
+        <v>8803</v>
       </c>
       <c r="E207" s="8" t="n"/>
       <c r="F207" s="8" t="n"/>
@@ -6628,11 +6628,11 @@
       </c>
       <c r="C208" s="6" t="inlineStr">
         <is>
-          <t>KI4571</t>
+          <t>LA7683</t>
         </is>
       </c>
       <c r="D208" s="7" t="n">
-        <v>280</v>
+        <v>5940</v>
       </c>
       <c r="E208" s="8" t="n"/>
       <c r="F208" s="8" t="n"/>
@@ -6648,21 +6648,21 @@
     <row r="209" ht="14" customHeight="1">
       <c r="A209" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>KI4572</t>
+          <t>IH6000</t>
         </is>
       </c>
       <c r="D209" s="7" t="n">
-        <v>140</v>
+        <v>6116</v>
       </c>
       <c r="E209" s="8" t="n"/>
       <c r="F209" s="8" t="n"/>
@@ -6678,21 +6678,21 @@
     <row r="210" ht="14" customHeight="1">
       <c r="A210" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
         <is>
-          <t>KJ0645</t>
+          <t>IH6001</t>
         </is>
       </c>
       <c r="D210" s="7" t="n">
-        <v>1483</v>
+        <v>7452</v>
       </c>
       <c r="E210" s="8" t="n"/>
       <c r="F210" s="8" t="n"/>
@@ -6708,21 +6708,21 @@
     <row r="211" ht="14" customHeight="1">
       <c r="A211" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
         <is>
-          <t>LA4019</t>
+          <t>JH6149</t>
         </is>
       </c>
       <c r="D211" s="7" t="n">
-        <v>190</v>
+        <v>373</v>
       </c>
       <c r="E211" s="8" t="n"/>
       <c r="F211" s="8" t="n"/>
@@ -6738,21 +6738,21 @@
     <row r="212" ht="14" customHeight="1">
       <c r="A212" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="C212" s="6" t="inlineStr">
         <is>
-          <t>LA7682</t>
+          <t>JH6151</t>
         </is>
       </c>
       <c r="D212" s="7" t="n">
-        <v>8803</v>
+        <v>575</v>
       </c>
       <c r="E212" s="8" t="n"/>
       <c r="F212" s="8" t="n"/>
@@ -6768,21 +6768,21 @@
     <row r="213" ht="14" customHeight="1">
       <c r="A213" s="4" t="inlineStr">
         <is>
-          <t>6B</t>
+          <t>6C</t>
         </is>
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="C213" s="6" t="inlineStr">
         <is>
-          <t>LA7683</t>
+          <t>KJ5430</t>
         </is>
       </c>
       <c r="D213" s="7" t="n">
-        <v>5940</v>
+        <v>94</v>
       </c>
       <c r="E213" s="8" t="n"/>
       <c r="F213" s="8" t="n"/>
@@ -6803,16 +6803,16 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>SAMBA</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="C214" s="6" t="inlineStr">
         <is>
-          <t>IH6000</t>
+          <t>KJ5431</t>
         </is>
       </c>
       <c r="D214" s="7" t="n">
-        <v>6116</v>
+        <v>16</v>
       </c>
       <c r="E214" s="8" t="n"/>
       <c r="F214" s="8" t="n"/>
@@ -6833,16 +6833,16 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>SAMBA</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="C215" s="6" t="inlineStr">
         <is>
-          <t>IH6001</t>
+          <t>KJ8225</t>
         </is>
       </c>
       <c r="D215" s="7" t="n">
-        <v>7452</v>
+        <v>1841</v>
       </c>
       <c r="E215" s="8" t="n"/>
       <c r="F215" s="8" t="n"/>
@@ -6863,16 +6863,16 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
         <is>
-          <t>JH6149</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D216" s="7" t="n">
-        <v>373</v>
+        <v>4279</v>
       </c>
       <c r="E216" s="8" t="n"/>
       <c r="F216" s="8" t="n"/>
@@ -6885,54 +6885,31 @@
         </is>
       </c>
     </row>
-    <row r="217" ht="14" customHeight="1">
-      <c r="A217" s="4" t="inlineStr">
-        <is>
-          <t>6C</t>
-        </is>
-      </c>
-      <c r="B217" s="5" t="inlineStr">
-        <is>
-          <t>SAMBA GOLF</t>
-        </is>
-      </c>
-      <c r="C217" s="6" t="inlineStr">
-        <is>
-          <t>JH6151</t>
-        </is>
-      </c>
-      <c r="D217" s="7" t="n">
-        <v>575</v>
-      </c>
-      <c r="E217" s="8" t="n"/>
-      <c r="F217" s="8" t="n"/>
-      <c r="G217" s="8" t="n"/>
-      <c r="H217" s="9" t="n"/>
-      <c r="I217" s="9" t="n"/>
-      <c r="J217" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="217" ht="16" customHeight="1">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>── 7部 ──</t>
         </is>
       </c>
     </row>
     <row r="218" ht="14" customHeight="1">
       <c r="A218" s="4" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
         <is>
-          <t>KJ5430</t>
+          <t>HQ3330</t>
         </is>
       </c>
       <c r="D218" s="7" t="n">
-        <v>94</v>
+        <v>2725</v>
       </c>
       <c r="E218" s="8" t="n"/>
       <c r="F218" s="8" t="n"/>
@@ -6948,21 +6925,21 @@
     <row r="219" ht="14" customHeight="1">
       <c r="A219" s="4" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C219" s="6" t="inlineStr">
         <is>
-          <t>KJ5431</t>
+          <t>HQ7638</t>
         </is>
       </c>
       <c r="D219" s="7" t="n">
-        <v>16</v>
+        <v>529</v>
       </c>
       <c r="E219" s="8" t="n"/>
       <c r="F219" s="8" t="n"/>
@@ -6978,21 +6955,21 @@
     <row r="220" ht="14" customHeight="1">
       <c r="A220" s="4" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C220" s="6" t="inlineStr">
         <is>
-          <t>KJ8225</t>
+          <t>JS1067</t>
         </is>
       </c>
       <c r="D220" s="7" t="n">
-        <v>1841</v>
+        <v>1633</v>
       </c>
       <c r="E220" s="8" t="n"/>
       <c r="F220" s="8" t="n"/>
@@ -7008,21 +6985,21 @@
     <row r="221" ht="14" customHeight="1">
       <c r="A221" s="4" t="inlineStr">
         <is>
-          <t>6C</t>
+          <t>7A</t>
         </is>
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>GHOST SPRINT W</t>
         </is>
       </c>
       <c r="C221" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KI4563</t>
         </is>
       </c>
       <c r="D221" s="7" t="n">
-        <v>4279</v>
+        <v>505</v>
       </c>
       <c r="E221" s="8" t="n"/>
       <c r="F221" s="8" t="n"/>
@@ -7035,10 +7012,33 @@
         </is>
       </c>
     </row>
-    <row r="222" ht="16" customHeight="1">
-      <c r="A222" s="3" t="inlineStr">
-        <is>
-          <t>── 7部 ──</t>
+    <row r="222" ht="14" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="B222" s="5" t="inlineStr">
+        <is>
+          <t>GHOST SPRINT W</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>KI4569</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="n">
+        <v>410</v>
+      </c>
+      <c r="E222" s="8" t="n"/>
+      <c r="F222" s="8" t="n"/>
+      <c r="G222" s="8" t="n"/>
+      <c r="H222" s="9" t="n"/>
+      <c r="I222" s="9" t="n"/>
+      <c r="J222" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -7055,11 +7055,11 @@
       </c>
       <c r="C223" s="6" t="inlineStr">
         <is>
-          <t>HQ3330</t>
+          <t>KJ0644</t>
         </is>
       </c>
       <c r="D223" s="7" t="n">
-        <v>8451</v>
+        <v>378</v>
       </c>
       <c r="E223" s="8" t="n"/>
       <c r="F223" s="8" t="n"/>
@@ -7085,11 +7085,11 @@
       </c>
       <c r="C224" s="6" t="inlineStr">
         <is>
-          <t>HQ7638</t>
+          <t>KJ0646</t>
         </is>
       </c>
       <c r="D224" s="7" t="n">
-        <v>529</v>
+        <v>1580</v>
       </c>
       <c r="E224" s="8" t="n"/>
       <c r="F224" s="8" t="n"/>
@@ -7115,11 +7115,11 @@
       </c>
       <c r="C225" s="6" t="inlineStr">
         <is>
-          <t>JS1067</t>
+          <t>LA7682</t>
         </is>
       </c>
       <c r="D225" s="7" t="n">
-        <v>3229</v>
+        <v>3424</v>
       </c>
       <c r="E225" s="8" t="n"/>
       <c r="F225" s="8" t="n"/>
@@ -7145,11 +7145,11 @@
       </c>
       <c r="C226" s="6" t="inlineStr">
         <is>
-          <t>KI4563</t>
+          <t>LA7683</t>
         </is>
       </c>
       <c r="D226" s="7" t="n">
-        <v>882</v>
+        <v>8233</v>
       </c>
       <c r="E226" s="8" t="n"/>
       <c r="F226" s="8" t="n"/>
@@ -7165,21 +7165,21 @@
     <row r="227" ht="14" customHeight="1">
       <c r="A227" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>TOKYO W NATI</t>
         </is>
       </c>
       <c r="C227" s="6" t="inlineStr">
         <is>
-          <t>KI4569</t>
+          <t>HP5175</t>
         </is>
       </c>
       <c r="D227" s="7" t="n">
-        <v>410</v>
+        <v>2859</v>
       </c>
       <c r="E227" s="8" t="n"/>
       <c r="F227" s="8" t="n"/>
@@ -7195,21 +7195,21 @@
     <row r="228" ht="14" customHeight="1">
       <c r="A228" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C228" s="6" t="inlineStr">
         <is>
-          <t>KI7740</t>
+          <t>HQ2887</t>
         </is>
       </c>
       <c r="D228" s="7" t="n">
-        <v>1919</v>
+        <v>300</v>
       </c>
       <c r="E228" s="8" t="n"/>
       <c r="F228" s="8" t="n"/>
@@ -7225,21 +7225,21 @@
     <row r="229" ht="14" customHeight="1">
       <c r="A229" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C229" s="6" t="inlineStr">
         <is>
-          <t>KJ0644</t>
+          <t>HQ9512</t>
         </is>
       </c>
       <c r="D229" s="7" t="n">
-        <v>378</v>
+        <v>598</v>
       </c>
       <c r="E229" s="8" t="n"/>
       <c r="F229" s="8" t="n"/>
@@ -7255,21 +7255,21 @@
     <row r="230" ht="14" customHeight="1">
       <c r="A230" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C230" s="6" t="inlineStr">
         <is>
-          <t>KJ0646</t>
+          <t>IH3999</t>
         </is>
       </c>
       <c r="D230" s="7" t="n">
-        <v>1580</v>
+        <v>525</v>
       </c>
       <c r="E230" s="8" t="n"/>
       <c r="F230" s="8" t="n"/>
@@ -7285,21 +7285,21 @@
     <row r="231" ht="14" customHeight="1">
       <c r="A231" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C231" s="6" t="inlineStr">
         <is>
-          <t>LA7682</t>
+          <t>JQ0597</t>
         </is>
       </c>
       <c r="D231" s="7" t="n">
-        <v>6683</v>
+        <v>5268</v>
       </c>
       <c r="E231" s="8" t="n"/>
       <c r="F231" s="8" t="n"/>
@@ -7315,21 +7315,21 @@
     <row r="232" ht="14" customHeight="1">
       <c r="A232" s="4" t="inlineStr">
         <is>
-          <t>7A</t>
+          <t>7B</t>
         </is>
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C232" s="6" t="inlineStr">
         <is>
-          <t>LA7683</t>
+          <t>KI3584</t>
         </is>
       </c>
       <c r="D232" s="7" t="n">
-        <v>11880</v>
+        <v>683</v>
       </c>
       <c r="E232" s="8" t="n"/>
       <c r="F232" s="8" t="n"/>
@@ -7350,16 +7350,16 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W NATI</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C233" s="6" t="inlineStr">
         <is>
-          <t>HP5175</t>
+          <t>KJ5221</t>
         </is>
       </c>
       <c r="D233" s="7" t="n">
-        <v>5718</v>
+        <v>1257</v>
       </c>
       <c r="E233" s="8" t="n"/>
       <c r="F233" s="8" t="n"/>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C234" s="6" t="inlineStr">
         <is>
-          <t>HQ2887</t>
+          <t>KJ7499</t>
         </is>
       </c>
       <c r="D234" s="7" t="n">
-        <v>6049</v>
+        <v>331</v>
       </c>
       <c r="E234" s="8" t="n"/>
       <c r="F234" s="8" t="n"/>
@@ -7415,11 +7415,11 @@
       </c>
       <c r="C235" s="6" t="inlineStr">
         <is>
-          <t>HQ9512</t>
+          <t>KJ7539</t>
         </is>
       </c>
       <c r="D235" s="7" t="n">
-        <v>1196</v>
+        <v>2730</v>
       </c>
       <c r="E235" s="8" t="n"/>
       <c r="F235" s="8" t="n"/>
@@ -7440,16 +7440,16 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C236" s="6" t="inlineStr">
         <is>
-          <t>IH3999</t>
+          <t>KJ7543</t>
         </is>
       </c>
       <c r="D236" s="7" t="n">
-        <v>1050</v>
+        <v>3211</v>
       </c>
       <c r="E236" s="8" t="n"/>
       <c r="F236" s="8" t="n"/>
@@ -7475,11 +7475,11 @@
       </c>
       <c r="C237" s="6" t="inlineStr">
         <is>
-          <t>JQ0597</t>
+          <t>KJ7544</t>
         </is>
       </c>
       <c r="D237" s="7" t="n">
-        <v>10536</v>
+        <v>673</v>
       </c>
       <c r="E237" s="8" t="n"/>
       <c r="F237" s="8" t="n"/>
@@ -7500,16 +7500,16 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>KI3584</t>
+          <t>KJ8377</t>
         </is>
       </c>
       <c r="D238" s="7" t="n">
-        <v>2131</v>
+        <v>1110</v>
       </c>
       <c r="E238" s="8" t="n"/>
       <c r="F238" s="8" t="n"/>
@@ -7535,11 +7535,11 @@
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>KJ5221</t>
+          <t>KJ8378</t>
         </is>
       </c>
       <c r="D239" s="7" t="n">
-        <v>2514</v>
+        <v>308</v>
       </c>
       <c r="E239" s="8" t="n"/>
       <c r="F239" s="8" t="n"/>
@@ -7565,11 +7565,11 @@
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>KJ7499</t>
+          <t>KK0030</t>
         </is>
       </c>
       <c r="D240" s="7" t="n">
-        <v>662</v>
+        <v>760</v>
       </c>
       <c r="E240" s="8" t="n"/>
       <c r="F240" s="8" t="n"/>
@@ -7595,11 +7595,11 @@
       </c>
       <c r="C241" s="6" t="inlineStr">
         <is>
-          <t>KJ7539</t>
+          <t>KK0031</t>
         </is>
       </c>
       <c r="D241" s="7" t="n">
-        <v>5460</v>
+        <v>1753</v>
       </c>
       <c r="E241" s="8" t="n"/>
       <c r="F241" s="8" t="n"/>
@@ -7625,11 +7625,11 @@
       </c>
       <c r="C242" s="6" t="inlineStr">
         <is>
-          <t>KJ7541</t>
+          <t>KK2621</t>
         </is>
       </c>
       <c r="D242" s="7" t="n">
-        <v>2812</v>
+        <v>2358</v>
       </c>
       <c r="E242" s="8" t="n"/>
       <c r="F242" s="8" t="n"/>
@@ -7642,54 +7642,31 @@
         </is>
       </c>
     </row>
-    <row r="243" ht="14" customHeight="1">
-      <c r="A243" s="4" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
-      <c r="B243" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C243" s="6" t="inlineStr">
-        <is>
-          <t>KJ7542</t>
-        </is>
-      </c>
-      <c r="D243" s="7" t="n">
-        <v>660</v>
-      </c>
-      <c r="E243" s="8" t="n"/>
-      <c r="F243" s="8" t="n"/>
-      <c r="G243" s="8" t="n"/>
-      <c r="H243" s="9" t="n"/>
-      <c r="I243" s="9" t="n"/>
-      <c r="J243" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="243" ht="16" customHeight="1">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>── 8部 ──</t>
         </is>
       </c>
     </row>
     <row r="244" ht="14" customHeight="1">
       <c r="A244" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C244" s="6" t="inlineStr">
         <is>
-          <t>KJ7543</t>
+          <t>IH6001</t>
         </is>
       </c>
       <c r="D244" s="7" t="n">
-        <v>8804</v>
+        <v>5000</v>
       </c>
       <c r="E244" s="8" t="n"/>
       <c r="F244" s="8" t="n"/>
@@ -7705,21 +7682,21 @@
     <row r="245" ht="14" customHeight="1">
       <c r="A245" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C245" s="6" t="inlineStr">
         <is>
-          <t>KJ7544</t>
+          <t>KH7374</t>
         </is>
       </c>
       <c r="D245" s="7" t="n">
-        <v>2622</v>
+        <v>5464</v>
       </c>
       <c r="E245" s="8" t="n"/>
       <c r="F245" s="8" t="n"/>
@@ -7735,21 +7712,21 @@
     <row r="246" ht="14" customHeight="1">
       <c r="A246" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>BUSENITZ</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>KJ7551</t>
+          <t>KI7713</t>
         </is>
       </c>
       <c r="D246" s="7" t="n">
-        <v>4172</v>
+        <v>264</v>
       </c>
       <c r="E246" s="8" t="n"/>
       <c r="F246" s="8" t="n"/>
@@ -7765,21 +7742,21 @@
     <row r="247" ht="14" customHeight="1">
       <c r="A247" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>BUSENITZ VINTAGE</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>KJ7552</t>
+          <t>KI7714</t>
         </is>
       </c>
       <c r="D247" s="7" t="n">
-        <v>1250</v>
+        <v>668</v>
       </c>
       <c r="E247" s="8" t="n"/>
       <c r="F247" s="8" t="n"/>
@@ -7795,21 +7772,21 @@
     <row r="248" ht="14" customHeight="1">
       <c r="A248" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>BUSENITZ VINTAGE</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>KJ8377</t>
+          <t>KI7725</t>
         </is>
       </c>
       <c r="D248" s="7" t="n">
-        <v>1110</v>
+        <v>636</v>
       </c>
       <c r="E248" s="8" t="n"/>
       <c r="F248" s="8" t="n"/>
@@ -7825,21 +7802,21 @@
     <row r="249" ht="14" customHeight="1">
       <c r="A249" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>BUSENITZ</t>
         </is>
       </c>
       <c r="C249" s="6" t="inlineStr">
         <is>
-          <t>KJ8378</t>
+          <t>KJ0259</t>
         </is>
       </c>
       <c r="D249" s="7" t="n">
-        <v>616</v>
+        <v>203</v>
       </c>
       <c r="E249" s="8" t="n"/>
       <c r="F249" s="8" t="n"/>
@@ -7855,21 +7832,21 @@
     <row r="250" ht="14" customHeight="1">
       <c r="A250" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>BUSENITZ</t>
         </is>
       </c>
       <c r="C250" s="6" t="inlineStr">
         <is>
-          <t>KK0030</t>
+          <t>KJ0260</t>
         </is>
       </c>
       <c r="D250" s="7" t="n">
-        <v>1520</v>
+        <v>865</v>
       </c>
       <c r="E250" s="8" t="n"/>
       <c r="F250" s="8" t="n"/>
@@ -7885,21 +7862,21 @@
     <row r="251" ht="14" customHeight="1">
       <c r="A251" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>BUSENITZ</t>
         </is>
       </c>
       <c r="C251" s="6" t="inlineStr">
         <is>
-          <t>KK0031</t>
+          <t>KJ0261</t>
         </is>
       </c>
       <c r="D251" s="7" t="n">
-        <v>3506</v>
+        <v>694</v>
       </c>
       <c r="E251" s="8" t="n"/>
       <c r="F251" s="8" t="n"/>
@@ -7915,21 +7892,21 @@
     <row r="252" ht="14" customHeight="1">
       <c r="A252" s="4" t="inlineStr">
         <is>
-          <t>7B</t>
+          <t>8A</t>
         </is>
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C252" s="6" t="inlineStr">
         <is>
-          <t>KK2621</t>
+          <t>KJ7892</t>
         </is>
       </c>
       <c r="D252" s="7" t="n">
-        <v>7554</v>
+        <v>10951</v>
       </c>
       <c r="E252" s="8" t="n"/>
       <c r="F252" s="8" t="n"/>
@@ -7942,10 +7919,33 @@
         </is>
       </c>
     </row>
-    <row r="253" ht="16" customHeight="1">
-      <c r="A253" s="3" t="inlineStr">
-        <is>
-          <t>── 8部 ──</t>
+    <row r="253" ht="14" customHeight="1">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
+      <c r="B253" s="5" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>KJ7893</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="n">
+        <v>675</v>
+      </c>
+      <c r="E253" s="8" t="n"/>
+      <c r="F253" s="8" t="n"/>
+      <c r="G253" s="8" t="n"/>
+      <c r="H253" s="9" t="n"/>
+      <c r="I253" s="9" t="n"/>
+      <c r="J253" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -7957,16 +7957,16 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>SAMBA</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C254" s="6" t="inlineStr">
         <is>
-          <t>IH6001</t>
+          <t>KJ7895</t>
         </is>
       </c>
       <c r="D254" s="7" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="E254" s="8" t="n"/>
       <c r="F254" s="8" t="n"/>
@@ -7987,16 +7987,16 @@
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C255" s="6" t="inlineStr">
         <is>
-          <t>KH7374</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D255" s="7" t="n">
-        <v>5464</v>
+        <v>2436</v>
       </c>
       <c r="E255" s="8" t="n"/>
       <c r="F255" s="8" t="n"/>
@@ -8012,21 +8012,21 @@
     <row r="256" ht="14" customHeight="1">
       <c r="A256" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ</t>
+          <t>BB F50 GHOST SPRINT</t>
         </is>
       </c>
       <c r="C256" s="6" t="inlineStr">
         <is>
-          <t>KI7713</t>
+          <t>HP4218</t>
         </is>
       </c>
       <c r="D256" s="7" t="n">
-        <v>264</v>
+        <v>7247</v>
       </c>
       <c r="E256" s="8" t="n"/>
       <c r="F256" s="8" t="n"/>
@@ -8042,21 +8042,21 @@
     <row r="257" ht="14" customHeight="1">
       <c r="A257" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ VINTAGE</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C257" s="6" t="inlineStr">
         <is>
-          <t>KI7714</t>
+          <t>HQ7636</t>
         </is>
       </c>
       <c r="D257" s="7" t="n">
-        <v>668</v>
+        <v>637</v>
       </c>
       <c r="E257" s="8" t="n"/>
       <c r="F257" s="8" t="n"/>
@@ -8072,21 +8072,21 @@
     <row r="258" ht="14" customHeight="1">
       <c r="A258" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ VINTAGE</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C258" s="6" t="inlineStr">
         <is>
-          <t>KI7725</t>
+          <t>HQ7637</t>
         </is>
       </c>
       <c r="D258" s="7" t="n">
-        <v>636</v>
+        <v>365</v>
       </c>
       <c r="E258" s="8" t="n"/>
       <c r="F258" s="8" t="n"/>
@@ -8102,21 +8102,21 @@
     <row r="259" ht="14" customHeight="1">
       <c r="A259" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ</t>
+          <t>adidas F50 ADIFRAME</t>
         </is>
       </c>
       <c r="C259" s="6" t="inlineStr">
         <is>
-          <t>KJ0259</t>
+          <t>KH6569</t>
         </is>
       </c>
       <c r="D259" s="7" t="n">
-        <v>203</v>
+        <v>402</v>
       </c>
       <c r="E259" s="8" t="n"/>
       <c r="F259" s="8" t="n"/>
@@ -8132,21 +8132,21 @@
     <row r="260" ht="14" customHeight="1">
       <c r="A260" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ</t>
+          <t>adidas F50 ADIFRAME</t>
         </is>
       </c>
       <c r="C260" s="6" t="inlineStr">
         <is>
-          <t>KJ0260</t>
+          <t>KH6570</t>
         </is>
       </c>
       <c r="D260" s="7" t="n">
-        <v>865</v>
+        <v>402</v>
       </c>
       <c r="E260" s="8" t="n"/>
       <c r="F260" s="8" t="n"/>
@@ -8162,21 +8162,21 @@
     <row r="261" ht="14" customHeight="1">
       <c r="A261" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>BUSENITZ</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C261" s="6" t="inlineStr">
         <is>
-          <t>KJ0261</t>
+          <t>KI0435</t>
         </is>
       </c>
       <c r="D261" s="7" t="n">
-        <v>694</v>
+        <v>2882</v>
       </c>
       <c r="E261" s="8" t="n"/>
       <c r="F261" s="8" t="n"/>
@@ -8192,21 +8192,21 @@
     <row r="262" ht="14" customHeight="1">
       <c r="A262" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C262" s="6" t="inlineStr">
         <is>
-          <t>KJ7892</t>
+          <t>KI0436</t>
         </is>
       </c>
       <c r="D262" s="7" t="n">
-        <v>10951</v>
+        <v>4981</v>
       </c>
       <c r="E262" s="8" t="n"/>
       <c r="F262" s="8" t="n"/>
@@ -8222,21 +8222,21 @@
     <row r="263" ht="14" customHeight="1">
       <c r="A263" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C263" s="6" t="inlineStr">
         <is>
-          <t>KJ7893</t>
+          <t>KI7738</t>
         </is>
       </c>
       <c r="D263" s="7" t="n">
-        <v>675</v>
+        <v>1198</v>
       </c>
       <c r="E263" s="8" t="n"/>
       <c r="F263" s="8" t="n"/>
@@ -8252,21 +8252,21 @@
     <row r="264" ht="14" customHeight="1">
       <c r="A264" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C264" s="6" t="inlineStr">
         <is>
-          <t>KJ7895</t>
+          <t>KI7739</t>
         </is>
       </c>
       <c r="D264" s="7" t="n">
-        <v>200</v>
+        <v>853</v>
       </c>
       <c r="E264" s="8" t="n"/>
       <c r="F264" s="8" t="n"/>
@@ -8282,21 +8282,21 @@
     <row r="265" ht="14" customHeight="1">
       <c r="A265" s="4" t="inlineStr">
         <is>
-          <t>8A</t>
+          <t>8B</t>
         </is>
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KI7740</t>
         </is>
       </c>
       <c r="D265" s="7" t="n">
-        <v>2436</v>
+        <v>2944</v>
       </c>
       <c r="E265" s="8" t="n"/>
       <c r="F265" s="8" t="n"/>
@@ -8317,16 +8317,16 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>BB F50 GHOST SPRINT</t>
+          <t>adidas F50 ADIFRAME W</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
         <is>
-          <t>HP4218</t>
+          <t>KK0908</t>
         </is>
       </c>
       <c r="D266" s="7" t="n">
-        <v>7247</v>
+        <v>345</v>
       </c>
       <c r="E266" s="8" t="n"/>
       <c r="F266" s="8" t="n"/>
@@ -8347,16 +8347,16 @@
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>adidas F50 ADIFRAME W</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
         <is>
-          <t>HQ7636</t>
+          <t>KK0909</t>
         </is>
       </c>
       <c r="D267" s="7" t="n">
-        <v>637</v>
+        <v>310</v>
       </c>
       <c r="E267" s="8" t="n"/>
       <c r="F267" s="8" t="n"/>
@@ -8382,11 +8382,11 @@
       </c>
       <c r="C268" s="6" t="inlineStr">
         <is>
-          <t>HQ7637</t>
+          <t>KZ7290</t>
         </is>
       </c>
       <c r="D268" s="7" t="n">
-        <v>365</v>
+        <v>930</v>
       </c>
       <c r="E268" s="8" t="n"/>
       <c r="F268" s="8" t="n"/>
@@ -8407,16 +8407,16 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME</t>
+          <t>GHOST SPRINT BALLET W</t>
         </is>
       </c>
       <c r="C269" s="6" t="inlineStr">
         <is>
-          <t>KH6569</t>
+          <t>KZ7291</t>
         </is>
       </c>
       <c r="D269" s="7" t="n">
-        <v>402</v>
+        <v>1230</v>
       </c>
       <c r="E269" s="8" t="n"/>
       <c r="F269" s="8" t="n"/>
@@ -8432,21 +8432,21 @@
     <row r="270" ht="14" customHeight="1">
       <c r="A270" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C270" s="6" t="inlineStr">
         <is>
-          <t>KH6570</t>
+          <t>IH3991</t>
         </is>
       </c>
       <c r="D270" s="7" t="n">
-        <v>402</v>
+        <v>442</v>
       </c>
       <c r="E270" s="8" t="n"/>
       <c r="F270" s="8" t="n"/>
@@ -8462,21 +8462,21 @@
     <row r="271" ht="14" customHeight="1">
       <c r="A271" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C271" s="6" t="inlineStr">
         <is>
-          <t>KI0435</t>
+          <t>IH3994</t>
         </is>
       </c>
       <c r="D271" s="7" t="n">
-        <v>2882</v>
+        <v>1829</v>
       </c>
       <c r="E271" s="8" t="n"/>
       <c r="F271" s="8" t="n"/>
@@ -8492,21 +8492,21 @@
     <row r="272" ht="14" customHeight="1">
       <c r="A272" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C272" s="6" t="inlineStr">
         <is>
-          <t>KI0436</t>
+          <t>IH3999</t>
         </is>
       </c>
       <c r="D272" s="7" t="n">
-        <v>4981</v>
+        <v>2874</v>
       </c>
       <c r="E272" s="8" t="n"/>
       <c r="F272" s="8" t="n"/>
@@ -8522,21 +8522,21 @@
     <row r="273" ht="14" customHeight="1">
       <c r="A273" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C273" s="6" t="inlineStr">
         <is>
-          <t>KI7738</t>
+          <t>JR4790</t>
         </is>
       </c>
       <c r="D273" s="7" t="n">
-        <v>1198</v>
+        <v>4793</v>
       </c>
       <c r="E273" s="8" t="n"/>
       <c r="F273" s="8" t="n"/>
@@ -8552,21 +8552,21 @@
     <row r="274" ht="14" customHeight="1">
       <c r="A274" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C274" s="6" t="inlineStr">
         <is>
-          <t>KI7739</t>
+          <t>KI3584</t>
         </is>
       </c>
       <c r="D274" s="7" t="n">
-        <v>853</v>
+        <v>2100</v>
       </c>
       <c r="E274" s="8" t="n"/>
       <c r="F274" s="8" t="n"/>
@@ -8582,21 +8582,21 @@
     <row r="275" ht="14" customHeight="1">
       <c r="A275" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
         <is>
-          <t>KI7740</t>
+          <t>KJ7510</t>
         </is>
       </c>
       <c r="D275" s="7" t="n">
-        <v>2944</v>
+        <v>4200</v>
       </c>
       <c r="E275" s="8" t="n"/>
       <c r="F275" s="8" t="n"/>
@@ -8612,21 +8612,21 @@
     <row r="276" ht="14" customHeight="1">
       <c r="A276" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr">
         <is>
-          <t>KK0908</t>
+          <t>KJ7542</t>
         </is>
       </c>
       <c r="D276" s="7" t="n">
-        <v>345</v>
+        <v>480</v>
       </c>
       <c r="E276" s="8" t="n"/>
       <c r="F276" s="8" t="n"/>
@@ -8642,21 +8642,21 @@
     <row r="277" ht="14" customHeight="1">
       <c r="A277" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
         <is>
-          <t>KK0909</t>
+          <t>KJ8377</t>
         </is>
       </c>
       <c r="D277" s="7" t="n">
-        <v>310</v>
+        <v>1366</v>
       </c>
       <c r="E277" s="8" t="n"/>
       <c r="F277" s="8" t="n"/>
@@ -8672,21 +8672,21 @@
     <row r="278" ht="14" customHeight="1">
       <c r="A278" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C278" s="6" t="inlineStr">
         <is>
-          <t>KZ7290</t>
+          <t>KJ8378</t>
         </is>
       </c>
       <c r="D278" s="7" t="n">
-        <v>930</v>
+        <v>600</v>
       </c>
       <c r="E278" s="8" t="n"/>
       <c r="F278" s="8" t="n"/>
@@ -8702,21 +8702,21 @@
     <row r="279" ht="14" customHeight="1">
       <c r="A279" s="4" t="inlineStr">
         <is>
-          <t>8B</t>
+          <t>8C</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C279" s="6" t="inlineStr">
         <is>
-          <t>KZ7291</t>
+          <t>LA3255</t>
         </is>
       </c>
       <c r="D279" s="7" t="n">
-        <v>1230</v>
+        <v>1598</v>
       </c>
       <c r="E279" s="8" t="n"/>
       <c r="F279" s="8" t="n"/>
@@ -8729,54 +8729,31 @@
         </is>
       </c>
     </row>
-    <row r="280" ht="14" customHeight="1">
-      <c r="A280" s="4" t="inlineStr">
-        <is>
-          <t>8C</t>
-        </is>
-      </c>
-      <c r="B280" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C280" s="6" t="inlineStr">
-        <is>
-          <t>IH3991</t>
-        </is>
-      </c>
-      <c r="D280" s="7" t="n">
-        <v>442</v>
-      </c>
-      <c r="E280" s="8" t="n"/>
-      <c r="F280" s="8" t="n"/>
-      <c r="G280" s="8" t="n"/>
-      <c r="H280" s="9" t="n"/>
-      <c r="I280" s="9" t="n"/>
-      <c r="J280" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="280" ht="16" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>── 9部 ──</t>
         </is>
       </c>
     </row>
     <row r="281" ht="14" customHeight="1">
       <c r="A281" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C281" s="6" t="inlineStr">
         <is>
-          <t>IH3994</t>
+          <t>IG6045</t>
         </is>
       </c>
       <c r="D281" s="7" t="n">
-        <v>1829</v>
+        <v>28903</v>
       </c>
       <c r="E281" s="8" t="n"/>
       <c r="F281" s="8" t="n"/>
@@ -8792,21 +8769,21 @@
     <row r="282" ht="14" customHeight="1">
       <c r="A282" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C282" s="6" t="inlineStr">
         <is>
-          <t>IH3999</t>
+          <t>IG6047</t>
         </is>
       </c>
       <c r="D282" s="7" t="n">
-        <v>4064</v>
+        <v>916</v>
       </c>
       <c r="E282" s="8" t="n"/>
       <c r="F282" s="8" t="n"/>
@@ -8822,21 +8799,21 @@
     <row r="283" ht="14" customHeight="1">
       <c r="A283" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C283" s="6" t="inlineStr">
         <is>
-          <t>JR4790</t>
+          <t>IG6049</t>
         </is>
       </c>
       <c r="D283" s="7" t="n">
-        <v>4793</v>
+        <v>5950</v>
       </c>
       <c r="E283" s="8" t="n"/>
       <c r="F283" s="8" t="n"/>
@@ -8852,21 +8829,21 @@
     <row r="284" ht="14" customHeight="1">
       <c r="A284" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C284" s="6" t="inlineStr">
         <is>
-          <t>KI3584</t>
+          <t>KK4234</t>
         </is>
       </c>
       <c r="D284" s="7" t="n">
-        <v>2100</v>
+        <v>4146</v>
       </c>
       <c r="E284" s="8" t="n"/>
       <c r="F284" s="8" t="n"/>
@@ -8882,21 +8859,21 @@
     <row r="285" ht="14" customHeight="1">
       <c r="A285" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C285" s="6" t="inlineStr">
         <is>
-          <t>KJ7510</t>
+          <t>KZ7071</t>
         </is>
       </c>
       <c r="D285" s="7" t="n">
-        <v>4200</v>
+        <v>6969</v>
       </c>
       <c r="E285" s="8" t="n"/>
       <c r="F285" s="8" t="n"/>
@@ -8912,21 +8889,21 @@
     <row r="286" ht="14" customHeight="1">
       <c r="A286" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9A</t>
         </is>
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C286" s="6" t="inlineStr">
         <is>
-          <t>KJ7542</t>
+          <t>KZ7072</t>
         </is>
       </c>
       <c r="D286" s="7" t="n">
-        <v>480</v>
+        <v>5468</v>
       </c>
       <c r="E286" s="8" t="n"/>
       <c r="F286" s="8" t="n"/>
@@ -8942,7 +8919,7 @@
     <row r="287" ht="14" customHeight="1">
       <c r="A287" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B287" s="5" t="inlineStr">
@@ -8952,11 +8929,11 @@
       </c>
       <c r="C287" s="6" t="inlineStr">
         <is>
-          <t>KJ7552</t>
+          <t>IH3994</t>
         </is>
       </c>
       <c r="D287" s="7" t="n">
-        <v>775</v>
+        <v>1177</v>
       </c>
       <c r="E287" s="8" t="n"/>
       <c r="F287" s="8" t="n"/>
@@ -8972,21 +8949,21 @@
     <row r="288" ht="14" customHeight="1">
       <c r="A288" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
         <is>
-          <t>KJ8377</t>
+          <t>JI0182</t>
         </is>
       </c>
       <c r="D288" s="7" t="n">
-        <v>1682</v>
+        <v>322</v>
       </c>
       <c r="E288" s="8" t="n"/>
       <c r="F288" s="8" t="n"/>
@@ -9002,21 +8979,21 @@
     <row r="289" ht="14" customHeight="1">
       <c r="A289" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
         <is>
-          <t>KJ8378</t>
+          <t>KH9653</t>
         </is>
       </c>
       <c r="D289" s="7" t="n">
-        <v>600</v>
+        <v>1120</v>
       </c>
       <c r="E289" s="8" t="n"/>
       <c r="F289" s="8" t="n"/>
@@ -9032,21 +9009,21 @@
     <row r="290" ht="14" customHeight="1">
       <c r="A290" s="4" t="inlineStr">
         <is>
-          <t>8C</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C290" s="6" t="inlineStr">
         <is>
-          <t>LA3255</t>
+          <t>KJ1674</t>
         </is>
       </c>
       <c r="D290" s="7" t="n">
-        <v>1598</v>
+        <v>2103</v>
       </c>
       <c r="E290" s="8" t="n"/>
       <c r="F290" s="8" t="n"/>
@@ -9059,31 +9036,54 @@
         </is>
       </c>
     </row>
-    <row r="291" ht="16" customHeight="1">
-      <c r="A291" s="3" t="inlineStr">
-        <is>
-          <t>── 9部 ──</t>
+    <row r="291" ht="14" customHeight="1">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
+      <c r="B291" s="5" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0</t>
+        </is>
+      </c>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>KJ7895</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="n">
+        <v>11247</v>
+      </c>
+      <c r="E291" s="8" t="n"/>
+      <c r="F291" s="8" t="n"/>
+      <c r="G291" s="8" t="n"/>
+      <c r="H291" s="9" t="n"/>
+      <c r="I291" s="9" t="n"/>
+      <c r="J291" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="292" ht="14" customHeight="1">
       <c r="A292" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C292" s="6" t="inlineStr">
         <is>
-          <t>IG6045</t>
+          <t>KZ6449</t>
         </is>
       </c>
       <c r="D292" s="7" t="n">
-        <v>28903</v>
+        <v>7616</v>
       </c>
       <c r="E292" s="8" t="n"/>
       <c r="F292" s="8" t="n"/>
@@ -9099,21 +9099,21 @@
     <row r="293" ht="14" customHeight="1">
       <c r="A293" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C293" s="6" t="inlineStr">
         <is>
-          <t>IG6047</t>
+          <t>KZ8301</t>
         </is>
       </c>
       <c r="D293" s="7" t="n">
-        <v>916</v>
+        <v>6025</v>
       </c>
       <c r="E293" s="8" t="n"/>
       <c r="F293" s="8" t="n"/>
@@ -9129,21 +9129,21 @@
     <row r="294" ht="14" customHeight="1">
       <c r="A294" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9B</t>
         </is>
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C294" s="6" t="inlineStr">
         <is>
-          <t>IG6049</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D294" s="7" t="n">
-        <v>5950</v>
+        <v>1154</v>
       </c>
       <c r="E294" s="8" t="n"/>
       <c r="F294" s="8" t="n"/>
@@ -9159,21 +9159,21 @@
     <row r="295" ht="14" customHeight="1">
       <c r="A295" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>HP5123</t>
         </is>
       </c>
       <c r="C295" s="6" t="inlineStr">
         <is>
-          <t>KK4234</t>
+          <t>HP5123</t>
         </is>
       </c>
       <c r="D295" s="7" t="n">
-        <v>4146</v>
+        <v>2000</v>
       </c>
       <c r="E295" s="8" t="n"/>
       <c r="F295" s="8" t="n"/>
@@ -9189,21 +9189,21 @@
     <row r="296" ht="14" customHeight="1">
       <c r="A296" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C296" s="6" t="inlineStr">
         <is>
-          <t>KZ7071</t>
+          <t>HQ4909</t>
         </is>
       </c>
       <c r="D296" s="7" t="n">
-        <v>6969</v>
+        <v>1865</v>
       </c>
       <c r="E296" s="8" t="n"/>
       <c r="F296" s="8" t="n"/>
@@ -9219,21 +9219,21 @@
     <row r="297" ht="14" customHeight="1">
       <c r="A297" s="4" t="inlineStr">
         <is>
-          <t>9A</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>SL 72 RS EL I</t>
         </is>
       </c>
       <c r="C297" s="6" t="inlineStr">
         <is>
-          <t>KZ7072</t>
+          <t>IH2978</t>
         </is>
       </c>
       <c r="D297" s="7" t="n">
-        <v>5468</v>
+        <v>727</v>
       </c>
       <c r="E297" s="8" t="n"/>
       <c r="F297" s="8" t="n"/>
@@ -9249,21 +9249,21 @@
     <row r="298" ht="14" customHeight="1">
       <c r="A298" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>SL 72 RS EL C</t>
         </is>
       </c>
       <c r="C298" s="6" t="inlineStr">
         <is>
-          <t>IH3994</t>
+          <t>IH2982</t>
         </is>
       </c>
       <c r="D298" s="7" t="n">
-        <v>1177</v>
+        <v>260</v>
       </c>
       <c r="E298" s="8" t="n"/>
       <c r="F298" s="8" t="n"/>
@@ -9279,21 +9279,21 @@
     <row r="299" ht="14" customHeight="1">
       <c r="A299" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>SL 72 RS EL C</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
         <is>
-          <t>JI0182</t>
+          <t>JH9953</t>
         </is>
       </c>
       <c r="D299" s="7" t="n">
-        <v>2145</v>
+        <v>263</v>
       </c>
       <c r="E299" s="8" t="n"/>
       <c r="F299" s="8" t="n"/>
@@ -9309,21 +9309,21 @@
     <row r="300" ht="14" customHeight="1">
       <c r="A300" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>SL 72 RS EL I</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
         <is>
-          <t>JI0183</t>
+          <t>JI3089</t>
         </is>
       </c>
       <c r="D300" s="7" t="n">
-        <v>2079</v>
+        <v>455</v>
       </c>
       <c r="E300" s="8" t="n"/>
       <c r="F300" s="8" t="n"/>
@@ -9339,7 +9339,7 @@
     <row r="301" ht="14" customHeight="1">
       <c r="A301" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B301" s="5" t="inlineStr">
@@ -9349,11 +9349,11 @@
       </c>
       <c r="C301" s="6" t="inlineStr">
         <is>
-          <t>KH9653</t>
+          <t>JQ9824</t>
         </is>
       </c>
       <c r="D301" s="7" t="n">
-        <v>1120</v>
+        <v>1608</v>
       </c>
       <c r="E301" s="8" t="n"/>
       <c r="F301" s="8" t="n"/>
@@ -9369,7 +9369,7 @@
     <row r="302" ht="14" customHeight="1">
       <c r="A302" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B302" s="5" t="inlineStr">
@@ -9379,11 +9379,11 @@
       </c>
       <c r="C302" s="6" t="inlineStr">
         <is>
-          <t>KJ1674</t>
+          <t>KH9652</t>
         </is>
       </c>
       <c r="D302" s="7" t="n">
-        <v>2103</v>
+        <v>890</v>
       </c>
       <c r="E302" s="8" t="n"/>
       <c r="F302" s="8" t="n"/>
@@ -9399,21 +9399,21 @@
     <row r="303" ht="14" customHeight="1">
       <c r="A303" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C303" s="6" t="inlineStr">
         <is>
-          <t>KJ7510</t>
+          <t>KH9653</t>
         </is>
       </c>
       <c r="D303" s="7" t="n">
-        <v>3929</v>
+        <v>1134</v>
       </c>
       <c r="E303" s="8" t="n"/>
       <c r="F303" s="8" t="n"/>
@@ -9429,21 +9429,21 @@
     <row r="304" ht="14" customHeight="1">
       <c r="A304" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C304" s="6" t="inlineStr">
         <is>
-          <t>KJ7895</t>
+          <t>KH9656</t>
         </is>
       </c>
       <c r="D304" s="7" t="n">
-        <v>11247</v>
+        <v>152</v>
       </c>
       <c r="E304" s="8" t="n"/>
       <c r="F304" s="8" t="n"/>
@@ -9459,21 +9459,21 @@
     <row r="305" ht="14" customHeight="1">
       <c r="A305" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>KZ6449</t>
+          <t>KH9657</t>
         </is>
       </c>
       <c r="D305" s="7" t="n">
-        <v>7616</v>
+        <v>300</v>
       </c>
       <c r="E305" s="8" t="n"/>
       <c r="F305" s="8" t="n"/>
@@ -9489,21 +9489,21 @@
     <row r="306" ht="14" customHeight="1">
       <c r="A306" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>KZ8301</t>
+          <t>KH9658</t>
         </is>
       </c>
       <c r="D306" s="7" t="n">
-        <v>6025</v>
+        <v>152</v>
       </c>
       <c r="E306" s="8" t="n"/>
       <c r="F306" s="8" t="n"/>
@@ -9519,21 +9519,21 @@
     <row r="307" ht="14" customHeight="1">
       <c r="A307" s="4" t="inlineStr">
         <is>
-          <t>9B</t>
+          <t>9C</t>
         </is>
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>SL 72 RS J</t>
         </is>
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KJ0690</t>
         </is>
       </c>
       <c r="D307" s="7" t="n">
-        <v>1154</v>
+        <v>1352</v>
       </c>
       <c r="E307" s="8" t="n"/>
       <c r="F307" s="8" t="n"/>
@@ -9554,16 +9554,16 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>HP5123</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C308" s="6" t="inlineStr">
         <is>
-          <t>HP5123</t>
+          <t>KJ1666</t>
         </is>
       </c>
       <c r="D308" s="7" t="n">
-        <v>4000</v>
+        <v>2516</v>
       </c>
       <c r="E308" s="8" t="n"/>
       <c r="F308" s="8" t="n"/>
@@ -9589,11 +9589,11 @@
       </c>
       <c r="C309" s="6" t="inlineStr">
         <is>
-          <t>HQ4909</t>
+          <t>KJ1667</t>
         </is>
       </c>
       <c r="D309" s="7" t="n">
-        <v>9127</v>
+        <v>1704</v>
       </c>
       <c r="E309" s="8" t="n"/>
       <c r="F309" s="8" t="n"/>
@@ -9614,16 +9614,16 @@
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS EL I</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C310" s="6" t="inlineStr">
         <is>
-          <t>IH2978</t>
+          <t>KJ1669</t>
         </is>
       </c>
       <c r="D310" s="7" t="n">
-        <v>1454</v>
+        <v>1032</v>
       </c>
       <c r="E310" s="8" t="n"/>
       <c r="F310" s="8" t="n"/>
@@ -9644,16 +9644,16 @@
       </c>
       <c r="B311" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS EL C</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C311" s="6" t="inlineStr">
         <is>
-          <t>IH2982</t>
+          <t>KJ1670</t>
         </is>
       </c>
       <c r="D311" s="7" t="n">
-        <v>520</v>
+        <v>1257</v>
       </c>
       <c r="E311" s="8" t="n"/>
       <c r="F311" s="8" t="n"/>
@@ -9674,16 +9674,16 @@
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS EL C</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C312" s="6" t="inlineStr">
         <is>
-          <t>JH9953</t>
+          <t>KJ1672</t>
         </is>
       </c>
       <c r="D312" s="7" t="n">
-        <v>526</v>
+        <v>2910</v>
       </c>
       <c r="E312" s="8" t="n"/>
       <c r="F312" s="8" t="n"/>
@@ -9704,16 +9704,16 @@
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS EL I</t>
+          <t>SL 72 RS</t>
         </is>
       </c>
       <c r="C313" s="6" t="inlineStr">
         <is>
-          <t>JI3089</t>
+          <t>KJ1673</t>
         </is>
       </c>
       <c r="D313" s="7" t="n">
-        <v>910</v>
+        <v>389</v>
       </c>
       <c r="E313" s="8" t="n"/>
       <c r="F313" s="8" t="n"/>
@@ -9734,16 +9734,16 @@
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>SL 72 OG W</t>
         </is>
       </c>
       <c r="C314" s="6" t="inlineStr">
         <is>
-          <t>JQ9824</t>
+          <t>KJ2282</t>
         </is>
       </c>
       <c r="D314" s="7" t="n">
-        <v>6432</v>
+        <v>1112</v>
       </c>
       <c r="E314" s="8" t="n"/>
       <c r="F314" s="8" t="n"/>
@@ -9756,54 +9756,31 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="14" customHeight="1">
-      <c r="A315" s="4" t="inlineStr">
-        <is>
-          <t>9C</t>
-        </is>
-      </c>
-      <c r="B315" s="5" t="inlineStr">
-        <is>
-          <t>SL 72 RS</t>
-        </is>
-      </c>
-      <c r="C315" s="6" t="inlineStr">
-        <is>
-          <t>KH9652</t>
-        </is>
-      </c>
-      <c r="D315" s="7" t="n">
-        <v>1540</v>
-      </c>
-      <c r="E315" s="8" t="n"/>
-      <c r="F315" s="8" t="n"/>
-      <c r="G315" s="8" t="n"/>
-      <c r="H315" s="9" t="n"/>
-      <c r="I315" s="9" t="n"/>
-      <c r="J315" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="315" ht="16" customHeight="1">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>── 10部 ──</t>
         </is>
       </c>
     </row>
     <row r="316" ht="14" customHeight="1">
       <c r="A316" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C316" s="6" t="inlineStr">
         <is>
-          <t>KH9653</t>
+          <t>IG6045</t>
         </is>
       </c>
       <c r="D316" s="7" t="n">
-        <v>1764</v>
+        <v>18755</v>
       </c>
       <c r="E316" s="8" t="n"/>
       <c r="F316" s="8" t="n"/>
@@ -9819,21 +9796,21 @@
     <row r="317" ht="14" customHeight="1">
       <c r="A317" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C317" s="6" t="inlineStr">
         <is>
-          <t>KH9656</t>
+          <t>IG6047</t>
         </is>
       </c>
       <c r="D317" s="7" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="E317" s="8" t="n"/>
       <c r="F317" s="8" t="n"/>
@@ -9849,21 +9826,21 @@
     <row r="318" ht="14" customHeight="1">
       <c r="A318" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZGAIA W</t>
         </is>
       </c>
       <c r="C318" s="6" t="inlineStr">
         <is>
-          <t>KH9657</t>
+          <t>IG6049</t>
         </is>
       </c>
       <c r="D318" s="7" t="n">
-        <v>600</v>
+        <v>2015</v>
       </c>
       <c r="E318" s="8" t="n"/>
       <c r="F318" s="8" t="n"/>
@@ -9879,21 +9856,21 @@
     <row r="319" ht="14" customHeight="1">
       <c r="A319" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZMILLEN</t>
         </is>
       </c>
       <c r="C319" s="6" t="inlineStr">
         <is>
-          <t>KH9658</t>
+          <t>IH0874</t>
         </is>
       </c>
       <c r="D319" s="7" t="n">
-        <v>304</v>
+        <v>600</v>
       </c>
       <c r="E319" s="8" t="n"/>
       <c r="F319" s="8" t="n"/>
@@ -9909,21 +9886,21 @@
     <row r="320" ht="14" customHeight="1">
       <c r="A320" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZMILLEN W</t>
         </is>
       </c>
       <c r="C320" s="6" t="inlineStr">
         <is>
-          <t>KH9671</t>
+          <t>JH5642</t>
         </is>
       </c>
       <c r="D320" s="7" t="n">
-        <v>137</v>
+        <v>580</v>
       </c>
       <c r="E320" s="8" t="n"/>
       <c r="F320" s="8" t="n"/>
@@ -9939,21 +9916,21 @@
     <row r="321" ht="14" customHeight="1">
       <c r="A321" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZMILLEN</t>
         </is>
       </c>
       <c r="C321" s="6" t="inlineStr">
         <is>
-          <t>KH9672</t>
+          <t>JI2632</t>
         </is>
       </c>
       <c r="D321" s="7" t="n">
-        <v>1544</v>
+        <v>500</v>
       </c>
       <c r="E321" s="8" t="n"/>
       <c r="F321" s="8" t="n"/>
@@ -9969,21 +9946,21 @@
     <row r="322" ht="14" customHeight="1">
       <c r="A322" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>OZMILLEN</t>
         </is>
       </c>
       <c r="C322" s="6" t="inlineStr">
         <is>
-          <t>KH9673</t>
+          <t>JI2633</t>
         </is>
       </c>
       <c r="D322" s="7" t="n">
-        <v>4979</v>
+        <v>1200</v>
       </c>
       <c r="E322" s="8" t="n"/>
       <c r="F322" s="8" t="n"/>
@@ -9999,21 +9976,21 @@
     <row r="323" ht="14" customHeight="1">
       <c r="A323" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS J</t>
+          <t>OZMILLEN</t>
         </is>
       </c>
       <c r="C323" s="6" t="inlineStr">
         <is>
-          <t>KJ0690</t>
+          <t>JP7827</t>
         </is>
       </c>
       <c r="D323" s="7" t="n">
-        <v>2704</v>
+        <v>2664</v>
       </c>
       <c r="E323" s="8" t="n"/>
       <c r="F323" s="8" t="n"/>
@@ -10029,21 +10006,21 @@
     <row r="324" ht="14" customHeight="1">
       <c r="A324" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C324" s="6" t="inlineStr">
         <is>
-          <t>KJ1666</t>
+          <t>KJ7852</t>
         </is>
       </c>
       <c r="D324" s="7" t="n">
-        <v>7162</v>
+        <v>1865</v>
       </c>
       <c r="E324" s="8" t="n"/>
       <c r="F324" s="8" t="n"/>
@@ -10059,21 +10036,21 @@
     <row r="325" ht="14" customHeight="1">
       <c r="A325" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C325" s="6" t="inlineStr">
         <is>
-          <t>KJ1667</t>
+          <t>KJ7853</t>
         </is>
       </c>
       <c r="D325" s="7" t="n">
-        <v>3408</v>
+        <v>2705</v>
       </c>
       <c r="E325" s="8" t="n"/>
       <c r="F325" s="8" t="n"/>
@@ -10089,21 +10066,21 @@
     <row r="326" ht="14" customHeight="1">
       <c r="A326" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C326" s="6" t="inlineStr">
         <is>
-          <t>KJ1669</t>
+          <t>KJ7892</t>
         </is>
       </c>
       <c r="D326" s="7" t="n">
-        <v>2064</v>
+        <v>2100</v>
       </c>
       <c r="E326" s="8" t="n"/>
       <c r="F326" s="8" t="n"/>
@@ -10119,21 +10096,21 @@
     <row r="327" ht="14" customHeight="1">
       <c r="A327" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B327" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C327" s="6" t="inlineStr">
         <is>
-          <t>KJ1670</t>
+          <t>KK4234</t>
         </is>
       </c>
       <c r="D327" s="7" t="n">
-        <v>2514</v>
+        <v>2443</v>
       </c>
       <c r="E327" s="8" t="n"/>
       <c r="F327" s="8" t="n"/>
@@ -10149,21 +10126,21 @@
     <row r="328" ht="14" customHeight="1">
       <c r="A328" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C328" s="6" t="inlineStr">
         <is>
-          <t>KJ1672</t>
+          <t>KZ9344</t>
         </is>
       </c>
       <c r="D328" s="7" t="n">
-        <v>5820</v>
+        <v>2796</v>
       </c>
       <c r="E328" s="8" t="n"/>
       <c r="F328" s="8" t="n"/>
@@ -10179,21 +10156,21 @@
     <row r="329" ht="14" customHeight="1">
       <c r="A329" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10A</t>
         </is>
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
+          <t>LA6421</t>
         </is>
       </c>
       <c r="C329" s="6" t="inlineStr">
         <is>
-          <t>KJ1673</t>
+          <t>LA6421</t>
         </is>
       </c>
       <c r="D329" s="7" t="n">
-        <v>2284</v>
+        <v>300</v>
       </c>
       <c r="E329" s="8" t="n"/>
       <c r="F329" s="8" t="n"/>
@@ -10209,21 +10186,21 @@
     <row r="330" ht="14" customHeight="1">
       <c r="A330" s="4" t="inlineStr">
         <is>
-          <t>9C</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>SL 72 OG W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C330" s="6" t="inlineStr">
         <is>
-          <t>KJ2282</t>
+          <t>KH7374</t>
         </is>
       </c>
       <c r="D330" s="7" t="n">
-        <v>2644</v>
+        <v>1602</v>
       </c>
       <c r="E330" s="8" t="n"/>
       <c r="F330" s="8" t="n"/>
@@ -10236,31 +10213,54 @@
         </is>
       </c>
     </row>
-    <row r="331" ht="16" customHeight="1">
-      <c r="A331" s="3" t="inlineStr">
-        <is>
-          <t>── 10部 ──</t>
+    <row r="331" ht="14" customHeight="1">
+      <c r="A331" s="4" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
+      <c r="B331" s="5" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J</t>
+        </is>
+      </c>
+      <c r="C331" s="6" t="inlineStr">
+        <is>
+          <t>KJ7844</t>
+        </is>
+      </c>
+      <c r="D331" s="7" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E331" s="8" t="n"/>
+      <c r="F331" s="8" t="n"/>
+      <c r="G331" s="8" t="n"/>
+      <c r="H331" s="9" t="n"/>
+      <c r="I331" s="9" t="n"/>
+      <c r="J331" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="332" ht="14" customHeight="1">
       <c r="A332" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C332" s="6" t="inlineStr">
         <is>
-          <t>IG6045</t>
+          <t>KJ7845</t>
         </is>
       </c>
       <c r="D332" s="7" t="n">
-        <v>18755</v>
+        <v>1200</v>
       </c>
       <c r="E332" s="8" t="n"/>
       <c r="F332" s="8" t="n"/>
@@ -10276,21 +10276,21 @@
     <row r="333" ht="14" customHeight="1">
       <c r="A333" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C333" s="6" t="inlineStr">
         <is>
-          <t>IG6047</t>
+          <t>KJ7852</t>
         </is>
       </c>
       <c r="D333" s="7" t="n">
-        <v>309</v>
+        <v>3068</v>
       </c>
       <c r="E333" s="8" t="n"/>
       <c r="F333" s="8" t="n"/>
@@ -10306,21 +10306,21 @@
     <row r="334" ht="14" customHeight="1">
       <c r="A334" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
-          <t>OZGAIA W</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C334" s="6" t="inlineStr">
         <is>
-          <t>IG6049</t>
+          <t>KJ7853</t>
         </is>
       </c>
       <c r="D334" s="7" t="n">
-        <v>2015</v>
+        <v>1225</v>
       </c>
       <c r="E334" s="8" t="n"/>
       <c r="F334" s="8" t="n"/>
@@ -10336,21 +10336,21 @@
     <row r="335" ht="14" customHeight="1">
       <c r="A335" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>OZMILLEN</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C335" s="6" t="inlineStr">
         <is>
-          <t>IH0874</t>
+          <t>KJ7892</t>
         </is>
       </c>
       <c r="D335" s="7" t="n">
-        <v>600</v>
+        <v>1320</v>
       </c>
       <c r="E335" s="8" t="n"/>
       <c r="F335" s="8" t="n"/>
@@ -10366,21 +10366,21 @@
     <row r="336" ht="14" customHeight="1">
       <c r="A336" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>OZMILLEN W</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C336" s="6" t="inlineStr">
         <is>
-          <t>JH5642</t>
+          <t>KK2904</t>
         </is>
       </c>
       <c r="D336" s="7" t="n">
-        <v>580</v>
+        <v>1862</v>
       </c>
       <c r="E336" s="8" t="n"/>
       <c r="F336" s="8" t="n"/>
@@ -10396,21 +10396,21 @@
     <row r="337" ht="14" customHeight="1">
       <c r="A337" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>OZMILLEN</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C337" s="6" t="inlineStr">
         <is>
-          <t>JI2632</t>
+          <t>KK4234</t>
         </is>
       </c>
       <c r="D337" s="7" t="n">
-        <v>500</v>
+        <v>8123</v>
       </c>
       <c r="E337" s="8" t="n"/>
       <c r="F337" s="8" t="n"/>
@@ -10426,21 +10426,21 @@
     <row r="338" ht="14" customHeight="1">
       <c r="A338" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>OZMILLEN</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C338" s="6" t="inlineStr">
         <is>
-          <t>JI2633</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D338" s="7" t="n">
-        <v>1200</v>
+        <v>662</v>
       </c>
       <c r="E338" s="8" t="n"/>
       <c r="F338" s="8" t="n"/>
@@ -10456,21 +10456,21 @@
     <row r="339" ht="14" customHeight="1">
       <c r="A339" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10B</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>OZMILLEN</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C339" s="6" t="inlineStr">
         <is>
-          <t>JP7827</t>
+          <t>LA0522</t>
         </is>
       </c>
       <c r="D339" s="7" t="n">
-        <v>2664</v>
+        <v>1</v>
       </c>
       <c r="E339" s="8" t="n"/>
       <c r="F339" s="8" t="n"/>
@@ -10486,21 +10486,21 @@
     <row r="340" ht="14" customHeight="1">
       <c r="A340" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C340" s="6" t="inlineStr">
         <is>
-          <t>KJ7852</t>
+          <t>KH6397</t>
         </is>
       </c>
       <c r="D340" s="7" t="n">
-        <v>1865</v>
+        <v>310</v>
       </c>
       <c r="E340" s="8" t="n"/>
       <c r="F340" s="8" t="n"/>
@@ -10516,21 +10516,21 @@
     <row r="341" ht="14" customHeight="1">
       <c r="A341" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C341" s="6" t="inlineStr">
         <is>
-          <t>KJ7853</t>
+          <t>KI5241</t>
         </is>
       </c>
       <c r="D341" s="7" t="n">
-        <v>2705</v>
+        <v>310</v>
       </c>
       <c r="E341" s="8" t="n"/>
       <c r="F341" s="8" t="n"/>
@@ -10546,21 +10546,21 @@
     <row r="342" ht="14" customHeight="1">
       <c r="A342" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>SPEZIAL GOLF</t>
         </is>
       </c>
       <c r="C342" s="6" t="inlineStr">
         <is>
-          <t>KJ7892</t>
+          <t>KJ0849</t>
         </is>
       </c>
       <c r="D342" s="7" t="n">
-        <v>2100</v>
+        <v>3060</v>
       </c>
       <c r="E342" s="8" t="n"/>
       <c r="F342" s="8" t="n"/>
@@ -10576,21 +10576,21 @@
     <row r="343" ht="14" customHeight="1">
       <c r="A343" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>SPEZIAL GOLF</t>
         </is>
       </c>
       <c r="C343" s="6" t="inlineStr">
         <is>
-          <t>KK4234</t>
+          <t>KJ0850</t>
         </is>
       </c>
       <c r="D343" s="7" t="n">
-        <v>2443</v>
+        <v>2262</v>
       </c>
       <c r="E343" s="8" t="n"/>
       <c r="F343" s="8" t="n"/>
@@ -10606,21 +10606,21 @@
     <row r="344" ht="14" customHeight="1">
       <c r="A344" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>SPEZIAL GOLF</t>
         </is>
       </c>
       <c r="C344" s="6" t="inlineStr">
         <is>
-          <t>KZ9344</t>
+          <t>KJ0851</t>
         </is>
       </c>
       <c r="D344" s="7" t="n">
-        <v>2796</v>
+        <v>1770</v>
       </c>
       <c r="E344" s="8" t="n"/>
       <c r="F344" s="8" t="n"/>
@@ -10636,21 +10636,21 @@
     <row r="345" ht="14" customHeight="1">
       <c r="A345" s="4" t="inlineStr">
         <is>
-          <t>10A</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>LA6421</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C345" s="6" t="inlineStr">
         <is>
-          <t>LA6421</t>
+          <t>KK3015</t>
         </is>
       </c>
       <c r="D345" s="7" t="n">
-        <v>300</v>
+        <v>1030</v>
       </c>
       <c r="E345" s="8" t="n"/>
       <c r="F345" s="8" t="n"/>
@@ -10666,21 +10666,21 @@
     <row r="346" ht="14" customHeight="1">
       <c r="A346" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C346" s="6" t="inlineStr">
         <is>
-          <t>KH7374</t>
+          <t>KK3018</t>
         </is>
       </c>
       <c r="D346" s="7" t="n">
-        <v>1602</v>
+        <v>310</v>
       </c>
       <c r="E346" s="8" t="n"/>
       <c r="F346" s="8" t="n"/>
@@ -10696,21 +10696,21 @@
     <row r="347" ht="14" customHeight="1">
       <c r="A347" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C347" s="6" t="inlineStr">
         <is>
-          <t>KJ7844</t>
+          <t>KK3019</t>
         </is>
       </c>
       <c r="D347" s="7" t="n">
-        <v>1050</v>
+        <v>2774</v>
       </c>
       <c r="E347" s="8" t="n"/>
       <c r="F347" s="8" t="n"/>
@@ -10726,21 +10726,21 @@
     <row r="348" ht="14" customHeight="1">
       <c r="A348" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C348" s="6" t="inlineStr">
         <is>
-          <t>KJ7845</t>
+          <t>KK3025</t>
         </is>
       </c>
       <c r="D348" s="7" t="n">
-        <v>1200</v>
+        <v>994</v>
       </c>
       <c r="E348" s="8" t="n"/>
       <c r="F348" s="8" t="n"/>
@@ -10756,21 +10756,21 @@
     <row r="349" ht="14" customHeight="1">
       <c r="A349" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C349" s="6" t="inlineStr">
         <is>
-          <t>KJ7852</t>
+          <t>KK3026</t>
         </is>
       </c>
       <c r="D349" s="7" t="n">
-        <v>3068</v>
+        <v>432</v>
       </c>
       <c r="E349" s="8" t="n"/>
       <c r="F349" s="8" t="n"/>
@@ -10786,21 +10786,21 @@
     <row r="350" ht="14" customHeight="1">
       <c r="A350" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C350" s="6" t="inlineStr">
         <is>
-          <t>KJ7853</t>
+          <t>KK3027</t>
         </is>
       </c>
       <c r="D350" s="7" t="n">
-        <v>1225</v>
+        <v>432</v>
       </c>
       <c r="E350" s="8" t="n"/>
       <c r="F350" s="8" t="n"/>
@@ -10816,21 +10816,21 @@
     <row r="351" ht="14" customHeight="1">
       <c r="A351" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>10C</t>
         </is>
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="C351" s="6" t="inlineStr">
         <is>
-          <t>KJ7892</t>
+          <t>LA3255</t>
         </is>
       </c>
       <c r="D351" s="7" t="n">
-        <v>1320</v>
+        <v>1100</v>
       </c>
       <c r="E351" s="8" t="n"/>
       <c r="F351" s="8" t="n"/>
@@ -10843,54 +10843,31 @@
         </is>
       </c>
     </row>
-    <row r="352" ht="14" customHeight="1">
-      <c r="A352" s="4" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B352" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="C352" s="6" t="inlineStr">
-        <is>
-          <t>KK2904</t>
-        </is>
-      </c>
-      <c r="D352" s="7" t="n">
-        <v>1862</v>
-      </c>
-      <c r="E352" s="8" t="n"/>
-      <c r="F352" s="8" t="n"/>
-      <c r="G352" s="8" t="n"/>
-      <c r="H352" s="9" t="n"/>
-      <c r="I352" s="9" t="n"/>
-      <c r="J352" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="352" ht="16" customHeight="1">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>── 11部 ──</t>
         </is>
       </c>
     </row>
     <row r="353" ht="14" customHeight="1">
       <c r="A353" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C353" s="6" t="inlineStr">
         <is>
-          <t>KK4234</t>
+          <t>HP7087</t>
         </is>
       </c>
       <c r="D353" s="7" t="n">
-        <v>8123</v>
+        <v>888</v>
       </c>
       <c r="E353" s="8" t="n"/>
       <c r="F353" s="8" t="n"/>
@@ -10906,21 +10883,21 @@
     <row r="354" ht="14" customHeight="1">
       <c r="A354" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>S2G 26 TEX</t>
         </is>
       </c>
       <c r="C354" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>HP7088</t>
         </is>
       </c>
       <c r="D354" s="7" t="n">
-        <v>662</v>
+        <v>77</v>
       </c>
       <c r="E354" s="8" t="n"/>
       <c r="F354" s="8" t="n"/>
@@ -10936,21 +10913,21 @@
     <row r="355" ht="14" customHeight="1">
       <c r="A355" s="4" t="inlineStr">
         <is>
-          <t>10B</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B355" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C355" s="6" t="inlineStr">
         <is>
-          <t>LA0522</t>
+          <t>HQ5054</t>
         </is>
       </c>
       <c r="D355" s="7" t="n">
-        <v>1</v>
+        <v>1178</v>
       </c>
       <c r="E355" s="8" t="n"/>
       <c r="F355" s="8" t="n"/>
@@ -10966,21 +10943,21 @@
     <row r="356" ht="14" customHeight="1">
       <c r="A356" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B356" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>W ADIPOWER 26 SL BOA</t>
         </is>
       </c>
       <c r="C356" s="6" t="inlineStr">
         <is>
-          <t>KH6397</t>
+          <t>JP8385</t>
         </is>
       </c>
       <c r="D356" s="7" t="n">
-        <v>310</v>
+        <v>349</v>
       </c>
       <c r="E356" s="8" t="n"/>
       <c r="F356" s="8" t="n"/>
@@ -10996,21 +10973,21 @@
     <row r="357" ht="14" customHeight="1">
       <c r="A357" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26 SL</t>
         </is>
       </c>
       <c r="C357" s="6" t="inlineStr">
         <is>
-          <t>KI5241</t>
+          <t>JP8394</t>
         </is>
       </c>
       <c r="D357" s="7" t="n">
-        <v>3876</v>
+        <v>248</v>
       </c>
       <c r="E357" s="8" t="n"/>
       <c r="F357" s="8" t="n"/>
@@ -11026,21 +11003,21 @@
     <row r="358" ht="14" customHeight="1">
       <c r="A358" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26 SL</t>
         </is>
       </c>
       <c r="C358" s="6" t="inlineStr">
         <is>
-          <t>KI5303</t>
+          <t>JP8395</t>
         </is>
       </c>
       <c r="D358" s="7" t="n">
-        <v>747</v>
+        <v>79</v>
       </c>
       <c r="E358" s="8" t="n"/>
       <c r="F358" s="8" t="n"/>
@@ -11056,21 +11033,21 @@
     <row r="359" ht="14" customHeight="1">
       <c r="A359" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>W S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C359" s="6" t="inlineStr">
         <is>
-          <t>KJ0849</t>
+          <t>JQ3560</t>
         </is>
       </c>
       <c r="D359" s="7" t="n">
-        <v>4525</v>
+        <v>1203</v>
       </c>
       <c r="E359" s="8" t="n"/>
       <c r="F359" s="8" t="n"/>
@@ -11086,21 +11063,21 @@
     <row r="360" ht="14" customHeight="1">
       <c r="A360" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B360" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>W S2G 26 TEX</t>
         </is>
       </c>
       <c r="C360" s="6" t="inlineStr">
         <is>
-          <t>KJ0850</t>
+          <t>JQ3563</t>
         </is>
       </c>
       <c r="D360" s="7" t="n">
-        <v>7284</v>
+        <v>60</v>
       </c>
       <c r="E360" s="8" t="n"/>
       <c r="F360" s="8" t="n"/>
@@ -11116,21 +11093,21 @@
     <row r="361" ht="14" customHeight="1">
       <c r="A361" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C361" s="6" t="inlineStr">
         <is>
-          <t>KJ0851</t>
+          <t>JQ9311</t>
         </is>
       </c>
       <c r="D361" s="7" t="n">
-        <v>2913</v>
+        <v>452</v>
       </c>
       <c r="E361" s="8" t="n"/>
       <c r="F361" s="8" t="n"/>
@@ -11146,21 +11123,21 @@
     <row r="362" ht="14" customHeight="1">
       <c r="A362" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>S2G 26 TEX</t>
         </is>
       </c>
       <c r="C362" s="6" t="inlineStr">
         <is>
-          <t>KJ0852</t>
+          <t>JR1879</t>
         </is>
       </c>
       <c r="D362" s="7" t="n">
-        <v>3307</v>
+        <v>189</v>
       </c>
       <c r="E362" s="8" t="n"/>
       <c r="F362" s="8" t="n"/>
@@ -11176,21 +11153,21 @@
     <row r="363" ht="14" customHeight="1">
       <c r="A363" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B363" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26 SL BOA</t>
         </is>
       </c>
       <c r="C363" s="6" t="inlineStr">
         <is>
-          <t>KK3015</t>
+          <t>JS4138</t>
         </is>
       </c>
       <c r="D363" s="7" t="n">
-        <v>1612</v>
+        <v>377</v>
       </c>
       <c r="E363" s="8" t="n"/>
       <c r="F363" s="8" t="n"/>
@@ -11206,21 +11183,21 @@
     <row r="364" ht="14" customHeight="1">
       <c r="A364" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B364" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26 SL BOA</t>
         </is>
       </c>
       <c r="C364" s="6" t="inlineStr">
         <is>
-          <t>KK3017</t>
+          <t>JS4140</t>
         </is>
       </c>
       <c r="D364" s="7" t="n">
-        <v>100</v>
+        <v>221</v>
       </c>
       <c r="E364" s="8" t="n"/>
       <c r="F364" s="8" t="n"/>
@@ -11236,21 +11213,21 @@
     <row r="365" ht="14" customHeight="1">
       <c r="A365" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B365" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>S2G VENT</t>
         </is>
       </c>
       <c r="C365" s="6" t="inlineStr">
         <is>
-          <t>KK3018</t>
+          <t>KI1392</t>
         </is>
       </c>
       <c r="D365" s="7" t="n">
-        <v>310</v>
+        <v>1107</v>
       </c>
       <c r="E365" s="8" t="n"/>
       <c r="F365" s="8" t="n"/>
@@ -11266,21 +11243,21 @@
     <row r="366" ht="14" customHeight="1">
       <c r="A366" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B366" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>S2G VENT</t>
         </is>
       </c>
       <c r="C366" s="6" t="inlineStr">
         <is>
-          <t>KK3019</t>
+          <t>KI8398</t>
         </is>
       </c>
       <c r="D366" s="7" t="n">
-        <v>2774</v>
+        <v>1203</v>
       </c>
       <c r="E366" s="8" t="n"/>
       <c r="F366" s="8" t="n"/>
@@ -11296,21 +11273,21 @@
     <row r="367" ht="14" customHeight="1">
       <c r="A367" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B367" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>W S2G VENT</t>
         </is>
       </c>
       <c r="C367" s="6" t="inlineStr">
         <is>
-          <t>KK3021</t>
+          <t>KI8401</t>
         </is>
       </c>
       <c r="D367" s="7" t="n">
-        <v>1189</v>
+        <v>1200</v>
       </c>
       <c r="E367" s="8" t="n"/>
       <c r="F367" s="8" t="n"/>
@@ -11326,21 +11303,21 @@
     <row r="368" ht="14" customHeight="1">
       <c r="A368" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B368" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>W S2G VENT</t>
         </is>
       </c>
       <c r="C368" s="6" t="inlineStr">
         <is>
-          <t>KK3025</t>
+          <t>KI8402</t>
         </is>
       </c>
       <c r="D368" s="7" t="n">
-        <v>994</v>
+        <v>2584</v>
       </c>
       <c r="E368" s="8" t="n"/>
       <c r="F368" s="8" t="n"/>
@@ -11356,21 +11333,21 @@
     <row r="369" ht="14" customHeight="1">
       <c r="A369" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B369" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26</t>
         </is>
       </c>
       <c r="C369" s="6" t="inlineStr">
         <is>
-          <t>KK3026</t>
+          <t>KJ3010</t>
         </is>
       </c>
       <c r="D369" s="7" t="n">
-        <v>432</v>
+        <v>1205</v>
       </c>
       <c r="E369" s="8" t="n"/>
       <c r="F369" s="8" t="n"/>
@@ -11386,21 +11363,21 @@
     <row r="370" ht="14" customHeight="1">
       <c r="A370" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B370" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>S2G 26 TEX</t>
         </is>
       </c>
       <c r="C370" s="6" t="inlineStr">
         <is>
-          <t>KK3027</t>
+          <t>KK0666</t>
         </is>
       </c>
       <c r="D370" s="7" t="n">
-        <v>432</v>
+        <v>127</v>
       </c>
       <c r="E370" s="8" t="n"/>
       <c r="F370" s="8" t="n"/>
@@ -11416,21 +11393,21 @@
     <row r="371" ht="14" customHeight="1">
       <c r="A371" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B371" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26</t>
         </is>
       </c>
       <c r="C371" s="6" t="inlineStr">
         <is>
-          <t>KK3033</t>
+          <t>KK2836</t>
         </is>
       </c>
       <c r="D371" s="7" t="n">
-        <v>384</v>
+        <v>275</v>
       </c>
       <c r="E371" s="8" t="n"/>
       <c r="F371" s="8" t="n"/>
@@ -11446,21 +11423,21 @@
     <row r="372" ht="14" customHeight="1">
       <c r="A372" s="4" t="inlineStr">
         <is>
-          <t>10C</t>
+          <t>11A1</t>
         </is>
       </c>
       <c r="B372" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADIPOWER 26 SL</t>
         </is>
       </c>
       <c r="C372" s="6" t="inlineStr">
         <is>
-          <t>LA3255</t>
+          <t>KK2838</t>
         </is>
       </c>
       <c r="D372" s="7" t="n">
-        <v>1100</v>
+        <v>379</v>
       </c>
       <c r="E372" s="8" t="n"/>
       <c r="F372" s="8" t="n"/>
@@ -11473,10 +11450,33 @@
         </is>
       </c>
     </row>
-    <row r="373" ht="16" customHeight="1">
-      <c r="A373" s="3" t="inlineStr">
-        <is>
-          <t>── 11部 ──</t>
+    <row r="373" ht="14" customHeight="1">
+      <c r="A373" s="4" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
+      <c r="B373" s="5" t="inlineStr">
+        <is>
+          <t>ADIPOWER 26 SL BOA</t>
+        </is>
+      </c>
+      <c r="C373" s="6" t="inlineStr">
+        <is>
+          <t>KK2839</t>
+        </is>
+      </c>
+      <c r="D373" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="E373" s="8" t="n"/>
+      <c r="F373" s="8" t="n"/>
+      <c r="G373" s="8" t="n"/>
+      <c r="H373" s="9" t="n"/>
+      <c r="I373" s="9" t="n"/>
+      <c r="J373" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -11488,16 +11488,16 @@
       </c>
       <c r="B374" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>W ADIPOWER 26 SL BOA</t>
         </is>
       </c>
       <c r="C374" s="6" t="inlineStr">
         <is>
-          <t>HP7087</t>
+          <t>KK2843</t>
         </is>
       </c>
       <c r="D374" s="7" t="n">
-        <v>888</v>
+        <v>346</v>
       </c>
       <c r="E374" s="8" t="n"/>
       <c r="F374" s="8" t="n"/>
@@ -11518,16 +11518,16 @@
       </c>
       <c r="B375" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 TEX</t>
+          <t>W S2G 26 TEX</t>
         </is>
       </c>
       <c r="C375" s="6" t="inlineStr">
         <is>
-          <t>HP7088</t>
+          <t>KK2862</t>
         </is>
       </c>
       <c r="D375" s="7" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="E375" s="8" t="n"/>
       <c r="F375" s="8" t="n"/>
@@ -11548,16 +11548,16 @@
       </c>
       <c r="B376" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>S2G 26 TEX</t>
         </is>
       </c>
       <c r="C376" s="6" t="inlineStr">
         <is>
-          <t>HQ5054</t>
+          <t>KK2872</t>
         </is>
       </c>
       <c r="D376" s="7" t="n">
-        <v>1178</v>
+        <v>249</v>
       </c>
       <c r="E376" s="8" t="n"/>
       <c r="F376" s="8" t="n"/>
@@ -11573,21 +11573,21 @@
     <row r="377" ht="14" customHeight="1">
       <c r="A377" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B377" s="5" t="inlineStr">
         <is>
-          <t>W ADIPOWER 26 SL BOA</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C377" s="6" t="inlineStr">
         <is>
-          <t>JP8385</t>
+          <t>KK0036</t>
         </is>
       </c>
       <c r="D377" s="7" t="n">
-        <v>349</v>
+        <v>3490</v>
       </c>
       <c r="E377" s="8" t="n"/>
       <c r="F377" s="8" t="n"/>
@@ -11603,21 +11603,21 @@
     <row r="378" ht="14" customHeight="1">
       <c r="A378" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B378" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C378" s="6" t="inlineStr">
         <is>
-          <t>JP8394</t>
+          <t>KK0037</t>
         </is>
       </c>
       <c r="D378" s="7" t="n">
-        <v>248</v>
+        <v>1145</v>
       </c>
       <c r="E378" s="8" t="n"/>
       <c r="F378" s="8" t="n"/>
@@ -11633,21 +11633,21 @@
     <row r="379" ht="14" customHeight="1">
       <c r="A379" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B379" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C379" s="6" t="inlineStr">
         <is>
-          <t>JP8395</t>
+          <t>KK2523</t>
         </is>
       </c>
       <c r="D379" s="7" t="n">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="E379" s="8" t="n"/>
       <c r="F379" s="8" t="n"/>
@@ -11663,21 +11663,21 @@
     <row r="380" ht="14" customHeight="1">
       <c r="A380" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B380" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C380" s="6" t="inlineStr">
         <is>
-          <t>JQ3560</t>
+          <t>KK2524</t>
         </is>
       </c>
       <c r="D380" s="7" t="n">
-        <v>1203</v>
+        <v>100</v>
       </c>
       <c r="E380" s="8" t="n"/>
       <c r="F380" s="8" t="n"/>
@@ -11693,21 +11693,21 @@
     <row r="381" ht="14" customHeight="1">
       <c r="A381" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B381" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 TEX</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C381" s="6" t="inlineStr">
         <is>
-          <t>JQ3563</t>
+          <t>KK2572</t>
         </is>
       </c>
       <c r="D381" s="7" t="n">
-        <v>60</v>
+        <v>1597</v>
       </c>
       <c r="E381" s="8" t="n"/>
       <c r="F381" s="8" t="n"/>
@@ -11723,21 +11723,21 @@
     <row r="382" ht="14" customHeight="1">
       <c r="A382" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B382" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C382" s="6" t="inlineStr">
         <is>
-          <t>JQ9311</t>
+          <t>KK2573</t>
         </is>
       </c>
       <c r="D382" s="7" t="n">
-        <v>452</v>
+        <v>1267</v>
       </c>
       <c r="E382" s="8" t="n"/>
       <c r="F382" s="8" t="n"/>
@@ -11753,21 +11753,21 @@
     <row r="383" ht="14" customHeight="1">
       <c r="A383" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B383" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 TEX</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C383" s="6" t="inlineStr">
         <is>
-          <t>JR1879</t>
+          <t>KK2575</t>
         </is>
       </c>
       <c r="D383" s="7" t="n">
-        <v>189</v>
+        <v>3355</v>
       </c>
       <c r="E383" s="8" t="n"/>
       <c r="F383" s="8" t="n"/>
@@ -11783,21 +11783,21 @@
     <row r="384" ht="14" customHeight="1">
       <c r="A384" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B384" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA</t>
+          <t>TAEKWONDO MEI ELITE W</t>
         </is>
       </c>
       <c r="C384" s="6" t="inlineStr">
         <is>
-          <t>JS4138</t>
+          <t>KK2576</t>
         </is>
       </c>
       <c r="D384" s="7" t="n">
-        <v>377</v>
+        <v>1632</v>
       </c>
       <c r="E384" s="8" t="n"/>
       <c r="F384" s="8" t="n"/>
@@ -11813,21 +11813,21 @@
     <row r="385" ht="14" customHeight="1">
       <c r="A385" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11A2</t>
         </is>
       </c>
       <c r="B385" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA</t>
+          <t>adidas TAEKWONDO W</t>
         </is>
       </c>
       <c r="C385" s="6" t="inlineStr">
         <is>
-          <t>JS4140</t>
+          <t>KK2705</t>
         </is>
       </c>
       <c r="D385" s="7" t="n">
-        <v>221</v>
+        <v>2251</v>
       </c>
       <c r="E385" s="8" t="n"/>
       <c r="F385" s="8" t="n"/>
@@ -11843,21 +11843,21 @@
     <row r="386" ht="14" customHeight="1">
       <c r="A386" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B386" s="5" t="inlineStr">
         <is>
-          <t>S2G VENT</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C386" s="6" t="inlineStr">
         <is>
-          <t>KI1392</t>
+          <t>HQ5054</t>
         </is>
       </c>
       <c r="D386" s="7" t="n">
-        <v>1107</v>
+        <v>2563</v>
       </c>
       <c r="E386" s="8" t="n"/>
       <c r="F386" s="8" t="n"/>
@@ -11873,21 +11873,21 @@
     <row r="387" ht="14" customHeight="1">
       <c r="A387" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B387" s="5" t="inlineStr">
         <is>
-          <t>S2G VENT</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C387" s="6" t="inlineStr">
         <is>
-          <t>KI8398</t>
+          <t>JQ9311</t>
         </is>
       </c>
       <c r="D387" s="7" t="n">
-        <v>1203</v>
+        <v>1722</v>
       </c>
       <c r="E387" s="8" t="n"/>
       <c r="F387" s="8" t="n"/>
@@ -11903,21 +11903,21 @@
     <row r="388" ht="14" customHeight="1">
       <c r="A388" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B388" s="5" t="inlineStr">
         <is>
-          <t>W S2G VENT</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C388" s="6" t="inlineStr">
         <is>
-          <t>KI8401</t>
+          <t>KI3584</t>
         </is>
       </c>
       <c r="D388" s="7" t="n">
-        <v>1200</v>
+        <v>1274</v>
       </c>
       <c r="E388" s="8" t="n"/>
       <c r="F388" s="8" t="n"/>
@@ -11933,21 +11933,21 @@
     <row r="389" ht="14" customHeight="1">
       <c r="A389" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B389" s="5" t="inlineStr">
         <is>
-          <t>W S2G VENT</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C389" s="6" t="inlineStr">
         <is>
-          <t>KI8402</t>
+          <t>KJ7511</t>
         </is>
       </c>
       <c r="D389" s="7" t="n">
-        <v>2584</v>
+        <v>1269</v>
       </c>
       <c r="E389" s="8" t="n"/>
       <c r="F389" s="8" t="n"/>
@@ -11963,21 +11963,21 @@
     <row r="390" ht="14" customHeight="1">
       <c r="A390" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B390" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C390" s="6" t="inlineStr">
         <is>
-          <t>KJ3010</t>
+          <t>KJ7543</t>
         </is>
       </c>
       <c r="D390" s="7" t="n">
-        <v>1205</v>
+        <v>563</v>
       </c>
       <c r="E390" s="8" t="n"/>
       <c r="F390" s="8" t="n"/>
@@ -11993,21 +11993,21 @@
     <row r="391" ht="14" customHeight="1">
       <c r="A391" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B391" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 TEX</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C391" s="6" t="inlineStr">
         <is>
-          <t>KK0666</t>
+          <t>KJ7551</t>
         </is>
       </c>
       <c r="D391" s="7" t="n">
-        <v>127</v>
+        <v>1008</v>
       </c>
       <c r="E391" s="8" t="n"/>
       <c r="F391" s="8" t="n"/>
@@ -12023,21 +12023,21 @@
     <row r="392" ht="14" customHeight="1">
       <c r="A392" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B392" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C392" s="6" t="inlineStr">
         <is>
-          <t>KK2836</t>
+          <t>KJ7552</t>
         </is>
       </c>
       <c r="D392" s="7" t="n">
-        <v>275</v>
+        <v>975</v>
       </c>
       <c r="E392" s="8" t="n"/>
       <c r="F392" s="8" t="n"/>
@@ -12053,21 +12053,21 @@
     <row r="393" ht="14" customHeight="1">
       <c r="A393" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B393" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C393" s="6" t="inlineStr">
         <is>
-          <t>KK2838</t>
+          <t>KK0030</t>
         </is>
       </c>
       <c r="D393" s="7" t="n">
-        <v>379</v>
+        <v>493</v>
       </c>
       <c r="E393" s="8" t="n"/>
       <c r="F393" s="8" t="n"/>
@@ -12083,21 +12083,21 @@
     <row r="394" ht="14" customHeight="1">
       <c r="A394" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B394" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C394" s="6" t="inlineStr">
         <is>
-          <t>KK2839</t>
+          <t>KK0031</t>
         </is>
       </c>
       <c r="D394" s="7" t="n">
-        <v>483</v>
+        <v>694</v>
       </c>
       <c r="E394" s="8" t="n"/>
       <c r="F394" s="8" t="n"/>
@@ -12113,21 +12113,21 @@
     <row r="395" ht="14" customHeight="1">
       <c r="A395" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B395" s="5" t="inlineStr">
         <is>
-          <t>W ADIPOWER 26 SL BOA</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C395" s="6" t="inlineStr">
         <is>
-          <t>KK2843</t>
+          <t>KK0036</t>
         </is>
       </c>
       <c r="D395" s="7" t="n">
-        <v>346</v>
+        <v>472</v>
       </c>
       <c r="E395" s="8" t="n"/>
       <c r="F395" s="8" t="n"/>
@@ -12143,21 +12143,21 @@
     <row r="396" ht="14" customHeight="1">
       <c r="A396" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B396" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 TEX</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C396" s="6" t="inlineStr">
         <is>
-          <t>KK2862</t>
+          <t>KK0037</t>
         </is>
       </c>
       <c r="D396" s="7" t="n">
-        <v>62</v>
+        <v>2450</v>
       </c>
       <c r="E396" s="8" t="n"/>
       <c r="F396" s="8" t="n"/>
@@ -12173,21 +12173,21 @@
     <row r="397" ht="14" customHeight="1">
       <c r="A397" s="4" t="inlineStr">
         <is>
-          <t>11A1</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B397" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 TEX</t>
+          <t>W S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C397" s="6" t="inlineStr">
         <is>
-          <t>KK2872</t>
+          <t>KK2864</t>
         </is>
       </c>
       <c r="D397" s="7" t="n">
-        <v>249</v>
+        <v>548</v>
       </c>
       <c r="E397" s="8" t="n"/>
       <c r="F397" s="8" t="n"/>
@@ -12203,21 +12203,21 @@
     <row r="398" ht="14" customHeight="1">
       <c r="A398" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B398" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>W S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C398" s="6" t="inlineStr">
         <is>
-          <t>KK0036</t>
+          <t>KK2865</t>
         </is>
       </c>
       <c r="D398" s="7" t="n">
-        <v>3490</v>
+        <v>395</v>
       </c>
       <c r="E398" s="8" t="n"/>
       <c r="F398" s="8" t="n"/>
@@ -12233,21 +12233,21 @@
     <row r="399" ht="14" customHeight="1">
       <c r="A399" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B399" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="C399" s="6" t="inlineStr">
         <is>
-          <t>KK0037</t>
+          <t>KK2871</t>
         </is>
       </c>
       <c r="D399" s="7" t="n">
-        <v>1145</v>
+        <v>442</v>
       </c>
       <c r="E399" s="8" t="n"/>
       <c r="F399" s="8" t="n"/>
@@ -12263,21 +12263,21 @@
     <row r="400" ht="14" customHeight="1">
       <c r="A400" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B400" s="5" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C400" s="6" t="inlineStr">
         <is>
-          <t>KK2523</t>
+          <t>LA3432</t>
         </is>
       </c>
       <c r="D400" s="7" t="n">
-        <v>310</v>
+        <v>664</v>
       </c>
       <c r="E400" s="8" t="n"/>
       <c r="F400" s="8" t="n"/>
@@ -12293,21 +12293,21 @@
     <row r="401" ht="14" customHeight="1">
       <c r="A401" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B1</t>
         </is>
       </c>
       <c r="B401" s="5" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C401" s="6" t="inlineStr">
         <is>
-          <t>KK2524</t>
+          <t>LA3433</t>
         </is>
       </c>
       <c r="D401" s="7" t="n">
-        <v>100</v>
+        <v>5111</v>
       </c>
       <c r="E401" s="8" t="n"/>
       <c r="F401" s="8" t="n"/>
@@ -12320,54 +12320,31 @@
         </is>
       </c>
     </row>
-    <row r="402" ht="14" customHeight="1">
-      <c r="A402" s="4" t="inlineStr">
-        <is>
-          <t>11A2</t>
-        </is>
-      </c>
-      <c r="B402" s="5" t="inlineStr">
-        <is>
-          <t>TAEKWONDO MEI ELITE W</t>
-        </is>
-      </c>
-      <c r="C402" s="6" t="inlineStr">
-        <is>
-          <t>KK2572</t>
-        </is>
-      </c>
-      <c r="D402" s="7" t="n">
-        <v>1597</v>
-      </c>
-      <c r="E402" s="8" t="n"/>
-      <c r="F402" s="8" t="n"/>
-      <c r="G402" s="8" t="n"/>
-      <c r="H402" s="9" t="n"/>
-      <c r="I402" s="9" t="n"/>
-      <c r="J402" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="402" ht="16" customHeight="1">
+      <c r="A402" s="3" t="inlineStr">
+        <is>
+          <t>── 11部 (2) ──</t>
         </is>
       </c>
     </row>
     <row r="403" ht="14" customHeight="1">
       <c r="A403" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B403" s="5" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W</t>
+          <t>SAMBA J</t>
         </is>
       </c>
       <c r="C403" s="6" t="inlineStr">
         <is>
-          <t>KK2573</t>
+          <t>IF1944</t>
         </is>
       </c>
       <c r="D403" s="7" t="n">
-        <v>1267</v>
+        <v>3405</v>
       </c>
       <c r="E403" s="8" t="n"/>
       <c r="F403" s="8" t="n"/>
@@ -12383,21 +12360,21 @@
     <row r="404" ht="14" customHeight="1">
       <c r="A404" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B404" s="5" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W</t>
+          <t>SAMBA J</t>
         </is>
       </c>
       <c r="C404" s="6" t="inlineStr">
         <is>
-          <t>KK2575</t>
+          <t>IF1945</t>
         </is>
       </c>
       <c r="D404" s="7" t="n">
-        <v>3355</v>
+        <v>2673</v>
       </c>
       <c r="E404" s="8" t="n"/>
       <c r="F404" s="8" t="n"/>
@@ -12413,21 +12390,21 @@
     <row r="405" ht="14" customHeight="1">
       <c r="A405" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B405" s="5" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W</t>
+          <t>S2G 26 BOA</t>
         </is>
       </c>
       <c r="C405" s="6" t="inlineStr">
         <is>
-          <t>KK2576</t>
+          <t>JQ3463</t>
         </is>
       </c>
       <c r="D405" s="7" t="n">
-        <v>1632</v>
+        <v>3274</v>
       </c>
       <c r="E405" s="8" t="n"/>
       <c r="F405" s="8" t="n"/>
@@ -12443,21 +12420,21 @@
     <row r="406" ht="14" customHeight="1">
       <c r="A406" s="4" t="inlineStr">
         <is>
-          <t>11A2</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B406" s="5" t="inlineStr">
         <is>
-          <t>adidas TAEKWONDO W</t>
+          <t>W S2G 26 BOA</t>
         </is>
       </c>
       <c r="C406" s="6" t="inlineStr">
         <is>
-          <t>KK2705</t>
+          <t>KK2866</t>
         </is>
       </c>
       <c r="D406" s="7" t="n">
-        <v>2251</v>
+        <v>1084</v>
       </c>
       <c r="E406" s="8" t="n"/>
       <c r="F406" s="8" t="n"/>
@@ -12473,21 +12450,21 @@
     <row r="407" ht="14" customHeight="1">
       <c r="A407" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B407" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>W S2G 26 BOA</t>
         </is>
       </c>
       <c r="C407" s="6" t="inlineStr">
         <is>
-          <t>HQ5054</t>
+          <t>KK2867</t>
         </is>
       </c>
       <c r="D407" s="7" t="n">
-        <v>2563</v>
+        <v>62</v>
       </c>
       <c r="E407" s="8" t="n"/>
       <c r="F407" s="8" t="n"/>
@@ -12503,21 +12480,21 @@
     <row r="408" ht="14" customHeight="1">
       <c r="A408" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B408" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>S2G 26 BOA</t>
         </is>
       </c>
       <c r="C408" s="6" t="inlineStr">
         <is>
-          <t>JQ9311</t>
+          <t>KK2868</t>
         </is>
       </c>
       <c r="D408" s="7" t="n">
-        <v>1722</v>
+        <v>1989</v>
       </c>
       <c r="E408" s="8" t="n"/>
       <c r="F408" s="8" t="n"/>
@@ -12533,21 +12510,21 @@
     <row r="409" ht="14" customHeight="1">
       <c r="A409" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B409" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>S2G 26 BOA</t>
         </is>
       </c>
       <c r="C409" s="6" t="inlineStr">
         <is>
-          <t>KI3584</t>
+          <t>KK2869</t>
         </is>
       </c>
       <c r="D409" s="7" t="n">
-        <v>1274</v>
+        <v>32</v>
       </c>
       <c r="E409" s="8" t="n"/>
       <c r="F409" s="8" t="n"/>
@@ -12563,21 +12540,21 @@
     <row r="410" ht="14" customHeight="1">
       <c r="A410" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11B2</t>
         </is>
       </c>
       <c r="B410" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C410" s="6" t="inlineStr">
         <is>
-          <t>KJ7511</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D410" s="7" t="n">
-        <v>1269</v>
+        <v>4929</v>
       </c>
       <c r="E410" s="8" t="n"/>
       <c r="F410" s="8" t="n"/>
@@ -12593,21 +12570,21 @@
     <row r="411" ht="14" customHeight="1">
       <c r="A411" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B411" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="C411" s="6" t="inlineStr">
         <is>
-          <t>KJ7543</t>
+          <t>JR4790</t>
         </is>
       </c>
       <c r="D411" s="7" t="n">
-        <v>563</v>
+        <v>4659</v>
       </c>
       <c r="E411" s="8" t="n"/>
       <c r="F411" s="8" t="n"/>
@@ -12623,21 +12600,21 @@
     <row r="412" ht="14" customHeight="1">
       <c r="A412" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B412" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C412" s="6" t="inlineStr">
         <is>
-          <t>KJ7551</t>
+          <t>KZ6449</t>
         </is>
       </c>
       <c r="D412" s="7" t="n">
-        <v>1008</v>
+        <v>1670</v>
       </c>
       <c r="E412" s="8" t="n"/>
       <c r="F412" s="8" t="n"/>
@@ -12653,21 +12630,21 @@
     <row r="413" ht="14" customHeight="1">
       <c r="A413" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B413" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C413" s="6" t="inlineStr">
         <is>
-          <t>KJ7552</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D413" s="7" t="n">
-        <v>975</v>
+        <v>6999</v>
       </c>
       <c r="E413" s="8" t="n"/>
       <c r="F413" s="8" t="n"/>
@@ -12683,21 +12660,21 @@
     <row r="414" ht="14" customHeight="1">
       <c r="A414" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B414" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C414" s="6" t="inlineStr">
         <is>
-          <t>KK0030</t>
+          <t>KZ9163</t>
         </is>
       </c>
       <c r="D414" s="7" t="n">
-        <v>493</v>
+        <v>2034</v>
       </c>
       <c r="E414" s="8" t="n"/>
       <c r="F414" s="8" t="n"/>
@@ -12713,21 +12690,21 @@
     <row r="415" ht="14" customHeight="1">
       <c r="A415" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>11C</t>
         </is>
       </c>
       <c r="B415" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C415" s="6" t="inlineStr">
         <is>
-          <t>KK0031</t>
+          <t>LA1814</t>
         </is>
       </c>
       <c r="D415" s="7" t="n">
-        <v>694</v>
+        <v>4305</v>
       </c>
       <c r="E415" s="8" t="n"/>
       <c r="F415" s="8" t="n"/>
@@ -12740,54 +12717,31 @@
         </is>
       </c>
     </row>
-    <row r="416" ht="14" customHeight="1">
-      <c r="A416" s="4" t="inlineStr">
-        <is>
-          <t>11B1</t>
-        </is>
-      </c>
-      <c r="B416" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C416" s="6" t="inlineStr">
-        <is>
-          <t>KK0036</t>
-        </is>
-      </c>
-      <c r="D416" s="7" t="n">
-        <v>472</v>
-      </c>
-      <c r="E416" s="8" t="n"/>
-      <c r="F416" s="8" t="n"/>
-      <c r="G416" s="8" t="n"/>
-      <c r="H416" s="9" t="n"/>
-      <c r="I416" s="9" t="n"/>
-      <c r="J416" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="416" ht="16" customHeight="1">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>── 12部 ──</t>
         </is>
       </c>
     </row>
     <row r="417" ht="14" customHeight="1">
       <c r="A417" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B417" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C417" s="6" t="inlineStr">
         <is>
-          <t>KK0037</t>
+          <t>HQ5208</t>
         </is>
       </c>
       <c r="D417" s="7" t="n">
-        <v>2450</v>
+        <v>3259</v>
       </c>
       <c r="E417" s="8" t="n"/>
       <c r="F417" s="8" t="n"/>
@@ -12803,21 +12757,21 @@
     <row r="418" ht="14" customHeight="1">
       <c r="A418" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B418" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C418" s="6" t="inlineStr">
         <is>
-          <t>KK2864</t>
+          <t>JI0182</t>
         </is>
       </c>
       <c r="D418" s="7" t="n">
-        <v>548</v>
+        <v>310</v>
       </c>
       <c r="E418" s="8" t="n"/>
       <c r="F418" s="8" t="n"/>
@@ -12833,21 +12787,21 @@
     <row r="419" ht="14" customHeight="1">
       <c r="A419" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B419" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C419" s="6" t="inlineStr">
         <is>
-          <t>KK2865</t>
+          <t>KH9907</t>
         </is>
       </c>
       <c r="D419" s="7" t="n">
-        <v>395</v>
+        <v>3315</v>
       </c>
       <c r="E419" s="8" t="n"/>
       <c r="F419" s="8" t="n"/>
@@ -12863,21 +12817,21 @@
     <row r="420" ht="14" customHeight="1">
       <c r="A420" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B420" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C420" s="6" t="inlineStr">
         <is>
-          <t>KK2871</t>
+          <t>KH9908</t>
         </is>
       </c>
       <c r="D420" s="7" t="n">
-        <v>442</v>
+        <v>800</v>
       </c>
       <c r="E420" s="8" t="n"/>
       <c r="F420" s="8" t="n"/>
@@ -12893,21 +12847,21 @@
     <row r="421" ht="14" customHeight="1">
       <c r="A421" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B421" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C421" s="6" t="inlineStr">
         <is>
-          <t>LA3432</t>
+          <t>KH9909</t>
         </is>
       </c>
       <c r="D421" s="7" t="n">
-        <v>664</v>
+        <v>215</v>
       </c>
       <c r="E421" s="8" t="n"/>
       <c r="F421" s="8" t="n"/>
@@ -12923,21 +12877,21 @@
     <row r="422" ht="14" customHeight="1">
       <c r="A422" s="4" t="inlineStr">
         <is>
-          <t>11B1</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B422" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C422" s="6" t="inlineStr">
         <is>
-          <t>LA3433</t>
+          <t>KI9853</t>
         </is>
       </c>
       <c r="D422" s="7" t="n">
-        <v>5111</v>
+        <v>371</v>
       </c>
       <c r="E422" s="8" t="n"/>
       <c r="F422" s="8" t="n"/>
@@ -12950,31 +12904,54 @@
         </is>
       </c>
     </row>
-    <row r="423" ht="16" customHeight="1">
-      <c r="A423" s="3" t="inlineStr">
-        <is>
-          <t>── 11部 (2) ──</t>
+    <row r="423" ht="14" customHeight="1">
+      <c r="A423" s="4" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
+      <c r="B423" s="5" t="inlineStr">
+        <is>
+          <t>1609ER RS</t>
+        </is>
+      </c>
+      <c r="C423" s="6" t="inlineStr">
+        <is>
+          <t>KI9855</t>
+        </is>
+      </c>
+      <c r="D423" s="7" t="n">
+        <v>886</v>
+      </c>
+      <c r="E423" s="8" t="n"/>
+      <c r="F423" s="8" t="n"/>
+      <c r="G423" s="8" t="n"/>
+      <c r="H423" s="9" t="n"/>
+      <c r="I423" s="9" t="n"/>
+      <c r="J423" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="424" ht="14" customHeight="1">
       <c r="A424" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B424" s="5" t="inlineStr">
         <is>
-          <t>SAMBA J</t>
+          <t>1609ER RS</t>
         </is>
       </c>
       <c r="C424" s="6" t="inlineStr">
         <is>
-          <t>IF1944</t>
+          <t>KI9860</t>
         </is>
       </c>
       <c r="D424" s="7" t="n">
-        <v>3405</v>
+        <v>800</v>
       </c>
       <c r="E424" s="8" t="n"/>
       <c r="F424" s="8" t="n"/>
@@ -12990,21 +12967,21 @@
     <row r="425" ht="14" customHeight="1">
       <c r="A425" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12A</t>
         </is>
       </c>
       <c r="B425" s="5" t="inlineStr">
         <is>
-          <t>SAMBA J</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C425" s="6" t="inlineStr">
         <is>
-          <t>IF1945</t>
+          <t>KJ7510</t>
         </is>
       </c>
       <c r="D425" s="7" t="n">
-        <v>2673</v>
+        <v>6000</v>
       </c>
       <c r="E425" s="8" t="n"/>
       <c r="F425" s="8" t="n"/>
@@ -13020,21 +12997,21 @@
     <row r="426" ht="14" customHeight="1">
       <c r="A426" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B426" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 BOA</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C426" s="6" t="inlineStr">
         <is>
-          <t>JQ3463</t>
+          <t>HQ7468</t>
         </is>
       </c>
       <c r="D426" s="7" t="n">
-        <v>3274</v>
+        <v>7697</v>
       </c>
       <c r="E426" s="8" t="n"/>
       <c r="F426" s="8" t="n"/>
@@ -13050,21 +13027,21 @@
     <row r="427" ht="14" customHeight="1">
       <c r="A427" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B427" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 BOA</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C427" s="6" t="inlineStr">
         <is>
-          <t>KK2866</t>
+          <t>KJ7895</t>
         </is>
       </c>
       <c r="D427" s="7" t="n">
-        <v>1084</v>
+        <v>1467</v>
       </c>
       <c r="E427" s="8" t="n"/>
       <c r="F427" s="8" t="n"/>
@@ -13080,21 +13057,21 @@
     <row r="428" ht="14" customHeight="1">
       <c r="A428" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12C</t>
         </is>
       </c>
       <c r="B428" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 BOA</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C428" s="6" t="inlineStr">
         <is>
-          <t>KK2867</t>
+          <t>KZ9155</t>
         </is>
       </c>
       <c r="D428" s="7" t="n">
-        <v>62</v>
+        <v>4359</v>
       </c>
       <c r="E428" s="8" t="n"/>
       <c r="F428" s="8" t="n"/>
@@ -13110,21 +13087,21 @@
     <row r="429" ht="14" customHeight="1">
       <c r="A429" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B429" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 BOA</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="C429" s="6" t="inlineStr">
         <is>
-          <t>KK2868</t>
+          <t>HQ7468</t>
         </is>
       </c>
       <c r="D429" s="7" t="n">
-        <v>1989</v>
+        <v>9667</v>
       </c>
       <c r="E429" s="8" t="n"/>
       <c r="F429" s="8" t="n"/>
@@ -13140,21 +13117,21 @@
     <row r="430" ht="14" customHeight="1">
       <c r="A430" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B430" s="5" t="inlineStr">
         <is>
-          <t>S2G 26 BOA</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C430" s="6" t="inlineStr">
         <is>
-          <t>KK2869</t>
+          <t>KZ6450</t>
         </is>
       </c>
       <c r="D430" s="7" t="n">
-        <v>32</v>
+        <v>2586</v>
       </c>
       <c r="E430" s="8" t="n"/>
       <c r="F430" s="8" t="n"/>
@@ -13170,21 +13147,21 @@
     <row r="431" ht="14" customHeight="1">
       <c r="A431" s="4" t="inlineStr">
         <is>
-          <t>11B2</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B431" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C431" s="6" t="inlineStr">
         <is>
-          <t>KZ9155</t>
+          <t>KZ9161</t>
         </is>
       </c>
       <c r="D431" s="7" t="n">
-        <v>4929</v>
+        <v>860</v>
       </c>
       <c r="E431" s="8" t="n"/>
       <c r="F431" s="8" t="n"/>
@@ -13200,21 +13177,21 @@
     <row r="432" ht="14" customHeight="1">
       <c r="A432" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B432" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C432" s="6" t="inlineStr">
         <is>
-          <t>JR4790</t>
+          <t>KZ9163</t>
         </is>
       </c>
       <c r="D432" s="7" t="n">
-        <v>4659</v>
+        <v>1475</v>
       </c>
       <c r="E432" s="8" t="n"/>
       <c r="F432" s="8" t="n"/>
@@ -13230,21 +13207,21 @@
     <row r="433" ht="14" customHeight="1">
       <c r="A433" s="4" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B433" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="C433" s="6" t="inlineStr">
         <is>
-          <t>KZ6449</t>
+          <t>KZ9344</t>
         </is>
       </c>
       <c r="D433" s="7" t="n">
-        <v>4394</v>
+        <v>5000</v>
       </c>
       <c r="E433" s="8" t="n"/>
       <c r="F433" s="8" t="n"/>
@@ -13257,54 +13234,27 @@
         </is>
       </c>
     </row>
-    <row r="434" ht="14" customHeight="1">
-      <c r="A434" s="4" t="inlineStr">
-        <is>
-          <t>11C</t>
-        </is>
-      </c>
-      <c r="B434" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0</t>
-        </is>
-      </c>
-      <c r="C434" s="6" t="inlineStr">
-        <is>
-          <t>KZ9155</t>
-        </is>
-      </c>
-      <c r="D434" s="7" t="n">
-        <v>6999</v>
-      </c>
-      <c r="E434" s="8" t="n"/>
-      <c r="F434" s="8" t="n"/>
-      <c r="G434" s="8" t="n"/>
-      <c r="H434" s="9" t="n"/>
-      <c r="I434" s="9" t="n"/>
-      <c r="J434" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="434" ht="16" customHeight="1">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>── 外包  (永好) ──</t>
         </is>
       </c>
     </row>
     <row r="435" ht="14" customHeight="1">
-      <c r="A435" s="4" t="inlineStr">
-        <is>
-          <t>11C</t>
-        </is>
-      </c>
+      <c r="A435" s="11" t="inlineStr"/>
       <c r="B435" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C435" s="6" t="inlineStr">
         <is>
-          <t>KZ9163</t>
+          <t>IH6000</t>
         </is>
       </c>
       <c r="D435" s="7" t="n">
-        <v>5267</v>
+        <v>8068</v>
       </c>
       <c r="E435" s="8" t="n"/>
       <c r="F435" s="8" t="n"/>
@@ -13318,23 +13268,19 @@
       </c>
     </row>
     <row r="436" ht="14" customHeight="1">
-      <c r="A436" s="4" t="inlineStr">
-        <is>
-          <t>11C</t>
-        </is>
-      </c>
+      <c r="A436" s="11" t="inlineStr"/>
       <c r="B436" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C436" s="6" t="inlineStr">
         <is>
-          <t>LA1814</t>
+          <t>IH6001</t>
         </is>
       </c>
       <c r="D436" s="7" t="n">
-        <v>4305</v>
+        <v>16251</v>
       </c>
       <c r="E436" s="8" t="n"/>
       <c r="F436" s="8" t="n"/>
@@ -13347,31 +13293,46 @@
         </is>
       </c>
     </row>
-    <row r="437" ht="16" customHeight="1">
-      <c r="A437" s="3" t="inlineStr">
-        <is>
-          <t>── 12部 ──</t>
+    <row r="437" ht="14" customHeight="1">
+      <c r="A437" s="11" t="inlineStr"/>
+      <c r="B437" s="5" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J</t>
+        </is>
+      </c>
+      <c r="C437" s="6" t="inlineStr">
+        <is>
+          <t>KJ7844</t>
+        </is>
+      </c>
+      <c r="D437" s="7" t="n">
+        <v>800</v>
+      </c>
+      <c r="E437" s="8" t="n"/>
+      <c r="F437" s="8" t="n"/>
+      <c r="G437" s="8" t="n"/>
+      <c r="H437" s="9" t="n"/>
+      <c r="I437" s="9" t="n"/>
+      <c r="J437" s="10" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
     <row r="438" ht="14" customHeight="1">
-      <c r="A438" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A438" s="11" t="inlineStr"/>
       <c r="B438" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C438" s="6" t="inlineStr">
         <is>
-          <t>HQ5207</t>
+          <t>KJ7845</t>
         </is>
       </c>
       <c r="D438" s="7" t="n">
-        <v>5921</v>
+        <v>600</v>
       </c>
       <c r="E438" s="8" t="n"/>
       <c r="F438" s="8" t="n"/>
@@ -13385,23 +13346,19 @@
       </c>
     </row>
     <row r="439" ht="14" customHeight="1">
-      <c r="A439" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A439" s="11" t="inlineStr"/>
       <c r="B439" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C439" s="6" t="inlineStr">
         <is>
-          <t>HQ5208</t>
+          <t>KK4234</t>
         </is>
       </c>
       <c r="D439" s="7" t="n">
-        <v>3259</v>
+        <v>1743</v>
       </c>
       <c r="E439" s="8" t="n"/>
       <c r="F439" s="8" t="n"/>
@@ -13415,23 +13372,19 @@
       </c>
     </row>
     <row r="440" ht="14" customHeight="1">
-      <c r="A440" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A440" s="11" t="inlineStr"/>
       <c r="B440" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="C440" s="6" t="inlineStr">
         <is>
-          <t>HQ5209</t>
+          <t>KZ6449</t>
         </is>
       </c>
       <c r="D440" s="7" t="n">
-        <v>4458</v>
+        <v>16130</v>
       </c>
       <c r="E440" s="8" t="n"/>
       <c r="F440" s="8" t="n"/>
@@ -13444,54 +13397,27 @@
         </is>
       </c>
     </row>
-    <row r="441" ht="14" customHeight="1">
-      <c r="A441" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
-      <c r="B441" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C441" s="6" t="inlineStr">
-        <is>
-          <t>JI0182</t>
-        </is>
-      </c>
-      <c r="D441" s="7" t="n">
-        <v>310</v>
-      </c>
-      <c r="E441" s="8" t="n"/>
-      <c r="F441" s="8" t="n"/>
-      <c r="G441" s="8" t="n"/>
-      <c r="H441" s="9" t="n"/>
-      <c r="I441" s="9" t="n"/>
-      <c r="J441" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
+    <row r="441" ht="16" customHeight="1">
+      <c r="A441" s="3" t="inlineStr">
+        <is>
+          <t>── lay ra ──</t>
         </is>
       </c>
     </row>
     <row r="442" ht="14" customHeight="1">
-      <c r="A442" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A442" s="11" t="inlineStr"/>
       <c r="B442" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>RETROCROSS 25</t>
         </is>
       </c>
       <c r="C442" s="6" t="inlineStr">
         <is>
-          <t>KH9907</t>
+          <t>IH3396</t>
         </is>
       </c>
       <c r="D442" s="7" t="n">
-        <v>5180</v>
+        <v>1280</v>
       </c>
       <c r="E442" s="8" t="n"/>
       <c r="F442" s="8" t="n"/>
@@ -13505,23 +13431,19 @@
       </c>
     </row>
     <row r="443" ht="14" customHeight="1">
-      <c r="A443" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A443" s="11" t="inlineStr"/>
       <c r="B443" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>SAMBA</t>
         </is>
       </c>
       <c r="C443" s="6" t="inlineStr">
         <is>
-          <t>KH9908</t>
+          <t>IH6001</t>
         </is>
       </c>
       <c r="D443" s="7" t="n">
-        <v>1108</v>
+        <v>85282</v>
       </c>
       <c r="E443" s="8" t="n"/>
       <c r="F443" s="8" t="n"/>
@@ -13535,23 +13457,19 @@
       </c>
     </row>
     <row r="444" ht="14" customHeight="1">
-      <c r="A444" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A444" s="11" t="inlineStr"/>
       <c r="B444" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>RETROCROSS 25</t>
         </is>
       </c>
       <c r="C444" s="6" t="inlineStr">
         <is>
-          <t>KH9909</t>
+          <t>IH9978</t>
         </is>
       </c>
       <c r="D444" s="7" t="n">
-        <v>215</v>
+        <v>3001</v>
       </c>
       <c r="E444" s="8" t="n"/>
       <c r="F444" s="8" t="n"/>
@@ -13565,23 +13483,19 @@
       </c>
     </row>
     <row r="445" ht="14" customHeight="1">
-      <c r="A445" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A445" s="11" t="inlineStr"/>
       <c r="B445" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>RETROCROSS 25</t>
         </is>
       </c>
       <c r="C445" s="6" t="inlineStr">
         <is>
-          <t>KI9853</t>
+          <t>JP8521</t>
         </is>
       </c>
       <c r="D445" s="7" t="n">
-        <v>371</v>
+        <v>50</v>
       </c>
       <c r="E445" s="8" t="n"/>
       <c r="F445" s="8" t="n"/>
@@ -13595,23 +13509,19 @@
       </c>
     </row>
     <row r="446" ht="14" customHeight="1">
-      <c r="A446" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A446" s="11" t="inlineStr"/>
       <c r="B446" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="C446" s="6" t="inlineStr">
         <is>
-          <t>KI9855</t>
+          <t>JQ0598</t>
         </is>
       </c>
       <c r="D446" s="7" t="n">
-        <v>886</v>
+        <v>3870</v>
       </c>
       <c r="E446" s="8" t="n"/>
       <c r="F446" s="8" t="n"/>
@@ -13625,23 +13535,19 @@
       </c>
     </row>
     <row r="447" ht="14" customHeight="1">
-      <c r="A447" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
+      <c r="A447" s="11" t="inlineStr"/>
       <c r="B447" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>MEGARIDE F50</t>
         </is>
       </c>
       <c r="C447" s="6" t="inlineStr">
         <is>
-          <t>KI9857</t>
+          <t>KI4741</t>
         </is>
       </c>
       <c r="D447" s="7" t="n">
-        <v>790</v>
+        <v>159</v>
       </c>
       <c r="E447" s="8" t="n"/>
       <c r="F447" s="8" t="n"/>
@@ -13654,844 +13560,8 @@
         </is>
       </c>
     </row>
-    <row r="448" ht="14" customHeight="1">
-      <c r="A448" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
-      <c r="B448" s="5" t="inlineStr">
-        <is>
-          <t>1609ER RS</t>
-        </is>
-      </c>
-      <c r="C448" s="6" t="inlineStr">
-        <is>
-          <t>KI9860</t>
-        </is>
-      </c>
-      <c r="D448" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="E448" s="8" t="n"/>
-      <c r="F448" s="8" t="n"/>
-      <c r="G448" s="8" t="n"/>
-      <c r="H448" s="9" t="n"/>
-      <c r="I448" s="9" t="n"/>
-      <c r="J448" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="449" ht="14" customHeight="1">
-      <c r="A449" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
-      <c r="B449" s="5" t="inlineStr">
-        <is>
-          <t>1609ER RS</t>
-        </is>
-      </c>
-      <c r="C449" s="6" t="inlineStr">
-        <is>
-          <t>KI9861</t>
-        </is>
-      </c>
-      <c r="D449" s="7" t="n">
-        <v>345</v>
-      </c>
-      <c r="E449" s="8" t="n"/>
-      <c r="F449" s="8" t="n"/>
-      <c r="G449" s="8" t="n"/>
-      <c r="H449" s="9" t="n"/>
-      <c r="I449" s="9" t="n"/>
-      <c r="J449" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="450" ht="14" customHeight="1">
-      <c r="A450" s="4" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
-      <c r="B450" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C450" s="6" t="inlineStr">
-        <is>
-          <t>KJ7510</t>
-        </is>
-      </c>
-      <c r="D450" s="7" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E450" s="8" t="n"/>
-      <c r="F450" s="8" t="n"/>
-      <c r="G450" s="8" t="n"/>
-      <c r="H450" s="9" t="n"/>
-      <c r="I450" s="9" t="n"/>
-      <c r="J450" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="451" ht="14" customHeight="1">
-      <c r="A451" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B451" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0</t>
-        </is>
-      </c>
-      <c r="C451" s="6" t="inlineStr">
-        <is>
-          <t>HQ7468</t>
-        </is>
-      </c>
-      <c r="D451" s="7" t="n">
-        <v>8981</v>
-      </c>
-      <c r="E451" s="8" t="n"/>
-      <c r="F451" s="8" t="n"/>
-      <c r="G451" s="8" t="n"/>
-      <c r="H451" s="9" t="n"/>
-      <c r="I451" s="9" t="n"/>
-      <c r="J451" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="452" ht="14" customHeight="1">
-      <c r="A452" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B452" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C452" s="6" t="inlineStr">
-        <is>
-          <t>KJ7893</t>
-        </is>
-      </c>
-      <c r="D452" s="7" t="n">
-        <v>851</v>
-      </c>
-      <c r="E452" s="8" t="n"/>
-      <c r="F452" s="8" t="n"/>
-      <c r="G452" s="8" t="n"/>
-      <c r="H452" s="9" t="n"/>
-      <c r="I452" s="9" t="n"/>
-      <c r="J452" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="453" ht="14" customHeight="1">
-      <c r="A453" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B453" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0</t>
-        </is>
-      </c>
-      <c r="C453" s="6" t="inlineStr">
-        <is>
-          <t>KJ7895</t>
-        </is>
-      </c>
-      <c r="D453" s="7" t="n">
-        <v>4231</v>
-      </c>
-      <c r="E453" s="8" t="n"/>
-      <c r="F453" s="8" t="n"/>
-      <c r="G453" s="8" t="n"/>
-      <c r="H453" s="9" t="n"/>
-      <c r="I453" s="9" t="n"/>
-      <c r="J453" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="454" ht="14" customHeight="1">
-      <c r="A454" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B454" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C454" s="6" t="inlineStr">
-        <is>
-          <t>KZ6449</t>
-        </is>
-      </c>
-      <c r="D454" s="7" t="n">
-        <v>12202</v>
-      </c>
-      <c r="E454" s="8" t="n"/>
-      <c r="F454" s="8" t="n"/>
-      <c r="G454" s="8" t="n"/>
-      <c r="H454" s="9" t="n"/>
-      <c r="I454" s="9" t="n"/>
-      <c r="J454" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="455" ht="14" customHeight="1">
-      <c r="A455" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B455" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0</t>
-        </is>
-      </c>
-      <c r="C455" s="6" t="inlineStr">
-        <is>
-          <t>KZ9155</t>
-        </is>
-      </c>
-      <c r="D455" s="7" t="n">
-        <v>5880</v>
-      </c>
-      <c r="E455" s="8" t="n"/>
-      <c r="F455" s="8" t="n"/>
-      <c r="G455" s="8" t="n"/>
-      <c r="H455" s="9" t="n"/>
-      <c r="I455" s="9" t="n"/>
-      <c r="J455" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="456" ht="14" customHeight="1">
-      <c r="A456" s="4" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B456" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C456" s="6" t="inlineStr">
-        <is>
-          <t>LA1814</t>
-        </is>
-      </c>
-      <c r="D456" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E456" s="8" t="n"/>
-      <c r="F456" s="8" t="n"/>
-      <c r="G456" s="8" t="n"/>
-      <c r="H456" s="9" t="n"/>
-      <c r="I456" s="9" t="n"/>
-      <c r="J456" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="457" ht="14" customHeight="1">
-      <c r="A457" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B457" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0</t>
-        </is>
-      </c>
-      <c r="C457" s="6" t="inlineStr">
-        <is>
-          <t>HQ7468</t>
-        </is>
-      </c>
-      <c r="D457" s="7" t="n">
-        <v>14417</v>
-      </c>
-      <c r="E457" s="8" t="n"/>
-      <c r="F457" s="8" t="n"/>
-      <c r="G457" s="8" t="n"/>
-      <c r="H457" s="9" t="n"/>
-      <c r="I457" s="9" t="n"/>
-      <c r="J457" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="458" ht="14" customHeight="1">
-      <c r="A458" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B458" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C458" s="6" t="inlineStr">
-        <is>
-          <t>KJ7893</t>
-        </is>
-      </c>
-      <c r="D458" s="7" t="n">
-        <v>3696</v>
-      </c>
-      <c r="E458" s="8" t="n"/>
-      <c r="F458" s="8" t="n"/>
-      <c r="G458" s="8" t="n"/>
-      <c r="H458" s="9" t="n"/>
-      <c r="I458" s="9" t="n"/>
-      <c r="J458" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="459" ht="14" customHeight="1">
-      <c r="A459" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B459" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C459" s="6" t="inlineStr">
-        <is>
-          <t>KZ6450</t>
-        </is>
-      </c>
-      <c r="D459" s="7" t="n">
-        <v>2586</v>
-      </c>
-      <c r="E459" s="8" t="n"/>
-      <c r="F459" s="8" t="n"/>
-      <c r="G459" s="8" t="n"/>
-      <c r="H459" s="9" t="n"/>
-      <c r="I459" s="9" t="n"/>
-      <c r="J459" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="460" ht="14" customHeight="1">
-      <c r="A460" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B460" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="C460" s="6" t="inlineStr">
-        <is>
-          <t>KZ9161</t>
-        </is>
-      </c>
-      <c r="D460" s="7" t="n">
-        <v>1435</v>
-      </c>
-      <c r="E460" s="8" t="n"/>
-      <c r="F460" s="8" t="n"/>
-      <c r="G460" s="8" t="n"/>
-      <c r="H460" s="9" t="n"/>
-      <c r="I460" s="9" t="n"/>
-      <c r="J460" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="461" ht="14" customHeight="1">
-      <c r="A461" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B461" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="C461" s="6" t="inlineStr">
-        <is>
-          <t>KZ9162</t>
-        </is>
-      </c>
-      <c r="D461" s="7" t="n">
-        <v>4799</v>
-      </c>
-      <c r="E461" s="8" t="n"/>
-      <c r="F461" s="8" t="n"/>
-      <c r="G461" s="8" t="n"/>
-      <c r="H461" s="9" t="n"/>
-      <c r="I461" s="9" t="n"/>
-      <c r="J461" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="462" ht="14" customHeight="1">
-      <c r="A462" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B462" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="C462" s="6" t="inlineStr">
-        <is>
-          <t>KZ9163</t>
-        </is>
-      </c>
-      <c r="D462" s="7" t="n">
-        <v>2334</v>
-      </c>
-      <c r="E462" s="8" t="n"/>
-      <c r="F462" s="8" t="n"/>
-      <c r="G462" s="8" t="n"/>
-      <c r="H462" s="9" t="n"/>
-      <c r="I462" s="9" t="n"/>
-      <c r="J462" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="463" ht="14" customHeight="1">
-      <c r="A463" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B463" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="C463" s="6" t="inlineStr">
-        <is>
-          <t>KZ9344</t>
-        </is>
-      </c>
-      <c r="D463" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E463" s="8" t="n"/>
-      <c r="F463" s="8" t="n"/>
-      <c r="G463" s="8" t="n"/>
-      <c r="H463" s="9" t="n"/>
-      <c r="I463" s="9" t="n"/>
-      <c r="J463" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="464" ht="14" customHeight="1">
-      <c r="A464" s="4" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B464" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C464" s="6" t="inlineStr">
-        <is>
-          <t>LA1814</t>
-        </is>
-      </c>
-      <c r="D464" s="7" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E464" s="8" t="n"/>
-      <c r="F464" s="8" t="n"/>
-      <c r="G464" s="8" t="n"/>
-      <c r="H464" s="9" t="n"/>
-      <c r="I464" s="9" t="n"/>
-      <c r="J464" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="465" ht="16" customHeight="1">
-      <c r="A465" s="3" t="inlineStr">
-        <is>
-          <t>── 外包  (永好) ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="466" ht="14" customHeight="1">
-      <c r="A466" s="11" t="inlineStr"/>
-      <c r="B466" s="5" t="inlineStr">
-        <is>
-          <t>SAMBA</t>
-        </is>
-      </c>
-      <c r="C466" s="6" t="inlineStr">
-        <is>
-          <t>IH6000</t>
-        </is>
-      </c>
-      <c r="D466" s="7" t="n">
-        <v>8068</v>
-      </c>
-      <c r="E466" s="8" t="n"/>
-      <c r="F466" s="8" t="n"/>
-      <c r="G466" s="8" t="n"/>
-      <c r="H466" s="9" t="n"/>
-      <c r="I466" s="9" t="n"/>
-      <c r="J466" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="467" ht="14" customHeight="1">
-      <c r="A467" s="11" t="inlineStr"/>
-      <c r="B467" s="5" t="inlineStr">
-        <is>
-          <t>SAMBA</t>
-        </is>
-      </c>
-      <c r="C467" s="6" t="inlineStr">
-        <is>
-          <t>IH6001</t>
-        </is>
-      </c>
-      <c r="D467" s="7" t="n">
-        <v>16251</v>
-      </c>
-      <c r="E467" s="8" t="n"/>
-      <c r="F467" s="8" t="n"/>
-      <c r="G467" s="8" t="n"/>
-      <c r="H467" s="9" t="n"/>
-      <c r="I467" s="9" t="n"/>
-      <c r="J467" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="468" ht="14" customHeight="1">
-      <c r="A468" s="11" t="inlineStr"/>
-      <c r="B468" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C468" s="6" t="inlineStr">
-        <is>
-          <t>KJ7844</t>
-        </is>
-      </c>
-      <c r="D468" s="7" t="n">
-        <v>800</v>
-      </c>
-      <c r="E468" s="8" t="n"/>
-      <c r="F468" s="8" t="n"/>
-      <c r="G468" s="8" t="n"/>
-      <c r="H468" s="9" t="n"/>
-      <c r="I468" s="9" t="n"/>
-      <c r="J468" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="469" ht="14" customHeight="1">
-      <c r="A469" s="11" t="inlineStr"/>
-      <c r="B469" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C469" s="6" t="inlineStr">
-        <is>
-          <t>KJ7845</t>
-        </is>
-      </c>
-      <c r="D469" s="7" t="n">
-        <v>600</v>
-      </c>
-      <c r="E469" s="8" t="n"/>
-      <c r="F469" s="8" t="n"/>
-      <c r="G469" s="8" t="n"/>
-      <c r="H469" s="9" t="n"/>
-      <c r="I469" s="9" t="n"/>
-      <c r="J469" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="470" ht="14" customHeight="1">
-      <c r="A470" s="11" t="inlineStr"/>
-      <c r="B470" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C470" s="6" t="inlineStr">
-        <is>
-          <t>KK4234</t>
-        </is>
-      </c>
-      <c r="D470" s="7" t="n">
-        <v>1743</v>
-      </c>
-      <c r="E470" s="8" t="n"/>
-      <c r="F470" s="8" t="n"/>
-      <c r="G470" s="8" t="n"/>
-      <c r="H470" s="9" t="n"/>
-      <c r="I470" s="9" t="n"/>
-      <c r="J470" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="471" ht="14" customHeight="1">
-      <c r="A471" s="11" t="inlineStr"/>
-      <c r="B471" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J</t>
-        </is>
-      </c>
-      <c r="C471" s="6" t="inlineStr">
-        <is>
-          <t>KZ6449</t>
-        </is>
-      </c>
-      <c r="D471" s="7" t="n">
-        <v>16130</v>
-      </c>
-      <c r="E471" s="8" t="n"/>
-      <c r="F471" s="8" t="n"/>
-      <c r="G471" s="8" t="n"/>
-      <c r="H471" s="9" t="n"/>
-      <c r="I471" s="9" t="n"/>
-      <c r="J471" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="472" ht="16" customHeight="1">
-      <c r="A472" s="3" t="inlineStr">
-        <is>
-          <t>── lay ra ──</t>
-        </is>
-      </c>
-    </row>
-    <row r="473" ht="14" customHeight="1">
-      <c r="A473" s="11" t="inlineStr"/>
-      <c r="B473" s="5" t="inlineStr">
-        <is>
-          <t>RETROCROSS 25</t>
-        </is>
-      </c>
-      <c r="C473" s="6" t="inlineStr">
-        <is>
-          <t>IH3396</t>
-        </is>
-      </c>
-      <c r="D473" s="7" t="n">
-        <v>1280</v>
-      </c>
-      <c r="E473" s="8" t="n"/>
-      <c r="F473" s="8" t="n"/>
-      <c r="G473" s="8" t="n"/>
-      <c r="H473" s="9" t="n"/>
-      <c r="I473" s="9" t="n"/>
-      <c r="J473" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="474" ht="14" customHeight="1">
-      <c r="A474" s="11" t="inlineStr"/>
-      <c r="B474" s="5" t="inlineStr">
-        <is>
-          <t>SAMBA</t>
-        </is>
-      </c>
-      <c r="C474" s="6" t="inlineStr">
-        <is>
-          <t>IH6001</t>
-        </is>
-      </c>
-      <c r="D474" s="7" t="n">
-        <v>85282</v>
-      </c>
-      <c r="E474" s="8" t="n"/>
-      <c r="F474" s="8" t="n"/>
-      <c r="G474" s="8" t="n"/>
-      <c r="H474" s="9" t="n"/>
-      <c r="I474" s="9" t="n"/>
-      <c r="J474" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="475" ht="14" customHeight="1">
-      <c r="A475" s="11" t="inlineStr"/>
-      <c r="B475" s="5" t="inlineStr">
-        <is>
-          <t>RETROCROSS 25</t>
-        </is>
-      </c>
-      <c r="C475" s="6" t="inlineStr">
-        <is>
-          <t>IH9978</t>
-        </is>
-      </c>
-      <c r="D475" s="7" t="n">
-        <v>3001</v>
-      </c>
-      <c r="E475" s="8" t="n"/>
-      <c r="F475" s="8" t="n"/>
-      <c r="G475" s="8" t="n"/>
-      <c r="H475" s="9" t="n"/>
-      <c r="I475" s="9" t="n"/>
-      <c r="J475" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="476" ht="14" customHeight="1">
-      <c r="A476" s="11" t="inlineStr"/>
-      <c r="B476" s="5" t="inlineStr">
-        <is>
-          <t>RETROCROSS 25</t>
-        </is>
-      </c>
-      <c r="C476" s="6" t="inlineStr">
-        <is>
-          <t>JP8521</t>
-        </is>
-      </c>
-      <c r="D476" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="E476" s="8" t="n"/>
-      <c r="F476" s="8" t="n"/>
-      <c r="G476" s="8" t="n"/>
-      <c r="H476" s="9" t="n"/>
-      <c r="I476" s="9" t="n"/>
-      <c r="J476" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="477" ht="14" customHeight="1">
-      <c r="A477" s="11" t="inlineStr"/>
-      <c r="B477" s="5" t="inlineStr">
-        <is>
-          <t>TOKYO W</t>
-        </is>
-      </c>
-      <c r="C477" s="6" t="inlineStr">
-        <is>
-          <t>JQ0598</t>
-        </is>
-      </c>
-      <c r="D477" s="7" t="n">
-        <v>3870</v>
-      </c>
-      <c r="E477" s="8" t="n"/>
-      <c r="F477" s="8" t="n"/>
-      <c r="G477" s="8" t="n"/>
-      <c r="H477" s="9" t="n"/>
-      <c r="I477" s="9" t="n"/>
-      <c r="J477" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="478" ht="14" customHeight="1">
-      <c r="A478" s="11" t="inlineStr"/>
-      <c r="B478" s="5" t="inlineStr">
-        <is>
-          <t>MEGARIDE F50</t>
-        </is>
-      </c>
-      <c r="C478" s="6" t="inlineStr">
-        <is>
-          <t>KI4741</t>
-        </is>
-      </c>
-      <c r="D478" s="7" t="n">
-        <v>159</v>
-      </c>
-      <c r="E478" s="8" t="n"/>
-      <c r="F478" s="8" t="n"/>
-      <c r="G478" s="8" t="n"/>
-      <c r="H478" s="9" t="n"/>
-      <c r="I478" s="9" t="n"/>
-      <c r="J478" s="10" t="inlineStr">
-        <is>
-          <t>?</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" s="12" t="inlineStr">
+    <row r="449">
+      <c r="A449" s="12" t="inlineStr">
         <is>
           <t>＊ 紅色欄位 = MP 邏輯待確認（Jim 定義後更新）</t>
         </is>
@@ -14499,23 +13569,23 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A472:J472"/>
+    <mergeCell ref="A217:J217"/>
     <mergeCell ref="A99:J99"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A133:J133"/>
-    <mergeCell ref="A291:J291"/>
-    <mergeCell ref="A187:J187"/>
-    <mergeCell ref="A480:J480"/>
+    <mergeCell ref="A449:J449"/>
+    <mergeCell ref="A315:J315"/>
+    <mergeCell ref="A167:J167"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A253:J253"/>
-    <mergeCell ref="A373:J373"/>
-    <mergeCell ref="A465:J465"/>
-    <mergeCell ref="A172:J172"/>
+    <mergeCell ref="A243:J243"/>
+    <mergeCell ref="A352:J352"/>
+    <mergeCell ref="A441:J441"/>
+    <mergeCell ref="A434:J434"/>
+    <mergeCell ref="A416:J416"/>
+    <mergeCell ref="A402:J402"/>
     <mergeCell ref="A54:J54"/>
-    <mergeCell ref="A437:J437"/>
-    <mergeCell ref="A331:J331"/>
-    <mergeCell ref="A222:J222"/>
-    <mergeCell ref="A423:J423"/>
+    <mergeCell ref="A182:J182"/>
+    <mergeCell ref="A280:J280"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22445,7 +21515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -22486,7 +21556,7 @@
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
-          <t>▼ 進度表有 但 廠務編制表無  (47 個 ART)</t>
+          <t>▼ 進度表有 但 廠務編制表無  (41 個 ART)</t>
         </is>
       </c>
     </row>
@@ -22872,12 +21942,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KI9857</t>
+          <t>KI9862</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -22894,12 +21964,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>KI9861</t>
+          <t>KJ0851</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>1609ER RS</t>
+          <t>SPEZIAL GOLF</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -22916,12 +21986,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>KI9862</t>
+          <t>KJ2282</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>SL 72 OG W</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -22938,12 +22008,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>KJ0851</t>
+          <t>KJ5430</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -22960,12 +22030,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>KJ0852</t>
+          <t>KJ5431</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -22982,12 +22052,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>KJ2282</t>
+          <t>KJ7844</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>SL 72 OG W</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -23004,12 +22074,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>KJ5430</t>
+          <t>KJ7845</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -23026,12 +22096,12 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>KJ5431</t>
+          <t>KJ7893</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>ADISTAR XLG 2.0 J</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -23048,12 +22118,12 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>KJ7844</t>
+          <t>KJ8225</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>SAMBA GOLF</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -23070,12 +22140,12 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>KJ7845</t>
+          <t>KJ8322</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>ORGN ULTRA TECH</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -23092,12 +22162,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>KJ7893</t>
+          <t>KJ8377</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J</t>
+          <t>TOKYO MJ W</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -23114,12 +22184,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>KJ8225</t>
+          <t>KK2621</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>SAMBA GOLF</t>
+          <t>TOKYO W</t>
         </is>
       </c>
       <c r="D32" s="21" t="inlineStr">
@@ -23136,12 +22206,12 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>KJ8322</t>
+          <t>KK2839</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>ORGN ULTRA TECH</t>
+          <t>ADIPOWER 26 SL BOA</t>
         </is>
       </c>
       <c r="D33" s="21" t="inlineStr">
@@ -23158,12 +22228,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>KJ8377</t>
+          <t>KK2864</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>TOKYO MJ W</t>
+          <t>W S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="D34" s="21" t="inlineStr">
@@ -23180,12 +22250,12 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>KK2621</t>
+          <t>KK2865</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>TOKYO W</t>
+          <t>W S2G 26 LEATHER</t>
         </is>
       </c>
       <c r="D35" s="21" t="inlineStr">
@@ -23202,12 +22272,12 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>KK2839</t>
+          <t>KK2904</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="D36" s="21" t="inlineStr">
@@ -23224,12 +22294,12 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>KK2864</t>
+          <t>KK3018</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="D37" s="21" t="inlineStr">
@@ -23246,12 +22316,12 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>KK2865</t>
+          <t>KZ8301</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER</t>
+          <t>ADISTAR XLG 2.0</t>
         </is>
       </c>
       <c r="D38" s="21" t="inlineStr">
@@ -23268,7 +22338,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>KK2904</t>
+          <t>KZ9161</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -23290,12 +22360,12 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>KK3017</t>
+          <t>KZ9162</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="D40" s="21" t="inlineStr">
@@ -23312,12 +22382,12 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>KK3018</t>
+          <t>KZ9163</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="D41" s="21" t="inlineStr">
@@ -23334,12 +22404,12 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>KK3033</t>
+          <t>LA0522</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
+          <t>ADISTAR XLG 2.0 W</t>
         </is>
       </c>
       <c r="D42" s="21" t="inlineStr">
@@ -23356,12 +22426,12 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>KZ8301</t>
+          <t>LA3255</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0</t>
+          <t>HANDBALL SPEZIAL</t>
         </is>
       </c>
       <c r="D43" s="21" t="inlineStr">
@@ -23378,12 +22448,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>KZ9161</t>
+          <t>LA3614</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
+          <t>F50 TUNIT MEGA JAH JAH</t>
         </is>
       </c>
       <c r="D44" s="21" t="inlineStr">
@@ -23392,142 +22462,142 @@
         </is>
       </c>
     </row>
-    <row r="45" ht="14" customHeight="1">
-      <c r="A45" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>KZ9162</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="D45" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="14" customHeight="1">
-      <c r="A46" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>KZ9163</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="D46" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>▼ 廠務編制表有 但 進度表無  (11 個 ART)</t>
         </is>
       </c>
     </row>
     <row r="47" ht="14" customHeight="1">
-      <c r="A47" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>LA0522</t>
+          <t>HP5124</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W</t>
-        </is>
-      </c>
-      <c r="D47" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
+          <t>[5C] SL 72 ADITEX ( HP5124 , HP5123 )- 外包鞋面</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
         </is>
       </c>
     </row>
     <row r="48" ht="14" customHeight="1">
-      <c r="A48" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>LA1750</t>
+          <t>HQ5207</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>SL 72 RS</t>
-        </is>
-      </c>
-      <c r="D48" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
+          <t xml:space="preserve">[12A] 1609ER RS  ( KH9907 , KH9908 , KI9860 , </t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
         </is>
       </c>
     </row>
     <row r="49" ht="14" customHeight="1">
-      <c r="A49" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>LA3255</t>
+          <t>HQ5209</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL</t>
-        </is>
-      </c>
-      <c r="D49" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
+          <t xml:space="preserve">[12A] 1609ER RS  ( KH9907 , KH9908 , KI9860 , </t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
         </is>
       </c>
     </row>
     <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="20" t="inlineStr">
-        <is>
-          <t>進度表有/編制表無</t>
+      <c r="A50" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>LA3614</t>
+          <t>JI0183</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>F50 TUNIT MEGA JAH JAH</t>
-        </is>
-      </c>
-      <c r="D50" s="21" t="inlineStr">
-        <is>
-          <t>請確認是否需加入編制表</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="22" t="inlineStr">
-        <is>
-          <t>▼ 廠務編制表有 但 進度表無  (1 個 ART)</t>
+          <t>[9B] TOKYO W ( JI0182  , KJ7510 , JI0183 )- 外</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>JS1068</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>[7A] GHOST SPRINT W ( JS1067 , JS1068, KI4563</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="14" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>KH9671</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[9C] SL 72 RS ( KH9671 , KH9673 , KH9672  )- </t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
         </is>
       </c>
     </row>
@@ -23539,15 +22609,103 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>JS1068</t>
+          <t>KH9672</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>[7A] GHOST SPRINT W ( JS1067 , JS1068, KI4563</t>
+          <t xml:space="preserve">[9C] SL 72 RS ( KH9671 , KH9673 , KH9672  )- </t>
         </is>
       </c>
       <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="14" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>KH9673</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[9C] SL 72 RS ( KH9671 , KH9673 , KH9672  )- </t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>KI5303</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>[10C] HANDBALL SPEZIAL ( KI5303 , KK3015 )- 外包</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="14" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>KJ7541</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>[7B] TOKYO W (KJ7541 )- 外包鞋面</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>確認是否已停產或改ART</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>編制表有/進度表無</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>KK3021</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>[10C] HANDBALL SPEZIAL ( KK3021 , KK3025 , KK3</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
         <is>
           <t>確認是否已停產或改ART</t>
         </is>
@@ -23556,8 +22714,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A46:D46"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A52:D52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
